--- a/预测分析.xlsx
+++ b/预测分析.xlsx
@@ -1,34 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE35E5B-AFC9-4B5C-86D6-1A32F9A184B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E716B92-2D12-4DD6-A0FE-9882B6320998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$C$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$X$186</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="562">
   <si>
     <t>晶圆</t>
   </si>
@@ -42,66 +51,21 @@
     <t>STC9D03E</t>
   </si>
   <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>2100-A-2100</t>
-  </si>
-  <si>
-    <t>2100HBL</t>
-  </si>
-  <si>
-    <t>NR.2100HBL-2100</t>
-  </si>
-  <si>
-    <t>2100S</t>
-  </si>
-  <si>
-    <t>2100S-2100</t>
-  </si>
-  <si>
-    <t>PSTC9D03E</t>
-  </si>
-  <si>
     <t>PSTC9D03E-4</t>
   </si>
   <si>
-    <t>SC4643SA-A</t>
-  </si>
-  <si>
-    <t>SC4643SA-A-4643</t>
-  </si>
-  <si>
     <t>SC4643SA-BK-Q</t>
   </si>
   <si>
     <t>SC4643SA-Q-DE-40HK-2100</t>
   </si>
   <si>
-    <t>SC4643VB</t>
-  </si>
-  <si>
-    <t>NR.SC4643VB-A-4643</t>
-  </si>
-  <si>
-    <t>SC4643VB-A-4643</t>
-  </si>
-  <si>
     <t>SC4643VB-2.5S</t>
   </si>
   <si>
     <t>SC4643VB-A-4643-2.5S</t>
   </si>
   <si>
-    <t>SC4643VB-A</t>
-  </si>
-  <si>
-    <t>NR.SC4643VB-A-FFH-L43</t>
-  </si>
-  <si>
-    <t>SC4643VB-A-FFH-L43</t>
-  </si>
-  <si>
     <t>SC4643VB-BK-Q</t>
   </si>
   <si>
@@ -111,27 +75,12 @@
     <t>SC4643VB-Q-DE-40CK-4643</t>
   </si>
   <si>
-    <t>SC4643VB-G</t>
-  </si>
-  <si>
-    <t>SC4643VB-G(STC9D03E)-4643</t>
-  </si>
-  <si>
     <t>SC4643VB-G-BK-Q</t>
   </si>
   <si>
     <t>SC4643VB-G-Q-DE-40CK-4643</t>
   </si>
   <si>
-    <t>SC4643VB-P</t>
-  </si>
-  <si>
-    <t>NR.SC4643VB-P(STC9D03E)-4643</t>
-  </si>
-  <si>
-    <t>SC4643VB-P(STC9D03E)-4643</t>
-  </si>
-  <si>
     <t>SC4643VB-P-2.5S</t>
   </si>
   <si>
@@ -144,12 +93,6 @@
     <t>SC4643VB-P-Q-DE-40CR-4643</t>
   </si>
   <si>
-    <t>SC4643VB-S</t>
-  </si>
-  <si>
-    <t>SC4643VB-S(STC9D03E)-4643</t>
-  </si>
-  <si>
     <t>SC4643VB-S-BK-Q</t>
   </si>
   <si>
@@ -177,36 +120,12 @@
     <t>STC9A001I</t>
   </si>
   <si>
-    <t>PSTC9A001I-1</t>
-  </si>
-  <si>
-    <t>SC9641TS-P</t>
-  </si>
-  <si>
-    <t>NR.SC9641TS-P-I(STC9A001I)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9641TS-P-I(STC9A001I)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9641TS-P-I（STC9A001I)-41CPA</t>
-  </si>
-  <si>
     <t>SC9641TS-P-BK</t>
   </si>
   <si>
     <t>SC9641TS-P-AI-10AK-41CPA</t>
   </si>
   <si>
-    <t>SC9641TS-PC</t>
-  </si>
-  <si>
-    <t>NR.SC9641TS-PC(STC9A001I)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9641TS-PC(STC9A001I)-41CPA</t>
-  </si>
-  <si>
     <t>SC9641TS-PC-BK-Q</t>
   </si>
   <si>
@@ -219,1185 +138,1694 @@
     <t>SC9641TS-PC-Q-AI-10LR-9641PC</t>
   </si>
   <si>
-    <t>SC9641TS-PC-Q-AI-10AR-9641PC</t>
-  </si>
-  <si>
     <t>SC9641TS-P-TR</t>
   </si>
   <si>
     <t>SC9641TS-P-AI-10AR-G1630</t>
   </si>
   <si>
+    <t>SC9641TS-P-AI-10AR-41CPA</t>
+  </si>
+  <si>
+    <t>SC9648TS-TR</t>
+  </si>
+  <si>
+    <t>SC9648TS-AI-10AR-9648</t>
+  </si>
+  <si>
+    <t>STC4011B</t>
+  </si>
+  <si>
+    <t>SC4011SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC4011SO-N-CB-90NR-49E</t>
+  </si>
+  <si>
+    <t>STC4011B-DS</t>
+  </si>
+  <si>
+    <t>STC9D01C</t>
+  </si>
+  <si>
+    <t>SC4688DC-TR-Q</t>
+  </si>
+  <si>
+    <t>SC4688DC-Q-DC-40CR-4688</t>
+  </si>
+  <si>
+    <t>SC4688SA-BK-Q</t>
+  </si>
+  <si>
+    <t>SC4688SA-Q-DC-40CK-4688</t>
+  </si>
+  <si>
+    <t>SC4688SA-Q-DC-40CK-888K</t>
+  </si>
+  <si>
+    <t>SC4688DC-TR</t>
+  </si>
+  <si>
+    <t>SC4688DC-DC-40AR-2425</t>
+  </si>
+  <si>
+    <t>SC1645A1-BK</t>
+  </si>
+  <si>
+    <t>SC1645B1-BK</t>
+  </si>
+  <si>
+    <t>STC9910BN</t>
+  </si>
+  <si>
+    <t>SC9641TS-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9641TS-Q-CB-10LR-9641</t>
+  </si>
+  <si>
+    <t>SC9641TS-362-Q-CB-10LR-9641</t>
+  </si>
+  <si>
+    <t>STC9A001H</t>
+  </si>
+  <si>
+    <t>SC9642TS-EC-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9642TS-EC-Q-AH-4XLR-9642</t>
+  </si>
+  <si>
+    <t>STC4011E</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-A-TR</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-A-CE-90NR-4015</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-4015</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-512</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-515</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-CY19</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-G01M</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-QX11</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-NM</t>
+  </si>
+  <si>
+    <t>STC4011E-DS</t>
+  </si>
+  <si>
+    <t>STC9906P</t>
+  </si>
+  <si>
+    <t>SC2442SO-N-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2442SO-N-Q-CP-10CR-2442</t>
+  </si>
+  <si>
+    <t>SC2442SO-N-Q-CP-10CR-2662</t>
+  </si>
+  <si>
+    <t>SC2442SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2442SO-N-CP-10CR-2442</t>
+  </si>
+  <si>
+    <t>STC1898AD</t>
+  </si>
+  <si>
+    <t>PSTC1898AD-0</t>
+  </si>
+  <si>
+    <t>PSTC1898AD</t>
+  </si>
+  <si>
+    <t>SC1245A1</t>
+  </si>
+  <si>
+    <t>SC1245A1-41F</t>
+  </si>
+  <si>
+    <t>SC1245B1</t>
+  </si>
+  <si>
+    <t>SC1245B1-41F</t>
+  </si>
+  <si>
+    <t>SC1245B1-613HA</t>
+  </si>
+  <si>
+    <t>SC1245SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC1245SO-N-CD-00NR-1245</t>
+  </si>
+  <si>
+    <t>SC1245A3-BK</t>
+  </si>
+  <si>
+    <t>SC1245A3-CD-00CK-41F</t>
+  </si>
+  <si>
+    <t>SC1245S2-BK</t>
+  </si>
+  <si>
+    <t>SC1245S2-CD-00AK-41HL</t>
+  </si>
+  <si>
+    <t>STC9D04C</t>
+  </si>
+  <si>
+    <t>PSTC9D04C</t>
+  </si>
+  <si>
+    <t>SC60220SS-TB</t>
+  </si>
+  <si>
+    <t>SC60220SS-DC-00CB-60220</t>
+  </si>
+  <si>
+    <t>SC60221</t>
+  </si>
+  <si>
+    <t>NP.SC60221-60221</t>
+  </si>
+  <si>
+    <t>SC60221-D-100</t>
+  </si>
+  <si>
+    <t>SC60221-D-256</t>
+  </si>
+  <si>
+    <t>SC60221-D-360</t>
+  </si>
+  <si>
+    <t>SC60221-D-400</t>
+  </si>
+  <si>
+    <t>SC60221-D-50</t>
+  </si>
+  <si>
+    <t>SC60221-D-64</t>
+  </si>
+  <si>
+    <t>SC60221-U-256-976</t>
+  </si>
+  <si>
+    <t>SC60221-U-P1-256</t>
+  </si>
+  <si>
+    <t>SC60221-U-P1-256-244-mai</t>
+  </si>
+  <si>
+    <t>SC60224-D-1000</t>
+  </si>
+  <si>
+    <t>SC60224-D-1024</t>
+  </si>
+  <si>
+    <t>SC60224-D-1024-976-BSD-01</t>
+  </si>
+  <si>
+    <t>SC60224-D-1024-Z1</t>
+  </si>
+  <si>
+    <t>SC60224-D-16</t>
+  </si>
+  <si>
+    <t>SC60224-D-200</t>
+  </si>
+  <si>
+    <t>SC60224-D-500</t>
+  </si>
+  <si>
+    <t>SC60224-D-600</t>
+  </si>
+  <si>
+    <t>SC60224-U-P1-1024</t>
+  </si>
+  <si>
+    <t>SC60224-U-P4-1024</t>
+  </si>
+  <si>
+    <t>SC60228DC-TR</t>
+  </si>
+  <si>
+    <t>SC60228DC-DC-00AR-60228</t>
+  </si>
+  <si>
+    <t>SC60228DC-DC-00AR-NM</t>
+  </si>
+  <si>
+    <t>STC2899AI</t>
+  </si>
+  <si>
+    <t>S41F1</t>
+  </si>
+  <si>
+    <t>S41F1-41F</t>
+  </si>
+  <si>
+    <t>S41F1-S41H</t>
+  </si>
+  <si>
+    <t>S41H</t>
+  </si>
+  <si>
+    <t>S41H-S41H</t>
+  </si>
+  <si>
+    <t>S41H-A2</t>
+  </si>
+  <si>
+    <t>SC1645A1-AI-00HK-4601H</t>
+  </si>
+  <si>
+    <t>SC1645S1-BK</t>
+  </si>
+  <si>
+    <t>SC1645S1-AI-00AK-4601H</t>
+  </si>
+  <si>
+    <t>SC1845F1-BK</t>
+  </si>
+  <si>
+    <t>SC1845F1-AI-00HK-41F</t>
+  </si>
+  <si>
+    <t>SC1845F1-AI-00HK-S41H</t>
+  </si>
+  <si>
+    <t>SC1845S1-BK</t>
+  </si>
+  <si>
+    <t>SC1845S1-AI-00AK-S41H</t>
+  </si>
+  <si>
+    <t>SC1645B2-BK</t>
+  </si>
+  <si>
+    <t>SC1645B2-AI-0EHK-4601</t>
+  </si>
+  <si>
+    <t>SC1645B1-AI-00HK-4601</t>
+  </si>
+  <si>
+    <t>SC2448SO-TR-Q</t>
+  </si>
+  <si>
+    <t>FD1014A</t>
+  </si>
+  <si>
+    <t>SD2276VB-BK</t>
+  </si>
+  <si>
+    <t>SD2276VB-CA-90AK-276</t>
+  </si>
+  <si>
+    <t>STC9905E</t>
+  </si>
+  <si>
+    <t>SC9632VB-BK</t>
+  </si>
+  <si>
+    <t>SC9632VB-CE-00CK-9632</t>
+  </si>
+  <si>
+    <t>STC9902J</t>
+  </si>
+  <si>
+    <t>PSTC9902J</t>
+  </si>
+  <si>
+    <t>SC2402SO-N</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-Ag0.8-2402</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-CJ-0XLR-6571</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-CJ-90NR-2402</t>
+  </si>
+  <si>
+    <t>SC2402UA-BK</t>
+  </si>
+  <si>
+    <t>NM.SC2402UA-CJ-00AK</t>
+  </si>
+  <si>
+    <t>STC11102B</t>
+  </si>
+  <si>
+    <t>SC2442SO-N-Q-DB-60CR-2442</t>
+  </si>
+  <si>
+    <t>SC2442SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2442SO-Q-DB-60CR-2442</t>
+  </si>
+  <si>
+    <t>SC2442UA-BK-Q</t>
+  </si>
+  <si>
+    <t>SC2442UA-Q-DB-60AK-2442</t>
+  </si>
+  <si>
+    <t>SC2498UA-N-BK-Q</t>
+  </si>
+  <si>
+    <t>SC2943A2-BK</t>
+  </si>
+  <si>
+    <t>SC2943A2-Q-DB-4XHK-S41H</t>
+  </si>
+  <si>
+    <t>SC2498CUA-N-BK-Q</t>
+  </si>
+  <si>
+    <t>STC1898AI</t>
+  </si>
+  <si>
+    <t>PSTC1898AI</t>
+  </si>
+  <si>
+    <t>SC1134SO-N-TR-Q</t>
+  </si>
+  <si>
+    <t>SC1134SO-N-Q-CI-00LR-1134</t>
+  </si>
+  <si>
+    <t>SC1134UA-BK</t>
+  </si>
+  <si>
+    <t>SC1134UA-CI-00AK-1134</t>
+  </si>
+  <si>
+    <t>SC1134UA-CI-00AK-43F</t>
+  </si>
+  <si>
+    <t>SC1134UA-CI-00AK-44E</t>
+  </si>
+  <si>
+    <t>SC1134UA-CI-00AK-44L</t>
+  </si>
+  <si>
+    <t>SC1134BU-TR</t>
+  </si>
+  <si>
+    <t>SC1134BU-CI-00CR-1134</t>
+  </si>
+  <si>
+    <t>STC9910E</t>
+  </si>
+  <si>
+    <t>SC9625VB-BK</t>
+  </si>
+  <si>
+    <t>SC9625VB-CE-00CK-9625L</t>
+  </si>
+  <si>
+    <t>STC9901AF</t>
+  </si>
+  <si>
+    <t>PSTC9901AF</t>
+  </si>
+  <si>
+    <t>SC9314UA-BK</t>
+  </si>
+  <si>
+    <t>SC9314UA-CF-0XAK-2414</t>
+  </si>
+  <si>
+    <t>SC9314UA-CF-0XAK-94M</t>
+  </si>
+  <si>
+    <t>SC9314UA-CF-0XAK-17CA</t>
+  </si>
+  <si>
+    <t>STC9906J</t>
+  </si>
+  <si>
+    <t>SC2462UA-BK</t>
+  </si>
+  <si>
+    <t>SC2462UA-CJ-10AK-2462</t>
+  </si>
+  <si>
+    <t>SC2462UA-CJ-10AK-6472</t>
+  </si>
+  <si>
+    <t>SC2464SO-TR</t>
+  </si>
+  <si>
+    <t>SC2464SO-CJ-10CR-2464</t>
+  </si>
+  <si>
+    <t>STC9906I</t>
+  </si>
+  <si>
+    <t>PSTC9906I</t>
+  </si>
+  <si>
+    <t>SC2430UA-BK</t>
+  </si>
+  <si>
+    <t>SC2430UA-CI-10AK-2430</t>
+  </si>
+  <si>
+    <t>SC2434UA-BK</t>
+  </si>
+  <si>
+    <t>SC2434SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2434SO-N-CI-10CR-2434</t>
+  </si>
+  <si>
+    <t>SC2432SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2432SO-N-CI-10CR-2432</t>
+  </si>
+  <si>
+    <t>SC2438UA-BK</t>
+  </si>
+  <si>
+    <t>SC2438UA-CI-10AK-2438</t>
+  </si>
+  <si>
+    <t>STC9G002A</t>
+  </si>
+  <si>
+    <t>PSTC9G002A-0</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-GA-00NR-2402</t>
+  </si>
+  <si>
+    <t>预测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出货</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>订单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4643SA-S-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4643SA-S-Q-DE-40HR-2100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9625VB-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM.SC9625VB-CE-00CK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM.SC1134UA-CI-00AK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM.SC2402UA-GB-00AK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402UA-CJ-90AK-2402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402UA-GB-00AK-177</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402UA-GB-0XAK-U18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402UA-GB-0XAK-2402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402UA-GB-00AK-6501</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9G002B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD211VB-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD211VB-CA-90AK-KH211</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD211VB-CA-90AK-211</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FD1016A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD2276VB-CA-90AK-KH276</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9648TS-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9648TS-AI-10AK-9648</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9314UA-CF-0XAK-9201L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9314UA-CF-0XAK-9209</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM.SC9314UA-CF-0XAK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9314UA-Q-CF-0XAK-94M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9314UA-BK-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC60226SS-TB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM.SC60226SS-DC-00CB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1245UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1245UA-CD-0XHX-41F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2464UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2464UA-CJ-10AK-2464</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2462SO-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2462SO-Q-CJ-10CR-2462</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2448UA-N-BK-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC11102B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2448SO-Q-DB-60CR-2448</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2443UA-BK-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2443UA-Q-DB-60AK-2443</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2443SO-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2443SO-Q-DB-60CR-2443</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2442UA-BK-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2442UA-Q-CP-10AK-2442</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9906P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2442SO-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2442SO-CR-10CR-2442</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9906R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2438SO-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2434UA-CI-10AK-2434</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2438SO-CM-10CR-2438</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2438SO-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9906M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436UA-CI-10AK-2436</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436UA-CI-10AK-6210</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436SO-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436SO-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436SO-Q-CM-10CR-2436</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436SO-CM-10CR-2436</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2434SO-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2434SO-CM-10CR-2434</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432UA-CI-10AK-2432</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432UA-CI-10AK-6232</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-N-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-N-Q-CI-10CR-2432</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-Q-CM-10AR-NM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-Q-CM-10AR-2432</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-CM-10CR-2432</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134B1-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134B1-CI-00HK-43F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9633VB-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9634VB-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9633VB-CF-00CK-9633</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9634VB-CG-00CK-9634</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9634VB-CG-00CK-SZ48</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9625VB-BK-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9625VB-Q-CE-4XCK-9625L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9625VB-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9625VB-Q-CE-4XCR-9625L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2448UA-N-Q-DB-60AK-2448</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2438SO-Q-CM-10CR-2438</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645A2-AE-00HK-601HL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645A2-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-CI-00AK-3144</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1245A1-61HA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S41H-A2-S41H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645A1-AI-00HK-65HA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645A1-AI-00HK-1466</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4643VB-S-TR-Q</t>
+  </si>
+  <si>
+    <t>SC4643VB-S-Q-DE-40CR-4643</t>
+  </si>
+  <si>
+    <t>STC9D06F</t>
+  </si>
+  <si>
+    <t>SC4645VB-BK</t>
+  </si>
+  <si>
+    <t>SC4645VB-DF-00CK-4645</t>
+  </si>
+  <si>
+    <t>STC13103B</t>
+  </si>
+  <si>
+    <t>SC4665VB-BK</t>
+  </si>
+  <si>
+    <t>SC4665VB-HB-33CK-4665</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-CJ-90NR-NM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9A001G</t>
+  </si>
+  <si>
+    <t>SC9642TS-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9642TS-Q-AG-4XHR-9642</t>
+  </si>
+  <si>
+    <t>SC9642TS-E-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9642TS-E-Q-AH-4XLR-9642</t>
+  </si>
+  <si>
+    <t>SC9642TS-E362-Q-AH-4XLR-9642</t>
+  </si>
+  <si>
+    <t>SC9641TS-P-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9641TS-P-Q-AI-10LR-9641P</t>
+  </si>
+  <si>
+    <t>SC9625VB-CE-00CR-9625L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9625VB-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4688DC-Q-DC-40AR-6388</t>
+  </si>
+  <si>
+    <t>SC2462SO-TR</t>
+  </si>
+  <si>
+    <t>SC2462SO-CJ-10CR-2462</t>
+  </si>
+  <si>
+    <t>SC2498CUA-N-Q-DB-60CK-2498C</t>
+  </si>
+  <si>
+    <t>SC2498UA-N-Q-DB-60CK-2498</t>
+  </si>
+  <si>
+    <t>STC9910F</t>
+  </si>
+  <si>
+    <t>SC9621VB-BK</t>
+  </si>
+  <si>
+    <t>SC9621VB-CF-00CK-9621</t>
+  </si>
+  <si>
+    <t>SC9621VB-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9621VB-Q-CN-4XCR-9621</t>
+  </si>
+  <si>
+    <t>STC2899AE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645B1-AI-00HK-615HA</t>
+  </si>
+  <si>
+    <t>PSTC9G001C</t>
+  </si>
+  <si>
+    <t>SC1002N1-BK</t>
+  </si>
+  <si>
+    <t>SC1002N1-CL-00HK-42N</t>
+  </si>
+  <si>
+    <t>SC1002S1-BK</t>
+  </si>
+  <si>
+    <t>SC1002S1-CG-00AK-41F</t>
+  </si>
+  <si>
+    <t>SC1133UA-BK</t>
+  </si>
+  <si>
+    <t>SC1133UA-CJ-00AK-1133</t>
+  </si>
+  <si>
+    <t>SC1134BU-CI-00AR-1134</t>
+  </si>
+  <si>
+    <t>SC1134SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC1134SO-N-CF-00LR-1134</t>
+  </si>
+  <si>
+    <t>SC1138SO-N-TR-Q</t>
+  </si>
+  <si>
+    <t>SC1138SO-N-Q-CC-00LR-1138</t>
+  </si>
+  <si>
+    <t>SC1445A1</t>
+  </si>
+  <si>
+    <t>SC1445A1-41F</t>
+  </si>
+  <si>
+    <t>SC1645A1-AI-00HK-615HA</t>
+  </si>
+  <si>
+    <t>SC1645B1-AE-00HK-4601</t>
+  </si>
+  <si>
+    <t>SC1845S1-AI-00AK-41F</t>
+  </si>
+  <si>
+    <t>SC1945A1-BK</t>
+  </si>
+  <si>
+    <t>SC1945A1-AJ-00HK-N13</t>
+  </si>
+  <si>
+    <t>SC1945B1-BK</t>
+  </si>
+  <si>
+    <t>SC1945B1-AJ-00HK-N603</t>
+  </si>
+  <si>
+    <t>SC2063SO-TR</t>
+  </si>
+  <si>
+    <t>SC2063SO-GC-00NR-2063</t>
+  </si>
+  <si>
+    <t>SC2063UA-BK</t>
+  </si>
+  <si>
+    <t>SC2063UA-GC-00AK-2063</t>
+  </si>
+  <si>
+    <t>SC2064SO-TR</t>
+  </si>
+  <si>
+    <t>SC2064SO-GC-00NR-2064</t>
+  </si>
+  <si>
+    <t>SC2202SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2202SO-N-CE-00NR-2202</t>
+  </si>
+  <si>
+    <t>SC2242SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2242SO-Q-CH-10CR-2242</t>
+  </si>
+  <si>
+    <t>SC2242SO-Q-CH-10CR-2642</t>
+  </si>
+  <si>
+    <t>SC2242UA-BK</t>
+  </si>
+  <si>
+    <t>SC2242UA-CE-00AK-2242</t>
+  </si>
+  <si>
+    <t>SC2242UA-BK-Q</t>
+  </si>
+  <si>
+    <t>SC2242UA-Q-CH-10AK-2242</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-CJ-00NR-2402</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-CJ-00NR-6571</t>
+  </si>
+  <si>
+    <t>SC2413SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2413SO-N-CD-00LR-44E</t>
+  </si>
+  <si>
+    <t>SC2432SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2432SO-Q-CM-10CR-2432</t>
+  </si>
+  <si>
+    <t>SC243XSO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC243XSO-Q-CM-10CR-243X</t>
+  </si>
+  <si>
+    <t>SC2442UA-BK</t>
+  </si>
+  <si>
+    <t>SC2442UA-CP-10AK-2442</t>
+  </si>
+  <si>
+    <t>SC2442UA-CP-10AK-U18</t>
+  </si>
+  <si>
+    <t>SC2448SO-Q-DB-40CR-2448</t>
+  </si>
+  <si>
+    <t>SC2452SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2452SO-Q-DD-60AR-2452</t>
+  </si>
+  <si>
+    <t>SC2455SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2455SO-Q-CK-10CR-2455</t>
+  </si>
+  <si>
+    <t>SC2466SO-TR</t>
+  </si>
+  <si>
+    <t>SC2466SO-CO-10CR-2466</t>
+  </si>
+  <si>
+    <t>SC2498CUA-N-Q-DB-60AK-2498C</t>
+  </si>
+  <si>
+    <t>SC2498SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2498SO-Q-DB-60CR-2498</t>
+  </si>
+  <si>
+    <t>SC2498TSO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2498TSO-Q-CC-10CR-2498T</t>
+  </si>
+  <si>
+    <t>SC2498UA-N-Q-DB-60AK-2498</t>
+  </si>
+  <si>
+    <t>SC2527S6-AB-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2527S6-AB-Q-DA-40CR-2527</t>
+  </si>
+  <si>
+    <t>SC2527S6-SD-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2527S6-SD-Q-DA-40CR-2527</t>
+  </si>
+  <si>
+    <t>SC2546VB-AB-BK</t>
+  </si>
+  <si>
+    <t>SC2546VB-AB-DA-00AK-2546</t>
+  </si>
+  <si>
+    <t>SC25791CUA-A-Q</t>
+  </si>
+  <si>
+    <t>SC25791CUA-A(STC11210G-Q)-25791C</t>
+  </si>
+  <si>
+    <t>SC25791SE-TR-Q</t>
+  </si>
+  <si>
+    <t>SC25791SE-Q-CG-40CR-5791</t>
+  </si>
+  <si>
+    <t>SC25891CUA-A-Q</t>
+  </si>
+  <si>
+    <t>SC25891CUA-A-Q(STC11210G-Q)-25891C</t>
+  </si>
+  <si>
+    <t>SC25891SE-TR-Q</t>
+  </si>
+  <si>
+    <t>SC25891SE-Q-CG-40CR-5891</t>
+  </si>
+  <si>
+    <t>SC2943SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2943SO-Q-DB-60CR-2943</t>
+  </si>
+  <si>
+    <t>SC2948S2-BK</t>
+  </si>
+  <si>
+    <t>SC2948S2-DB-60AK-61H</t>
+  </si>
+  <si>
+    <t>SC2968S1-N-BK</t>
+  </si>
+  <si>
+    <t>SC2968S1-N-DC-4XAK-S21C</t>
+  </si>
+  <si>
+    <t>SC4001SE-TR</t>
+  </si>
+  <si>
+    <t>SC4001SE-CB-90CR-4001</t>
+  </si>
+  <si>
+    <t>SC4002BU-TR</t>
+  </si>
+  <si>
+    <t>SC4002BU-CA-00CR-4002</t>
+  </si>
+  <si>
+    <t>SC4002SO</t>
+  </si>
+  <si>
+    <t>SC4002SO(STC4000AA)-4002</t>
+  </si>
+  <si>
+    <t>SC4002SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC4002SO-N-CA-00NR-4002</t>
+  </si>
+  <si>
+    <t>SC4002UA-BK</t>
+  </si>
+  <si>
+    <t>SC4002UA-CA-00AK-4002</t>
+  </si>
+  <si>
+    <t>SC4002UA-CA-00AK-95A</t>
+  </si>
+  <si>
+    <t>SC4011DN</t>
+  </si>
+  <si>
+    <t>SC4011DN-4011</t>
+  </si>
+  <si>
+    <t>SC4019S7-BK</t>
+  </si>
+  <si>
+    <t>SC4019S7-CC-90AK-49E</t>
+  </si>
+  <si>
+    <t>SC4101DN</t>
+  </si>
+  <si>
+    <t>SC4101DN(STC11201B1)-4101</t>
+  </si>
+  <si>
+    <t>SC4103DN</t>
+  </si>
+  <si>
+    <t>SC4103DN(STC11201B1)-4103</t>
+  </si>
+  <si>
+    <t>SC4251D3-TR</t>
+  </si>
+  <si>
+    <t>SC4251D3-GA-00FR-4251</t>
+  </si>
+  <si>
+    <t>SC4391S6-TR</t>
+  </si>
+  <si>
+    <t>SC4391S6-GB-00NR-4391</t>
+  </si>
+  <si>
+    <t>SC4616BU</t>
+  </si>
+  <si>
+    <t>SC4616BU-4616</t>
+  </si>
+  <si>
+    <t>SC4616UA-10.2NF-BK</t>
+  </si>
+  <si>
+    <t>SC4616UA-10.2NF-CD-90AK-4616</t>
+  </si>
+  <si>
+    <t>SC4643SA-Q-DE-40CK-4643</t>
+  </si>
+  <si>
+    <t>SC4689SA-BK-Q</t>
+  </si>
+  <si>
+    <t>SC4689SA-Q-DF-40CK-4689</t>
+  </si>
+  <si>
+    <t>SC4703SO-TR</t>
+  </si>
+  <si>
+    <t>SC4703SO-GB-00NR-4703</t>
+  </si>
+  <si>
+    <t>SC4823S6-TR</t>
+  </si>
+  <si>
+    <t>SC4823S6-GA-00NR-4823</t>
+  </si>
+  <si>
+    <t>SC4923SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC4923SO-N-CD-00NR-4923</t>
+  </si>
+  <si>
+    <t>SC60104</t>
+  </si>
+  <si>
+    <t>NM.SC60104</t>
+  </si>
+  <si>
+    <t>SC60226SS-TB</t>
+  </si>
+  <si>
+    <t>NA.SC60226SS-DC</t>
+  </si>
+  <si>
+    <t>SC60370</t>
+  </si>
+  <si>
+    <t>SC60370(STC9D05C)-60370</t>
+  </si>
+  <si>
+    <t>SC69401DC-SPI-TR-Q</t>
+  </si>
+  <si>
+    <t>SC69401DC-SPI-Q-HD-4XCR-69401</t>
+  </si>
+  <si>
+    <t>SC69401DC-TR</t>
+  </si>
+  <si>
+    <t>SC69401DC-HD-4XCR-69401</t>
+  </si>
+  <si>
+    <t>SC69401DC-TR-Q</t>
+  </si>
+  <si>
+    <t>SC69401DC-Q-HD-4XCR-69401</t>
+  </si>
+  <si>
+    <t>SC69401HS-SPI-TR-Q</t>
+  </si>
+  <si>
+    <t>SC69401HS-SPI-Q-HD-4XTR-69401</t>
+  </si>
+  <si>
+    <t>SC69401HS-TR</t>
+  </si>
+  <si>
+    <t>SC69401HS-HD-4XTR-69401</t>
+  </si>
+  <si>
+    <t>SC69401HS-TR-Q</t>
+  </si>
+  <si>
+    <t>SC69401HS-Q-HD-4XTR-69401</t>
+  </si>
+  <si>
     <t>SC9641TS-P-AI-10LR-41CPA</t>
   </si>
   <si>
-    <t>SC9641TS-P-AI-10AR-41CPA</t>
-  </si>
-  <si>
-    <t>SC9648TS-P</t>
-  </si>
-  <si>
-    <t>NR.SC9648TS-P(STC9A001I)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9648TS-P(STC9A001I)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9648TS-P(STC9A001I)-9648</t>
-  </si>
-  <si>
-    <t>SC9648TS-P-9A001I(STC9A001I)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9648TS-P-9A001I(STC9A001I)-9648</t>
-  </si>
-  <si>
-    <t>SC9648TS-TR</t>
-  </si>
-  <si>
-    <t>SC9648TS-AI-10AR-9648</t>
-  </si>
-  <si>
-    <t>STC4011B</t>
-  </si>
-  <si>
-    <t>SC4011SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC4011SO-N-CB-90NR-49E</t>
-  </si>
-  <si>
-    <t>STC4011B-DS</t>
-  </si>
-  <si>
-    <t>STC9D01C</t>
-  </si>
-  <si>
-    <t>SC4688DA</t>
-  </si>
-  <si>
-    <t>SC4688DA(STC9D01C)-4688D</t>
-  </si>
-  <si>
-    <t>SC4688DC</t>
-  </si>
-  <si>
-    <t>SC4688DC-4688</t>
-  </si>
-  <si>
-    <t>SC4688DC-TR-Q</t>
-  </si>
-  <si>
-    <t>SC4688DC-Q-DC-40AR-4688</t>
-  </si>
-  <si>
-    <t>SC4688DC-Q-DC-40CR-6388</t>
-  </si>
-  <si>
-    <t>SC4688DC-Q-DC-40CR-4688</t>
-  </si>
-  <si>
-    <t>SC4688DC-DU-Q-DC-40AR-2425</t>
-  </si>
-  <si>
-    <t>SC4688SA</t>
-  </si>
-  <si>
-    <t>NP.SC4688SA-4688</t>
-  </si>
-  <si>
-    <t>NP.SC4688SA-888K</t>
-  </si>
-  <si>
-    <t>SC4688SA-A</t>
-  </si>
-  <si>
-    <t>SC4688SA-A(STC9D01C)-4688</t>
-  </si>
-  <si>
-    <t>SC4688SA-BK-Q</t>
-  </si>
-  <si>
-    <t>SC4688SA-Q-DC-40CK-4688</t>
-  </si>
-  <si>
-    <t>SC4688SA-Q-DC-40CK-888K</t>
-  </si>
-  <si>
-    <t>SC4695DC</t>
-  </si>
-  <si>
-    <t>SC4695DC-2425</t>
-  </si>
-  <si>
-    <t>SC4688DC-TR</t>
-  </si>
-  <si>
-    <t>SC4688DC-DC-40AR-2425</t>
+    <t>SC9642TS-E-TR</t>
+  </si>
+  <si>
+    <t>SC9642TS-E-AH-4XLR-9642</t>
+  </si>
+  <si>
+    <t>SC9675IM-HRF00-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9675IM-HRF00-Q-AB-4XAR-9675</t>
+  </si>
+  <si>
+    <t>SC9675IM-HRF11-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9675IM-HRF11-Q-AB-4XAR-9675</t>
+  </si>
+  <si>
+    <t>SC9675IM-LRF00-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9675IM-LRF00-Q-AB-4XAR-9675</t>
+  </si>
+  <si>
+    <t>SC9675IM-LRF01-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9675IM-LRF01-Q-AB-4XAR-9675</t>
+  </si>
+  <si>
+    <t>SC9675IM-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9675IM-Q-AB-4XAR-9675</t>
+  </si>
+  <si>
+    <t>SC9675T3-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9675T3-Q-AB-4XAR-9675</t>
+  </si>
+  <si>
+    <t>SC9683TS-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9683TS-Q-DB-4XAR-9683</t>
+  </si>
+  <si>
+    <t>SC9684TS-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9684TS-Q-DB-4XAR-9684</t>
+  </si>
+  <si>
+    <t>SC9685TS-RP120-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9685TS-RP120-Q-DB-46AR-96852</t>
+  </si>
+  <si>
+    <t>SD477VB-BK</t>
+  </si>
+  <si>
+    <t>SD477VB-GC-90AK-477S</t>
+  </si>
+  <si>
+    <t>SD477VB-GC-90AK-KH477</t>
+  </si>
+  <si>
+    <t>SL002147DC-TR</t>
+  </si>
+  <si>
+    <t>SL002147DC-GB-00AR-2147</t>
+  </si>
+  <si>
+    <t>SL54123ADC-TR</t>
+  </si>
+  <si>
+    <t>SL54123ADC-GB-00AR-54123A</t>
+  </si>
+  <si>
+    <t>SPD3242</t>
+  </si>
+  <si>
+    <t>SPD3242(STC35301)</t>
+  </si>
+  <si>
+    <t>VE1430Q1BA3R5</t>
+  </si>
+  <si>
+    <t>TRVE1430Q1BA3R5(VA2201D)-1430Q</t>
+  </si>
+  <si>
+    <t>VE1430Q1CA3R33</t>
+  </si>
+  <si>
+    <t>TRVE1430Q1CA3R33(VA2201D)-1430Q</t>
+  </si>
+  <si>
+    <t>VE1430Q1CA3R5</t>
+  </si>
+  <si>
+    <t>TRVE1430Q1CA3R5-1430Q</t>
+  </si>
+  <si>
+    <t>VE1430Q1VA3RADJ</t>
+  </si>
+  <si>
+    <t>TRVE1430Q1VA3RADJ(VA2201E)-1430Q</t>
+  </si>
+  <si>
+    <t>VE8602A5R</t>
+  </si>
+  <si>
+    <t>TRVE8602A5R-8602</t>
+  </si>
+  <si>
+    <t>VE8602AKR</t>
+  </si>
+  <si>
+    <t>VE8602AKR-8602</t>
+  </si>
+  <si>
+    <t>ZH6338</t>
+  </si>
+  <si>
+    <t>ZH6531</t>
+  </si>
+  <si>
+    <t>SC3100VB-BK-Q</t>
+  </si>
+  <si>
+    <t>SC3100VB-DG-00CK-3100</t>
+  </si>
+  <si>
+    <t>SC2033SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2033SO-N-GD-00NR-2033</t>
+  </si>
+  <si>
+    <t>SC919SO-N-TR-Q</t>
+  </si>
+  <si>
+    <t>SC919SO-N-Q-CD-90CR-919H</t>
+  </si>
+  <si>
+    <t>SC1645B1-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645A1-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9G001C</t>
+  </si>
+  <si>
+    <t>STC9G001C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC1002AG</t>
+  </si>
+  <si>
+    <t>STC11102C</t>
+  </si>
+  <si>
+    <t>STC1002AL</t>
+  </si>
+  <si>
+    <t>STC1898AJ</t>
+  </si>
+  <si>
+    <t>STC1002AF</t>
+  </si>
+  <si>
+    <t>STC1898AC</t>
+  </si>
+  <si>
+    <t>STC2899AB</t>
   </si>
   <si>
     <t>STC2899AE</t>
   </si>
   <si>
-    <t>SC1645A1</t>
-  </si>
-  <si>
-    <t>SC1645A1-1466</t>
-  </si>
-  <si>
-    <t>SC1645A1-4601H</t>
-  </si>
-  <si>
-    <t>SC1645A1-61H</t>
-  </si>
-  <si>
-    <t>SC1645A1-65HA</t>
-  </si>
-  <si>
-    <t>SC1645A1-BK</t>
-  </si>
-  <si>
-    <t>SC1645A1-AE-00HK-4601H</t>
-  </si>
-  <si>
-    <t>SC1645A1-AE-00HK-65HA</t>
-  </si>
-  <si>
-    <t>SC1645A1-AE-00HK-1466</t>
-  </si>
-  <si>
-    <t>SC1645A1R12</t>
-  </si>
-  <si>
-    <t>SC1645A1R12-4601H</t>
-  </si>
-  <si>
-    <t>SC1645A2</t>
-  </si>
-  <si>
-    <t>SC1645A2-601HL</t>
-  </si>
-  <si>
-    <t>SC1645B1</t>
-  </si>
-  <si>
-    <t>SC1645B1-4601</t>
-  </si>
-  <si>
-    <t>SC1645B1-615HA</t>
-  </si>
-  <si>
-    <t>SC1645B1-65HA</t>
-  </si>
-  <si>
-    <t>SC1645B1-BK</t>
-  </si>
-  <si>
-    <t>SC1645B1-AE-00HK-615HA</t>
-  </si>
-  <si>
-    <t>STC9910BN</t>
-  </si>
-  <si>
-    <t>SC9641TS</t>
-  </si>
-  <si>
-    <t>SC9641TS-9641</t>
-  </si>
-  <si>
-    <t>SC9641TS-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9641TS-Q-CB-10LR-9641</t>
-  </si>
-  <si>
-    <t>SC9641TS-362-Q-CB-10LR-9641</t>
-  </si>
-  <si>
-    <t>STC9A001G</t>
-  </si>
-  <si>
-    <t>SC9642TS</t>
-  </si>
-  <si>
-    <t>SC9642TS(9A001G)-9642</t>
-  </si>
-  <si>
-    <t>STC9A001H</t>
-  </si>
-  <si>
-    <t>SC9642TS-E</t>
-  </si>
-  <si>
-    <t>SC9642TS(9A001H)-E-9642</t>
-  </si>
-  <si>
-    <t>SC9642TS(STC9A001H)-E-9642</t>
-  </si>
-  <si>
-    <t>SC9642TS(STC9A001H)-E-白板</t>
-  </si>
-  <si>
-    <t>SC9642TS-EC</t>
-  </si>
-  <si>
-    <t>SC9642TS(STC9A001H)-EC-9642</t>
-  </si>
-  <si>
-    <t>SC9642TS-EC-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9642TS-EC-Q-AH-4XLR-9642</t>
-  </si>
-  <si>
-    <t>SC9642TS-EC-Q-AH-4XAR-9642</t>
-  </si>
-  <si>
-    <t>STC4011E</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-A-TR</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-A-CE-90NR-4015</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-4015</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-512</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-515</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-CY19</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-G01M</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-QX11</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-NM</t>
-  </si>
-  <si>
-    <t>STC4011E-DS</t>
-  </si>
-  <si>
-    <t>STC9906P</t>
-  </si>
-  <si>
-    <t>SC2442SE</t>
-  </si>
-  <si>
-    <t>SC2442SE-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-N</t>
-  </si>
-  <si>
-    <t>SC2442SO-N(STC9906P)-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-Q-CP-10CR-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-Q-CP-10CR-2662</t>
-  </si>
-  <si>
-    <t>SC2442UA</t>
-  </si>
-  <si>
-    <t>SC2442UA-2442</t>
-  </si>
-  <si>
-    <t>SC2442UA-U18</t>
-  </si>
-  <si>
-    <t>SC2662SO-N</t>
-  </si>
-  <si>
-    <t>SC2662SO-N-2662</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-CP-10CR-2442</t>
-  </si>
-  <si>
-    <t>STC1898AD</t>
-  </si>
-  <si>
-    <t>PSTC1898AD-0</t>
-  </si>
-  <si>
-    <t>PSTC1898AD</t>
-  </si>
-  <si>
-    <t>SC1245A1</t>
-  </si>
-  <si>
-    <t>SC1245A1-41F</t>
-  </si>
-  <si>
-    <t>SC1245A1-61HA</t>
-  </si>
-  <si>
-    <t>SC1245B1</t>
-  </si>
-  <si>
-    <t>SC1245B1-41F</t>
-  </si>
-  <si>
-    <t>SC1245B1-613HA</t>
-  </si>
-  <si>
-    <t>SC1245SO-N</t>
-  </si>
-  <si>
-    <t>SC1245SO-N-1245</t>
-  </si>
-  <si>
-    <t>SC1245SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC1245SO-N-CD-00NR-1245</t>
-  </si>
-  <si>
-    <t>SC1245UA</t>
-  </si>
-  <si>
-    <t>SC1245A3(STC1898AD)-41F</t>
-  </si>
-  <si>
-    <t>SC1245UA-1245</t>
-  </si>
-  <si>
-    <t>SC1245UA-41F</t>
-  </si>
-  <si>
-    <t>SC41HL-A2</t>
-  </si>
-  <si>
-    <t>SC41HL-A2-41HL</t>
-  </si>
-  <si>
-    <t>SC1245A3-BK</t>
-  </si>
-  <si>
-    <t>SC1245A3-CD-00CK-41F</t>
-  </si>
-  <si>
-    <t>SC1245S2-BK</t>
-  </si>
-  <si>
-    <t>SC1245S2-CD-00AK-41HL</t>
-  </si>
-  <si>
-    <t>STC9D04C</t>
-  </si>
-  <si>
-    <t>PSTC9D04C</t>
-  </si>
-  <si>
-    <t>SC60220</t>
-  </si>
-  <si>
-    <t>NP.SC60220-60220</t>
-  </si>
-  <si>
-    <t>SC60220-60220</t>
-  </si>
-  <si>
-    <t>SC60220SS-TB</t>
-  </si>
-  <si>
-    <t>SC60220SS-DC-00CB-60220</t>
-  </si>
-  <si>
-    <t>SC60221</t>
-  </si>
-  <si>
-    <t>NP.SC60221-60221</t>
-  </si>
-  <si>
-    <t>SC60221-D-100</t>
-  </si>
-  <si>
-    <t>SC60221-D-256</t>
-  </si>
-  <si>
-    <t>SC60221-D-360</t>
-  </si>
-  <si>
-    <t>SC60221-D-400</t>
-  </si>
-  <si>
-    <t>SC60221-D-50</t>
-  </si>
-  <si>
-    <t>SC60221-D-64</t>
-  </si>
-  <si>
-    <t>SC60221-U-256-976</t>
-  </si>
-  <si>
-    <t>SC60221-U-P1-256</t>
-  </si>
-  <si>
-    <t>SC60221-U-P1-256-244-mai</t>
-  </si>
-  <si>
-    <t>SC60224-D-1000</t>
-  </si>
-  <si>
-    <t>SC60224-D-1024</t>
-  </si>
-  <si>
-    <t>SC60224-D-1024-976-BSD-01</t>
-  </si>
-  <si>
-    <t>SC60224-D-1024-Z1</t>
-  </si>
-  <si>
-    <t>SC60224-D-16</t>
-  </si>
-  <si>
-    <t>SC60224-D-200</t>
-  </si>
-  <si>
-    <t>SC60224-D-500</t>
-  </si>
-  <si>
-    <t>SC60224-D-600</t>
-  </si>
-  <si>
-    <t>SC60224-U-P1-1024</t>
-  </si>
-  <si>
-    <t>SC60224-U-P4-1024</t>
-  </si>
-  <si>
-    <t>SC60226</t>
-  </si>
-  <si>
-    <t>NA.SC60226</t>
-  </si>
-  <si>
-    <t>NM.SC60226</t>
-  </si>
-  <si>
-    <t>NP.SC60226-60226</t>
-  </si>
-  <si>
-    <t>SC60228DC</t>
-  </si>
-  <si>
-    <t>NR.SC60228DC-60228</t>
-  </si>
-  <si>
-    <t>SC60228DC-60228</t>
-  </si>
-  <si>
-    <t>SC60228DC-白板</t>
-  </si>
-  <si>
-    <t>SC60228DC-TR</t>
-  </si>
-  <si>
-    <t>SC60228DC-DC-00AR-60228</t>
-  </si>
-  <si>
-    <t>SC60228DC-DC-00AR-NM</t>
-  </si>
-  <si>
-    <t>STC2899AI</t>
-  </si>
-  <si>
-    <t>S41F1</t>
-  </si>
-  <si>
-    <t>S41F1-41F</t>
-  </si>
-  <si>
-    <t>S41F1-S41H</t>
-  </si>
-  <si>
-    <t>S41H</t>
-  </si>
-  <si>
-    <t>S41H-S41H</t>
-  </si>
-  <si>
-    <t>S41H-A2</t>
-  </si>
-  <si>
-    <t>S41H-A2-S41H</t>
-  </si>
-  <si>
-    <t>SC1645A1(STC2899AI)-65HA</t>
-  </si>
-  <si>
-    <t>SC1645A1-AI-00HK-4601H</t>
-  </si>
-  <si>
-    <t>SC1645A2(STC2899AI)-601HL</t>
-  </si>
-  <si>
-    <t>SC1645B1(STC2899AI)-4601</t>
-  </si>
-  <si>
-    <t>SC1645B2</t>
-  </si>
-  <si>
-    <t>SC1645B2(STC2899AI)-4601</t>
-  </si>
-  <si>
-    <t>SC1645S1-BK</t>
-  </si>
-  <si>
-    <t>SC1645S1-AI-00AK-4601H</t>
-  </si>
-  <si>
-    <t>SC1845F1-BK</t>
-  </si>
-  <si>
-    <t>SC1845F1-AI-00HK-41F</t>
-  </si>
-  <si>
-    <t>SC1845F1-AI-00HK-S41H</t>
-  </si>
-  <si>
-    <t>SC1845S1-BK</t>
-  </si>
-  <si>
-    <t>SC1845S1-AI-00AK-S41H</t>
-  </si>
-  <si>
-    <t>SC1645B2-BK</t>
-  </si>
-  <si>
-    <t>SC1645B2-AI-0EHK-4601</t>
-  </si>
-  <si>
-    <t>SC1645B1-AI-00HK-4601</t>
-  </si>
-  <si>
-    <t>STC9906S</t>
-  </si>
-  <si>
-    <t>SC2448SO</t>
-  </si>
-  <si>
-    <t>SC2448SO-2448</t>
-  </si>
-  <si>
-    <t>SC2448UA-N</t>
-  </si>
-  <si>
-    <t>NM.SC2448UA-N</t>
-  </si>
-  <si>
-    <t>SC2448UA-N-2448</t>
-  </si>
-  <si>
-    <t>SC2448SO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2448SO-Q-CS-10CR-2448</t>
-  </si>
-  <si>
-    <t>FD1014A</t>
-  </si>
-  <si>
-    <t>KH276</t>
-  </si>
-  <si>
-    <t>SD2276(FD1014A)-KH276</t>
-  </si>
-  <si>
-    <t>PFD1014A</t>
-  </si>
-  <si>
-    <t>PFD1014A-0</t>
-  </si>
-  <si>
-    <t>SD2276</t>
-  </si>
-  <si>
-    <t>SD2276(FD1014A)-276</t>
-  </si>
-  <si>
-    <t>SD2276VB-BK</t>
-  </si>
-  <si>
-    <t>SD2276VB-CA-00AK-276</t>
-  </si>
-  <si>
-    <t>SD2276VB-CA-00AK-KH276</t>
-  </si>
-  <si>
-    <t>SD2276VB-CA-90AK-276</t>
-  </si>
-  <si>
-    <t>STC9905E</t>
-  </si>
-  <si>
-    <t>SC9632VB</t>
-  </si>
-  <si>
-    <t>SC9632VB-9632</t>
-  </si>
-  <si>
-    <t>SC9632VB-BK</t>
-  </si>
-  <si>
-    <t>SC9632VB-CE-00CK-9632</t>
-  </si>
-  <si>
-    <t>STC9902J</t>
-  </si>
-  <si>
-    <t>PSTC9902J</t>
-  </si>
-  <si>
-    <t>SC2402SO-N</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-2402</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-Ag0.8-2402</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-C(STC9902J)-2448</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-CJ-00NR-2402</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-CJ-0XLR-6571</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-CJ-90NR-2402</t>
-  </si>
-  <si>
-    <t>SC2402UA</t>
-  </si>
-  <si>
-    <t>NM.SC2402UA</t>
-  </si>
-  <si>
-    <t>SC2402UA-2402</t>
-  </si>
-  <si>
-    <t>SC2402UA-U18</t>
-  </si>
-  <si>
-    <t>SC2402UA-BK</t>
-  </si>
-  <si>
-    <t>NM.SC2402UA-CJ-00AK</t>
-  </si>
-  <si>
-    <t>STC11102B</t>
-  </si>
-  <si>
-    <t>SC2442SO</t>
-  </si>
-  <si>
-    <t>NM.SC2442SO(2943N1-1)</t>
-  </si>
-  <si>
-    <t>SC2442SO(2943N1-1)-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-N(2943S1)-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-Q-DB-60CR-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2442SO-Q-DB-60CR-2442</t>
-  </si>
-  <si>
-    <t>SC2442UA(2943S1-1)-2442</t>
-  </si>
-  <si>
-    <t>SC2442UA(2943S1-1)-U18</t>
-  </si>
-  <si>
-    <t>SC2442UA-BK-Q</t>
-  </si>
-  <si>
-    <t>SC2442UA-Q-DB-60AK-2442</t>
-  </si>
-  <si>
-    <t>SC2448SO(2948N1)-2448</t>
-  </si>
-  <si>
-    <t>SC2448SO(2948N1-1)-2448</t>
-  </si>
-  <si>
-    <t>SC2498UA-N-BK-Q</t>
-  </si>
-  <si>
-    <t>SC2498UA-N-Q-DB-60CK-2498</t>
-  </si>
-  <si>
-    <t>SC2498UA-N-Q-DB-60AK-2498</t>
-  </si>
-  <si>
-    <t>SC2943A2-BK</t>
-  </si>
-  <si>
-    <t>SC2943A2-Q-DB-4XHK-S41H</t>
-  </si>
-  <si>
-    <t>SC2498CUA-N-BK-Q</t>
-  </si>
-  <si>
-    <t>SC2498CUA-N-Q-DB-60AK-2498C</t>
-  </si>
-  <si>
-    <t>STC9906W</t>
-  </si>
-  <si>
-    <t>SC2443UA</t>
-  </si>
-  <si>
-    <t>SC2443UA-W(STC9906W)-2443</t>
-  </si>
-  <si>
-    <t>STC1898AI</t>
-  </si>
-  <si>
-    <t>PSTC1898AI</t>
-  </si>
-  <si>
-    <t>SC1134B1</t>
-  </si>
-  <si>
-    <t>SC1134B1-43F</t>
-  </si>
-  <si>
-    <t>SC1134BU</t>
-  </si>
-  <si>
-    <t>SC1134BU-1134</t>
-  </si>
-  <si>
-    <t>SC1134S2-BK</t>
-  </si>
-  <si>
-    <t>NM.SC1134S2-CI-00AK</t>
-  </si>
-  <si>
-    <t>SC1134S2-CI-00AK-44E</t>
-  </si>
-  <si>
-    <t>SC1134SO-N</t>
-  </si>
-  <si>
-    <t>SC1134SO-N-1134</t>
-  </si>
-  <si>
-    <t>SC1134SO-N-TR-Q</t>
-  </si>
-  <si>
-    <t>SC1134SO-N-Q-CI-00LR-1134</t>
-  </si>
-  <si>
-    <t>SC1134UA</t>
-  </si>
-  <si>
-    <t>NM.SC1134UA</t>
-  </si>
-  <si>
-    <t>SC1134UA-04E</t>
-  </si>
-  <si>
-    <t>SC1134UA-1134</t>
-  </si>
-  <si>
-    <t>SC1134UA-3144</t>
-  </si>
-  <si>
-    <t>SC1134UA-43F</t>
-  </si>
-  <si>
-    <t>SC1134UA-44E</t>
-  </si>
-  <si>
-    <t>SC1134UA-44L</t>
-  </si>
-  <si>
-    <t>SC1134UA-BK</t>
-  </si>
-  <si>
-    <t>SC1134UA-CI-00AK-1134</t>
-  </si>
-  <si>
-    <t>SC1134UA-CI-00AK-43F</t>
-  </si>
-  <si>
-    <t>SC1134UA-CI-00AK-44E</t>
-  </si>
-  <si>
-    <t>SC1134UA-CI-00AK-44L</t>
-  </si>
-  <si>
-    <t>SC1134BU-TR</t>
-  </si>
-  <si>
-    <t>SC1134BU-CI-00AR-1134</t>
-  </si>
-  <si>
-    <t>SC1134BU-CI-00CR-1134</t>
-  </si>
-  <si>
-    <t>SC1134S1-BK</t>
-  </si>
-  <si>
-    <t>SC1134S1-CI-00AK-43F</t>
-  </si>
-  <si>
-    <t>STC9910E</t>
-  </si>
-  <si>
-    <t>SC9625VB</t>
-  </si>
-  <si>
-    <t>NM.SC9625VB(STC9910E)</t>
-  </si>
-  <si>
-    <t>NR.SC9625VB(STC9910E)-9625</t>
-  </si>
-  <si>
-    <t>SC9625VB-L</t>
-  </si>
-  <si>
-    <t>NR.SC9625VB-L-9625L</t>
-  </si>
-  <si>
-    <t>SC9625VB-L-9625L</t>
-  </si>
-  <si>
-    <t>SC9625VB-BK</t>
-  </si>
-  <si>
-    <t>SC9625VB-CE-00CK-9625L</t>
-  </si>
-  <si>
-    <t>STC9A001F</t>
-  </si>
-  <si>
-    <t>AS04</t>
-  </si>
-  <si>
-    <t>SC9641TS-P(9A001F)-AS04</t>
-  </si>
-  <si>
-    <t>NR.SC9641TS-P（9A001F)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9641TS-P(9A001F)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9641TS-P（9A001F)-41CPA</t>
-  </si>
-  <si>
-    <t>STC9901AF</t>
-  </si>
-  <si>
-    <t>PSTC9901AF</t>
-  </si>
-  <si>
-    <t>SC9314UA</t>
-  </si>
-  <si>
-    <t>NM.SC9314UA</t>
-  </si>
-  <si>
-    <t>SC9314UA-17CA</t>
-  </si>
-  <si>
-    <t>SC9314UA-2414</t>
-  </si>
-  <si>
-    <t>SC9314UA-9201L</t>
-  </si>
-  <si>
-    <t>SC9314UA-9209</t>
-  </si>
-  <si>
-    <t>SC9314UA-94M</t>
-  </si>
-  <si>
-    <t>SC9314UA-BK</t>
-  </si>
-  <si>
-    <t>SC9314UA-CF-0XAK-2414</t>
-  </si>
-  <si>
-    <t>SC9314UA-CF-0XAK-94M</t>
-  </si>
-  <si>
-    <t>SC9314UA-CF-0XAK-17CA</t>
-  </si>
-  <si>
-    <t>STC9906J</t>
-  </si>
-  <si>
-    <t>SC2462SO</t>
-  </si>
-  <si>
-    <t>SC2462SO-2462</t>
-  </si>
-  <si>
-    <t>SC2462SO-6472</t>
-  </si>
-  <si>
-    <t>SC2462UA</t>
-  </si>
-  <si>
-    <t>SC2462UA-2462</t>
-  </si>
-  <si>
-    <t>SC2462UA-BK</t>
-  </si>
-  <si>
-    <t>SC2462UA-CJ-10AK-2462</t>
-  </si>
-  <si>
-    <t>SC2462UA-CJ-10AK-6472</t>
-  </si>
-  <si>
-    <t>SC2462UA-CJ-10HK-6472</t>
-  </si>
-  <si>
-    <t>SC2464SO</t>
-  </si>
-  <si>
-    <t>SC2464SO-2464</t>
-  </si>
-  <si>
-    <t>SC2464UA</t>
-  </si>
-  <si>
-    <t>SC2464UA-2464</t>
-  </si>
-  <si>
-    <t>SC2462SO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2462SO-Q-CJ-10CR-2462</t>
-  </si>
-  <si>
-    <t>SC2464SO-TR</t>
-  </si>
-  <si>
-    <t>SC2464SO-CJ-10CR-2464</t>
-  </si>
-  <si>
-    <t>STC9906I</t>
-  </si>
-  <si>
-    <t>PSTC9906I</t>
-  </si>
-  <si>
-    <t>SC2430UA</t>
-  </si>
-  <si>
-    <t>SC2430UA-2430</t>
-  </si>
-  <si>
-    <t>SC2430UA-BK</t>
-  </si>
-  <si>
-    <t>SC2430UA-CI-10AK-2430</t>
-  </si>
-  <si>
-    <t>SC2432HUA</t>
-  </si>
-  <si>
-    <t>SC2432HUA-2432H</t>
-  </si>
-  <si>
-    <t>SC2432SO</t>
-  </si>
-  <si>
-    <t>NM.SC2432SO</t>
-  </si>
-  <si>
-    <t>SC2432SO-2432</t>
-  </si>
-  <si>
-    <t>SC2432SO-N</t>
-  </si>
-  <si>
-    <t>SC2432SO-N-2432</t>
-  </si>
-  <si>
-    <t>SC2432UA</t>
-  </si>
-  <si>
-    <t>SC2432UA-1101</t>
-  </si>
-  <si>
-    <t>SC2432UA-2432</t>
-  </si>
-  <si>
-    <t>SC2432UA-6232</t>
-  </si>
-  <si>
-    <t>SC2434SO</t>
-  </si>
-  <si>
-    <t>SC2434SO-2434</t>
-  </si>
-  <si>
-    <t>SC2434SO-N</t>
-  </si>
-  <si>
-    <t>SC2434SO-N-2434</t>
-  </si>
-  <si>
-    <t>SC2434UA</t>
-  </si>
-  <si>
-    <t>SC2434UA-2434</t>
-  </si>
-  <si>
-    <t>SC2434UA-BK</t>
-  </si>
-  <si>
-    <t>SC2434UA-CI-10AK-2434</t>
-  </si>
-  <si>
-    <t>SC2436SO</t>
-  </si>
-  <si>
-    <t>SC2436SO-2436</t>
-  </si>
-  <si>
-    <t>SC2436UA</t>
-  </si>
-  <si>
-    <t>SC2436UA-2436</t>
-  </si>
-  <si>
-    <t>SC2438SO</t>
-  </si>
-  <si>
-    <t>SC2438SO-2438</t>
-  </si>
-  <si>
-    <t>SC2438UA</t>
-  </si>
-  <si>
-    <t>SC2438UA-2438</t>
-  </si>
-  <si>
-    <t>SC243XUA</t>
-  </si>
-  <si>
-    <t>NA.SC243XUA</t>
-  </si>
-  <si>
-    <t>NF.SC243XUA-243X</t>
-  </si>
-  <si>
-    <t>SC243XUA-243X</t>
-  </si>
-  <si>
-    <t>SC2434SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC2434SO-N-CI-10CR-2434</t>
-  </si>
-  <si>
-    <t>SC2432SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC2432SO-N-CI-10CR-2432</t>
-  </si>
-  <si>
-    <t>SC2438UA-BK</t>
-  </si>
-  <si>
-    <t>SC2438UA-CI-10AK-2438</t>
-  </si>
-  <si>
-    <t>STC9G002A</t>
-  </si>
-  <si>
-    <t>PSTC9G002A</t>
-  </si>
-  <si>
-    <t>PSTC9G002A-0</t>
-  </si>
-  <si>
-    <t>SC2402LSO-N-177</t>
-  </si>
-  <si>
-    <t>SC2402LSO-N-2402</t>
-  </si>
-  <si>
-    <t>SC2402SO-N（STC9G002A)-G-2402</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-G</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-G(STC9G002A)-177</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-GA-00LR-2402</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-GA-00NR-2402</t>
-  </si>
-  <si>
-    <t>SC2402LUA-2402</t>
-  </si>
-  <si>
-    <t>预测</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>未交</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出货</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>订单</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>STC2899AJ</t>
+  </si>
+  <si>
+    <t>STC9902E</t>
+  </si>
+  <si>
+    <t>STC9906H</t>
+  </si>
+  <si>
+    <t>STC9902D</t>
+  </si>
+  <si>
+    <t>STC9906M</t>
+  </si>
+  <si>
+    <t>STC11103D</t>
+  </si>
+  <si>
+    <t>STC9906K</t>
+  </si>
+  <si>
+    <t>STC9906O</t>
+  </si>
+  <si>
+    <t>STC11300C</t>
+  </si>
+  <si>
+    <t>STC11131A</t>
+  </si>
+  <si>
+    <t>STC11210G-Q</t>
+  </si>
+  <si>
+    <t>STC4001AB</t>
+  </si>
+  <si>
+    <t>STC4000AA</t>
+  </si>
+  <si>
+    <t>STC4011C</t>
+  </si>
+  <si>
+    <t>STC11201B1</t>
+  </si>
+  <si>
+    <t>STC11401A</t>
+  </si>
+  <si>
+    <t>STC11202B</t>
+  </si>
+  <si>
+    <t>STC9907D</t>
+  </si>
+  <si>
+    <t>STC9D01F</t>
+  </si>
+  <si>
+    <t>STC11205B</t>
+  </si>
+  <si>
+    <t>STC11205A_T</t>
+  </si>
+  <si>
+    <t>SC4009D</t>
+  </si>
+  <si>
+    <t>STC9D02C</t>
+  </si>
+  <si>
+    <t>STC9D05C</t>
+  </si>
+  <si>
+    <t>STC9H002DQ</t>
+  </si>
+  <si>
+    <t>STC9A002B</t>
+  </si>
+  <si>
+    <t>STC12100B</t>
+  </si>
+  <si>
+    <t>STC22304C</t>
+  </si>
+  <si>
+    <t>STC16100B</t>
+  </si>
+  <si>
+    <t>STC35301</t>
+  </si>
+  <si>
+    <t>VA2201D</t>
+  </si>
+  <si>
+    <t>VA2201E</t>
+  </si>
+  <si>
+    <t>V2302C</t>
+  </si>
+  <si>
+    <t>STC9D06G</t>
+  </si>
+  <si>
+    <t>STC9G001D</t>
+  </si>
+  <si>
+    <t>STC9913D</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1895,18 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1753,67 +2192,67 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D1" s="3" t="s">
-        <v>450</v>
+        <v>203</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>453</v>
+        <v>206</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>452</v>
+        <v>205</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>450</v>
+        <v>203</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>451</v>
+        <v>204</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>452</v>
+        <v>205</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>450</v>
+        <v>203</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>451</v>
+        <v>204</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>452</v>
+        <v>205</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>450</v>
+        <v>203</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>451</v>
+        <v>204</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>452</v>
+        <v>205</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>450</v>
+        <v>203</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>451</v>
+        <v>204</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>452</v>
+        <v>205</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>451</v>
+        <v>204</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>450</v>
+        <v>203</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>452</v>
+        <v>205</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>450</v>
+        <v>203</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>451</v>
+        <v>204</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>452</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
@@ -1892,68 +2331,68 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>177</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>189</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -1961,3076 +2400,3083 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>517</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>330</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>201</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>520</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>331</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>518</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>333</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>334</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>521</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>335</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>336</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>279</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>337</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>522</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>338</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>339</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>165</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>167</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
       <c r="C26" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>167</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>167</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>167</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>523</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>340</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
+        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>524</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>342</v>
       </c>
       <c r="C40" t="s">
-        <v>67</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>297</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B43" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>298</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>515</v>
       </c>
       <c r="C44" t="s">
-        <v>72</v>
+        <v>344</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>328</v>
       </c>
       <c r="B45" t="s">
-        <v>68</v>
+        <v>293</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>292</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>329</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>525</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>514</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>345</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="C49" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="B51" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="C51" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="B52" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="B53" t="s">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="C53" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="B54" t="s">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="C54" t="s">
-        <v>89</v>
+        <v>346</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>80</v>
+        <v>526</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>347</v>
       </c>
       <c r="C55" t="s">
-        <v>91</v>
+        <v>348</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>80</v>
+        <v>526</v>
       </c>
       <c r="B56" t="s">
-        <v>90</v>
+        <v>349</v>
       </c>
       <c r="C56" t="s">
-        <v>92</v>
+        <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>510</v>
       </c>
       <c r="C57" t="s">
-        <v>94</v>
+        <v>511</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>80</v>
+        <v>516</v>
       </c>
       <c r="B58" t="s">
-        <v>95</v>
+        <v>351</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
+        <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>516</v>
       </c>
       <c r="B59" t="s">
-        <v>95</v>
+        <v>353</v>
       </c>
       <c r="C59" t="s">
-        <v>97</v>
+        <v>354</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>80</v>
+        <v>516</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>355</v>
       </c>
       <c r="C60" t="s">
-        <v>99</v>
+        <v>356</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>527</v>
       </c>
       <c r="B61" t="s">
-        <v>100</v>
+        <v>357</v>
       </c>
       <c r="C61" t="s">
-        <v>101</v>
+        <v>358</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>102</v>
+        <v>528</v>
       </c>
       <c r="B62" t="s">
-        <v>103</v>
+        <v>359</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>360</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>102</v>
+        <v>528</v>
       </c>
       <c r="B63" t="s">
-        <v>103</v>
+        <v>359</v>
       </c>
       <c r="C63" t="s">
-        <v>105</v>
+        <v>361</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>527</v>
       </c>
       <c r="B64" t="s">
-        <v>103</v>
+        <v>362</v>
       </c>
       <c r="C64" t="s">
-        <v>106</v>
+        <v>363</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>528</v>
       </c>
       <c r="B65" t="s">
-        <v>103</v>
+        <v>364</v>
       </c>
       <c r="C65" t="s">
-        <v>107</v>
+        <v>365</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C66" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>102</v>
+        <v>200</v>
       </c>
       <c r="B67" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="C67" t="s">
-        <v>110</v>
+        <v>202</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="C68" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="B69" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="C69" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="C70" t="s">
-        <v>115</v>
+        <v>307</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="B71" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="C71" t="s">
-        <v>117</v>
+        <v>366</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="B72" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="C72" t="s">
-        <v>118</v>
+        <v>367</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>102</v>
+        <v>221</v>
       </c>
       <c r="B73" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
       <c r="C73" t="s">
-        <v>119</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>102</v>
+        <v>221</v>
       </c>
       <c r="B74" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="C74" t="s">
-        <v>121</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>122</v>
+        <v>221</v>
       </c>
       <c r="B75" t="s">
-        <v>123</v>
+        <v>214</v>
       </c>
       <c r="C75" t="s">
-        <v>124</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>122</v>
+        <v>221</v>
       </c>
       <c r="B76" t="s">
-        <v>125</v>
+        <v>214</v>
       </c>
       <c r="C76" t="s">
-        <v>126</v>
+        <v>217</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>122</v>
+        <v>221</v>
       </c>
       <c r="B77" t="s">
-        <v>125</v>
+        <v>214</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>215</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="B78" t="s">
-        <v>129</v>
+        <v>214</v>
       </c>
       <c r="C78" t="s">
-        <v>130</v>
+        <v>216</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B79" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C79" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>131</v>
+        <v>529</v>
       </c>
       <c r="B80" t="s">
-        <v>132</v>
+        <v>368</v>
       </c>
       <c r="C80" t="s">
-        <v>134</v>
+        <v>369</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="B81" t="s">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="C81" t="s">
-        <v>135</v>
+        <v>192</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="B82" t="s">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="C82" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="B83" t="s">
-        <v>138</v>
+        <v>272</v>
       </c>
       <c r="C83" t="s">
-        <v>139</v>
+        <v>273</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>131</v>
+        <v>259</v>
       </c>
       <c r="B84" t="s">
-        <v>138</v>
+        <v>277</v>
       </c>
       <c r="C84" t="s">
-        <v>140</v>
+        <v>278</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>141</v>
+        <v>259</v>
       </c>
       <c r="B85" t="s">
-        <v>142</v>
+        <v>274</v>
       </c>
       <c r="C85" t="s">
-        <v>143</v>
+        <v>275</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>141</v>
+        <v>259</v>
       </c>
       <c r="B86" t="s">
-        <v>144</v>
+        <v>274</v>
       </c>
       <c r="C86" t="s">
-        <v>145</v>
+        <v>276</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>141</v>
+        <v>530</v>
       </c>
       <c r="B87" t="s">
-        <v>144</v>
+        <v>370</v>
       </c>
       <c r="C87" t="s">
-        <v>146</v>
+        <v>371</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="B88" t="s">
-        <v>144</v>
+        <v>269</v>
       </c>
       <c r="C88" t="s">
-        <v>147</v>
+        <v>271</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="B89" t="s">
-        <v>144</v>
+        <v>269</v>
       </c>
       <c r="C89" t="s">
-        <v>148</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="B90" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="C90" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>141</v>
+        <v>259</v>
       </c>
       <c r="B91" t="s">
-        <v>144</v>
+        <v>267</v>
       </c>
       <c r="C91" t="s">
-        <v>150</v>
+        <v>268</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="B92" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="C92" t="s">
-        <v>151</v>
+        <v>256</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>141</v>
+        <v>259</v>
       </c>
       <c r="B93" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C93" t="s">
-        <v>152</v>
+        <v>266</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="B94" t="s">
-        <v>154</v>
+        <v>264</v>
       </c>
       <c r="C94" t="s">
-        <v>155</v>
+        <v>265</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="B95" t="s">
-        <v>156</v>
+        <v>260</v>
       </c>
       <c r="C95" t="s">
-        <v>157</v>
+        <v>262</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="B96" t="s">
-        <v>156</v>
+        <v>260</v>
       </c>
       <c r="C96" t="s">
-        <v>158</v>
+        <v>261</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="B97" t="s">
-        <v>159</v>
+        <v>255</v>
       </c>
       <c r="C97" t="s">
-        <v>160</v>
+        <v>257</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="B98" t="s">
-        <v>159</v>
+        <v>258</v>
       </c>
       <c r="C98" t="s">
-        <v>161</v>
+        <v>291</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="B99" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="C99" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>153</v>
+        <v>530</v>
       </c>
       <c r="B100" t="s">
-        <v>162</v>
+        <v>372</v>
       </c>
       <c r="C100" t="s">
-        <v>164</v>
+        <v>373</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
       <c r="B101" t="s">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="C101" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
       <c r="B102" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="C102" t="s">
-        <v>168</v>
+        <v>74</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="B103" t="s">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="C103" t="s">
-        <v>171</v>
+        <v>73</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="B104" t="s">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="C104" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>169</v>
+        <v>254</v>
       </c>
       <c r="B105" t="s">
-        <v>172</v>
+        <v>252</v>
       </c>
       <c r="C105" t="s">
-        <v>174</v>
+        <v>253</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="B106" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="C106" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="B107" t="s">
-        <v>175</v>
+        <v>374</v>
       </c>
       <c r="C107" t="s">
-        <v>177</v>
+        <v>375</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="B108" t="s">
-        <v>178</v>
+        <v>374</v>
       </c>
       <c r="C108" t="s">
-        <v>179</v>
+        <v>376</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="B109" t="s">
-        <v>180</v>
+        <v>249</v>
       </c>
       <c r="C109" t="s">
-        <v>181</v>
+        <v>250</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="B110" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="C110" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>169</v>
+        <v>243</v>
       </c>
       <c r="B111" t="s">
-        <v>182</v>
+        <v>247</v>
       </c>
       <c r="C111" t="s">
-        <v>184</v>
+        <v>248</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>169</v>
+        <v>243</v>
       </c>
       <c r="B112" t="s">
-        <v>182</v>
+        <v>245</v>
       </c>
       <c r="C112" t="s">
-        <v>185</v>
+        <v>246</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>169</v>
+        <v>243</v>
       </c>
       <c r="B113" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
       <c r="C113" t="s">
-        <v>187</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="B114" t="s">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>189</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>169</v>
+        <v>243</v>
       </c>
       <c r="B115" t="s">
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="C115" t="s">
-        <v>191</v>
+        <v>290</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>192</v>
+        <v>531</v>
       </c>
       <c r="B116" t="s">
-        <v>193</v>
+        <v>378</v>
       </c>
       <c r="C116" t="s">
-        <v>193</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>192</v>
+        <v>532</v>
       </c>
       <c r="B117" t="s">
-        <v>194</v>
+        <v>380</v>
       </c>
       <c r="C117" t="s">
-        <v>195</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B118" t="s">
-        <v>194</v>
+        <v>319</v>
       </c>
       <c r="C118" t="s">
-        <v>196</v>
+        <v>320</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B119" t="s">
-        <v>197</v>
+        <v>240</v>
       </c>
       <c r="C119" t="s">
-        <v>198</v>
+        <v>241</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B120" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="C120" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B121" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C121" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B122" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C122" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B123" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C123" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>192</v>
+        <v>533</v>
       </c>
       <c r="B124" t="s">
-        <v>204</v>
+        <v>382</v>
       </c>
       <c r="C124" t="s">
-        <v>204</v>
+        <v>383</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="B125" t="s">
-        <v>205</v>
+        <v>162</v>
       </c>
       <c r="C125" t="s">
-        <v>205</v>
+        <v>321</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="B126" t="s">
-        <v>206</v>
+        <v>162</v>
       </c>
       <c r="C126" t="s">
-        <v>206</v>
+        <v>384</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="B127" t="s">
-        <v>207</v>
+        <v>385</v>
       </c>
       <c r="C127" t="s">
-        <v>207</v>
+        <v>386</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>192</v>
+        <v>534</v>
       </c>
       <c r="B128" t="s">
-        <v>208</v>
+        <v>387</v>
       </c>
       <c r="C128" t="s">
-        <v>208</v>
+        <v>388</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="B129" t="s">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="C129" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="B130" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="C130" t="s">
-        <v>210</v>
+        <v>389</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>192</v>
+        <v>535</v>
       </c>
       <c r="B131" t="s">
-        <v>211</v>
+        <v>390</v>
       </c>
       <c r="C131" t="s">
-        <v>211</v>
+        <v>391</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>192</v>
+        <v>535</v>
       </c>
       <c r="B132" t="s">
-        <v>212</v>
+        <v>392</v>
       </c>
       <c r="C132" t="s">
-        <v>212</v>
+        <v>393</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>192</v>
+        <v>535</v>
       </c>
       <c r="B133" t="s">
-        <v>213</v>
+        <v>394</v>
       </c>
       <c r="C133" t="s">
-        <v>213</v>
+        <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>192</v>
+        <v>536</v>
       </c>
       <c r="B134" t="s">
-        <v>214</v>
+        <v>396</v>
       </c>
       <c r="C134" t="s">
-        <v>214</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>192</v>
+        <v>536</v>
       </c>
       <c r="B135" t="s">
-        <v>215</v>
+        <v>398</v>
       </c>
       <c r="C135" t="s">
-        <v>215</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>192</v>
+        <v>536</v>
       </c>
       <c r="B136" t="s">
-        <v>216</v>
+        <v>400</v>
       </c>
       <c r="C136" t="s">
-        <v>216</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>192</v>
+        <v>536</v>
       </c>
       <c r="B137" t="s">
-        <v>217</v>
+        <v>402</v>
       </c>
       <c r="C137" t="s">
-        <v>217</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="B138" t="s">
-        <v>218</v>
+        <v>160</v>
       </c>
       <c r="C138" t="s">
-        <v>218</v>
+        <v>161</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="B139" t="s">
-        <v>219</v>
+        <v>404</v>
       </c>
       <c r="C139" t="s">
-        <v>219</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="B140" t="s">
-        <v>220</v>
+        <v>406</v>
       </c>
       <c r="C140" t="s">
-        <v>221</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>192</v>
+        <v>519</v>
       </c>
       <c r="B141" t="s">
-        <v>220</v>
+        <v>408</v>
       </c>
       <c r="C141" t="s">
-        <v>222</v>
+        <v>409</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>192</v>
+        <v>559</v>
       </c>
       <c r="B142" t="s">
-        <v>220</v>
+        <v>508</v>
       </c>
       <c r="C142" t="s">
-        <v>223</v>
+        <v>509</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>192</v>
+        <v>537</v>
       </c>
       <c r="B143" t="s">
-        <v>224</v>
+        <v>410</v>
       </c>
       <c r="C143" t="s">
-        <v>225</v>
+        <v>411</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>192</v>
+        <v>538</v>
       </c>
       <c r="B144" t="s">
-        <v>224</v>
+        <v>412</v>
       </c>
       <c r="C144" t="s">
-        <v>226</v>
+        <v>413</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>192</v>
+        <v>538</v>
       </c>
       <c r="B145" t="s">
-        <v>224</v>
+        <v>414</v>
       </c>
       <c r="C145" t="s">
-        <v>227</v>
+        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>192</v>
+        <v>538</v>
       </c>
       <c r="B146" t="s">
-        <v>228</v>
+        <v>416</v>
       </c>
       <c r="C146" t="s">
-        <v>229</v>
+        <v>417</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>192</v>
+        <v>538</v>
       </c>
       <c r="B147" t="s">
-        <v>228</v>
+        <v>418</v>
       </c>
       <c r="C147" t="s">
-        <v>230</v>
+        <v>419</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>231</v>
+        <v>538</v>
       </c>
       <c r="B148" t="s">
-        <v>232</v>
+        <v>418</v>
       </c>
       <c r="C148" t="s">
-        <v>233</v>
+        <v>420</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>231</v>
+        <v>38</v>
       </c>
       <c r="B149" t="s">
-        <v>232</v>
+        <v>421</v>
       </c>
       <c r="C149" t="s">
-        <v>234</v>
+        <v>422</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>231</v>
+        <v>38</v>
       </c>
       <c r="B150" t="s">
-        <v>235</v>
+        <v>39</v>
       </c>
       <c r="C150" t="s">
-        <v>236</v>
+        <v>40</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B151" t="s">
-        <v>237</v>
+        <v>60</v>
       </c>
       <c r="C151" t="s">
-        <v>238</v>
+        <v>61</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B152" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>239</v>
+        <v>68</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B153" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="C153" t="s">
-        <v>240</v>
+        <v>69</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B154" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="C154" t="s">
-        <v>241</v>
+        <v>67</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B155" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="C155" t="s">
-        <v>242</v>
+        <v>66</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B156" t="s">
-        <v>243</v>
+        <v>62</v>
       </c>
       <c r="C156" t="s">
-        <v>244</v>
+        <v>65</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B157" t="s">
-        <v>245</v>
+        <v>62</v>
       </c>
       <c r="C157" t="s">
-        <v>246</v>
+        <v>64</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B158" t="s">
-        <v>247</v>
+        <v>62</v>
       </c>
       <c r="C158" t="s">
-        <v>248</v>
+        <v>63</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>231</v>
+        <v>539</v>
       </c>
       <c r="B159" t="s">
-        <v>247</v>
+        <v>423</v>
       </c>
       <c r="C159" t="s">
-        <v>249</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>231</v>
+        <v>540</v>
       </c>
       <c r="B160" t="s">
-        <v>250</v>
+        <v>425</v>
       </c>
       <c r="C160" t="s">
-        <v>251</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>231</v>
+        <v>540</v>
       </c>
       <c r="B161" t="s">
-        <v>252</v>
+        <v>427</v>
       </c>
       <c r="C161" t="s">
-        <v>253</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>231</v>
+        <v>541</v>
       </c>
       <c r="B162" t="s">
-        <v>120</v>
+        <v>429</v>
       </c>
       <c r="C162" t="s">
-        <v>254</v>
+        <v>430</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>255</v>
+        <v>542</v>
       </c>
       <c r="B163" t="s">
-        <v>256</v>
+        <v>431</v>
       </c>
       <c r="C163" t="s">
-        <v>257</v>
+        <v>432</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>255</v>
+        <v>543</v>
       </c>
       <c r="B164" t="s">
-        <v>258</v>
+        <v>433</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>255</v>
+        <v>543</v>
       </c>
       <c r="B165" t="s">
-        <v>258</v>
+        <v>435</v>
       </c>
       <c r="C165" t="s">
-        <v>260</v>
+        <v>436</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>255</v>
+        <v>3</v>
       </c>
       <c r="B166" t="s">
-        <v>261</v>
+        <v>5</v>
       </c>
       <c r="C166" t="s">
-        <v>262</v>
+        <v>6</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B167" t="s">
-        <v>264</v>
+        <v>5</v>
       </c>
       <c r="C167" t="s">
-        <v>265</v>
+        <v>437</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B168" t="s">
-        <v>266</v>
+        <v>24</v>
       </c>
       <c r="C168" t="s">
-        <v>266</v>
+        <v>25</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B169" t="s">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="C169" t="s">
-        <v>267</v>
+        <v>209</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B170" t="s">
-        <v>268</v>
+        <v>7</v>
       </c>
       <c r="C170" t="s">
-        <v>269</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B171" t="s">
-        <v>270</v>
+        <v>9</v>
       </c>
       <c r="C171" t="s">
-        <v>271</v>
+        <v>10</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B172" t="s">
-        <v>270</v>
+        <v>9</v>
       </c>
       <c r="C172" t="s">
-        <v>272</v>
+        <v>11</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B173" t="s">
-        <v>270</v>
+        <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>273</v>
+        <v>13</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B174" t="s">
-        <v>263</v>
+        <v>14</v>
       </c>
       <c r="C174" t="s">
-        <v>263</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>274</v>
+        <v>3</v>
       </c>
       <c r="B175" t="s">
-        <v>275</v>
+        <v>22</v>
       </c>
       <c r="C175" t="s">
-        <v>276</v>
+        <v>23</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>274</v>
+        <v>3</v>
       </c>
       <c r="B176" t="s">
-        <v>277</v>
+        <v>16</v>
       </c>
       <c r="C176" t="s">
-        <v>278</v>
+        <v>17</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
       <c r="B177" t="s">
-        <v>280</v>
+        <v>18</v>
       </c>
       <c r="C177" t="s">
-        <v>280</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
       <c r="B178" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="C178" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
       <c r="B179" t="s">
-        <v>281</v>
+        <v>20</v>
       </c>
       <c r="C179" t="s">
-        <v>283</v>
+        <v>21</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="B180" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="C180" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="B181" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="C181" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>279</v>
+        <v>42</v>
       </c>
       <c r="B182" t="s">
-        <v>285</v>
+        <v>48</v>
       </c>
       <c r="C182" t="s">
-        <v>287</v>
+        <v>49</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>279</v>
+        <v>42</v>
       </c>
       <c r="B183" t="s">
-        <v>285</v>
+        <v>43</v>
       </c>
       <c r="C183" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>279</v>
+        <v>42</v>
       </c>
       <c r="B184" t="s">
-        <v>289</v>
+        <v>43</v>
       </c>
       <c r="C184" t="s">
-        <v>290</v>
+        <v>44</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>279</v>
+        <v>42</v>
       </c>
       <c r="B185" t="s">
-        <v>289</v>
+        <v>45</v>
       </c>
       <c r="C185" t="s">
-        <v>291</v>
+        <v>47</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>279</v>
+        <v>42</v>
       </c>
       <c r="B186" t="s">
-        <v>289</v>
+        <v>45</v>
       </c>
       <c r="C186" t="s">
-        <v>292</v>
+        <v>46</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>279</v>
+        <v>544</v>
       </c>
       <c r="B187" t="s">
-        <v>293</v>
+        <v>438</v>
       </c>
       <c r="C187" t="s">
-        <v>294</v>
+        <v>439</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>279</v>
+        <v>545</v>
       </c>
       <c r="B188" t="s">
-        <v>279</v>
+        <v>440</v>
       </c>
       <c r="C188" t="s">
-        <v>279</v>
+        <v>441</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>295</v>
+        <v>546</v>
       </c>
       <c r="B189" t="s">
-        <v>296</v>
+        <v>442</v>
       </c>
       <c r="C189" t="s">
-        <v>297</v>
+        <v>443</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>295</v>
+        <v>547</v>
       </c>
       <c r="B190" t="s">
-        <v>296</v>
+        <v>444</v>
       </c>
       <c r="C190" t="s">
-        <v>298</v>
+        <v>445</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>295</v>
+        <v>548</v>
       </c>
       <c r="B191" t="s">
-        <v>156</v>
+        <v>446</v>
       </c>
       <c r="C191" t="s">
-        <v>299</v>
+        <v>447</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B192" t="s">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="C192" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B193" t="s">
-        <v>301</v>
+        <v>95</v>
       </c>
       <c r="C193" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B194" t="s">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="C194" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B195" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="C195" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B196" t="s">
-        <v>305</v>
+        <v>99</v>
       </c>
       <c r="C196" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B197" t="s">
-        <v>256</v>
+        <v>100</v>
       </c>
       <c r="C197" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B198" t="s">
-        <v>256</v>
+        <v>101</v>
       </c>
       <c r="C198" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B199" t="s">
-        <v>309</v>
+        <v>102</v>
       </c>
       <c r="C199" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B200" t="s">
-        <v>309</v>
+        <v>103</v>
       </c>
       <c r="C200" t="s">
-        <v>311</v>
-      </c>
-      <c r="G200" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B201" t="s">
-        <v>312</v>
+        <v>104</v>
       </c>
       <c r="C201" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B202" t="s">
-        <v>314</v>
+        <v>105</v>
       </c>
       <c r="C202" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>316</v>
+        <v>91</v>
       </c>
       <c r="B203" t="s">
-        <v>317</v>
+        <v>106</v>
       </c>
       <c r="C203" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B204" t="s">
-        <v>320</v>
+        <v>107</v>
       </c>
       <c r="C204" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B205" t="s">
-        <v>321</v>
+        <v>108</v>
       </c>
       <c r="C205" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>323</v>
+        <v>109</v>
       </c>
       <c r="C206" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B207" t="s">
-        <v>325</v>
+        <v>110</v>
       </c>
       <c r="C207" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B208" t="s">
-        <v>325</v>
+        <v>111</v>
       </c>
       <c r="C208" t="s">
-        <v>327</v>
+        <v>111</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B209" t="s">
-        <v>328</v>
+        <v>112</v>
       </c>
       <c r="C209" t="s">
-        <v>329</v>
+        <v>112</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B210" t="s">
-        <v>330</v>
+        <v>113</v>
       </c>
       <c r="C210" t="s">
-        <v>331</v>
+        <v>113</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B211" t="s">
-        <v>332</v>
+        <v>114</v>
       </c>
       <c r="C211" t="s">
-        <v>333</v>
+        <v>114</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B212" t="s">
-        <v>332</v>
+        <v>115</v>
       </c>
       <c r="C212" t="s">
-        <v>334</v>
+        <v>115</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B213" t="s">
-        <v>332</v>
+        <v>234</v>
       </c>
       <c r="C213" t="s">
-        <v>335</v>
+        <v>235</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B214" t="s">
-        <v>332</v>
+        <v>448</v>
       </c>
       <c r="C214" t="s">
-        <v>336</v>
+        <v>449</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B215" t="s">
-        <v>332</v>
+        <v>116</v>
       </c>
       <c r="C215" t="s">
-        <v>337</v>
+        <v>118</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B216" t="s">
-        <v>332</v>
+        <v>116</v>
       </c>
       <c r="C216" t="s">
-        <v>338</v>
+        <v>117</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>319</v>
+        <v>549</v>
       </c>
       <c r="B217" t="s">
-        <v>332</v>
+        <v>450</v>
       </c>
       <c r="C217" t="s">
-        <v>339</v>
+        <v>451</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>319</v>
+        <v>550</v>
       </c>
       <c r="B218" t="s">
-        <v>340</v>
+        <v>452</v>
       </c>
       <c r="C218" t="s">
-        <v>341</v>
+        <v>453</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>319</v>
+        <v>550</v>
       </c>
       <c r="B219" t="s">
-        <v>340</v>
+        <v>454</v>
       </c>
       <c r="C219" t="s">
-        <v>342</v>
+        <v>455</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>319</v>
+        <v>550</v>
       </c>
       <c r="B220" t="s">
-        <v>340</v>
+        <v>456</v>
       </c>
       <c r="C220" t="s">
-        <v>343</v>
+        <v>457</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>319</v>
+        <v>550</v>
       </c>
       <c r="B221" t="s">
-        <v>340</v>
+        <v>458</v>
       </c>
       <c r="C221" t="s">
-        <v>344</v>
+        <v>459</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>319</v>
+        <v>550</v>
       </c>
       <c r="B222" t="s">
-        <v>345</v>
+        <v>460</v>
       </c>
       <c r="C222" t="s">
-        <v>346</v>
+        <v>461</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>319</v>
+        <v>550</v>
       </c>
       <c r="B223" t="s">
-        <v>345</v>
+        <v>462</v>
       </c>
       <c r="C223" t="s">
-        <v>347</v>
+        <v>463</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>319</v>
+        <v>561</v>
       </c>
       <c r="B224" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="C224" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>350</v>
+        <v>177</v>
       </c>
       <c r="B225" t="s">
-        <v>351</v>
+        <v>179</v>
       </c>
       <c r="C225" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>350</v>
+        <v>177</v>
       </c>
       <c r="B226" t="s">
-        <v>351</v>
+        <v>179</v>
       </c>
       <c r="C226" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>350</v>
+        <v>177</v>
       </c>
       <c r="B227" t="s">
-        <v>354</v>
+        <v>179</v>
       </c>
       <c r="C227" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>350</v>
+        <v>177</v>
       </c>
       <c r="B228" t="s">
-        <v>354</v>
+        <v>179</v>
       </c>
       <c r="C228" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>350</v>
+        <v>177</v>
       </c>
       <c r="B229" t="s">
-        <v>357</v>
+        <v>179</v>
       </c>
       <c r="C229" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>359</v>
+        <v>177</v>
       </c>
       <c r="B230" t="s">
-        <v>360</v>
+        <v>179</v>
       </c>
       <c r="C230" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>359</v>
+        <v>177</v>
       </c>
       <c r="B231" t="s">
-        <v>50</v>
+        <v>233</v>
       </c>
       <c r="C231" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="G231" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="B232" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="C232" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="B233" t="s">
-        <v>50</v>
+        <v>326</v>
       </c>
       <c r="C233" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>365</v>
+        <v>174</v>
       </c>
       <c r="B234" t="s">
-        <v>366</v>
+        <v>175</v>
       </c>
       <c r="C234" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>365</v>
+        <v>174</v>
       </c>
       <c r="B235" t="s">
-        <v>367</v>
+        <v>210</v>
       </c>
       <c r="C235" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>365</v>
+        <v>174</v>
       </c>
       <c r="B236" t="s">
-        <v>367</v>
+        <v>286</v>
       </c>
       <c r="C236" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>365</v>
+        <v>174</v>
       </c>
       <c r="B237" t="s">
-        <v>367</v>
+        <v>317</v>
       </c>
       <c r="C237" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>365</v>
+        <v>174</v>
       </c>
       <c r="B238" t="s">
-        <v>367</v>
+        <v>288</v>
       </c>
       <c r="C238" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>365</v>
+        <v>141</v>
       </c>
       <c r="B239" t="s">
-        <v>367</v>
+        <v>142</v>
       </c>
       <c r="C239" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>365</v>
+        <v>141</v>
       </c>
       <c r="B240" t="s">
-        <v>367</v>
+        <v>281</v>
       </c>
       <c r="C240" t="s">
-        <v>373</v>
+        <v>283</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>365</v>
+        <v>141</v>
       </c>
       <c r="B241" t="s">
-        <v>374</v>
+        <v>282</v>
       </c>
       <c r="C241" t="s">
-        <v>375</v>
+        <v>285</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>365</v>
+        <v>141</v>
       </c>
       <c r="B242" t="s">
-        <v>374</v>
+        <v>282</v>
       </c>
       <c r="C242" t="s">
-        <v>376</v>
+        <v>284</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>365</v>
+        <v>26</v>
       </c>
       <c r="B243" t="s">
-        <v>374</v>
+        <v>27</v>
       </c>
       <c r="C243" t="s">
-        <v>377</v>
+        <v>28</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>378</v>
+        <v>26</v>
       </c>
       <c r="B244" t="s">
-        <v>379</v>
+        <v>29</v>
       </c>
       <c r="C244" t="s">
-        <v>380</v>
+        <v>30</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>378</v>
+        <v>26</v>
       </c>
       <c r="B245" t="s">
-        <v>379</v>
+        <v>31</v>
       </c>
       <c r="C245" t="s">
-        <v>381</v>
+        <v>32</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>378</v>
+        <v>26</v>
       </c>
       <c r="B246" t="s">
-        <v>382</v>
+        <v>33</v>
       </c>
       <c r="C246" t="s">
-        <v>383</v>
+        <v>34</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>378</v>
+        <v>26</v>
       </c>
       <c r="B247" t="s">
-        <v>384</v>
+        <v>33</v>
       </c>
       <c r="C247" t="s">
-        <v>385</v>
+        <v>35</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>378</v>
+        <v>26</v>
       </c>
       <c r="B248" t="s">
-        <v>384</v>
+        <v>33</v>
       </c>
       <c r="C248" t="s">
-        <v>386</v>
+        <v>464</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>378</v>
+        <v>26</v>
       </c>
       <c r="B249" t="s">
-        <v>384</v>
+        <v>314</v>
       </c>
       <c r="C249" t="s">
-        <v>387</v>
+        <v>315</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>378</v>
+        <v>52</v>
       </c>
       <c r="B250" t="s">
-        <v>388</v>
+        <v>53</v>
       </c>
       <c r="C250" t="s">
-        <v>389</v>
+        <v>54</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>378</v>
+        <v>52</v>
       </c>
       <c r="B251" t="s">
-        <v>390</v>
+        <v>53</v>
       </c>
       <c r="C251" t="s">
-        <v>391</v>
+        <v>55</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>378</v>
+        <v>56</v>
       </c>
       <c r="B252" t="s">
-        <v>392</v>
+        <v>57</v>
       </c>
       <c r="C252" t="s">
-        <v>393</v>
+        <v>58</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>378</v>
+        <v>56</v>
       </c>
       <c r="B253" t="s">
-        <v>394</v>
+        <v>465</v>
       </c>
       <c r="C253" t="s">
-        <v>395</v>
+        <v>466</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>396</v>
+        <v>56</v>
       </c>
       <c r="B254" t="s">
-        <v>397</v>
+        <v>311</v>
       </c>
       <c r="C254" t="s">
-        <v>397</v>
+        <v>312</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>396</v>
+        <v>56</v>
       </c>
       <c r="B255" t="s">
-        <v>398</v>
+        <v>311</v>
       </c>
       <c r="C255" t="s">
-        <v>399</v>
+        <v>313</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>396</v>
+        <v>308</v>
       </c>
       <c r="B256" t="s">
-        <v>400</v>
+        <v>309</v>
       </c>
       <c r="C256" t="s">
-        <v>401</v>
+        <v>310</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>396</v>
+        <v>26</v>
       </c>
       <c r="B257" t="s">
-        <v>402</v>
+        <v>227</v>
       </c>
       <c r="C257" t="s">
-        <v>403</v>
+        <v>228</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>396</v>
+        <v>26</v>
       </c>
       <c r="B258" t="s">
-        <v>404</v>
+        <v>36</v>
       </c>
       <c r="C258" t="s">
-        <v>405</v>
+        <v>37</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>396</v>
+        <v>551</v>
       </c>
       <c r="B259" t="s">
-        <v>404</v>
+        <v>467</v>
       </c>
       <c r="C259" t="s">
-        <v>406</v>
+        <v>468</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>396</v>
+        <v>551</v>
       </c>
       <c r="B260" t="s">
-        <v>407</v>
+        <v>469</v>
       </c>
       <c r="C260" t="s">
-        <v>408</v>
+        <v>470</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>396</v>
+        <v>551</v>
       </c>
       <c r="B261" t="s">
-        <v>409</v>
+        <v>471</v>
       </c>
       <c r="C261" t="s">
-        <v>410</v>
+        <v>472</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>396</v>
+        <v>551</v>
       </c>
       <c r="B262" t="s">
-        <v>409</v>
+        <v>473</v>
       </c>
       <c r="C262" t="s">
-        <v>411</v>
+        <v>474</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>396</v>
+        <v>551</v>
       </c>
       <c r="B263" t="s">
-        <v>409</v>
+        <v>475</v>
       </c>
       <c r="C263" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>396</v>
+        <v>551</v>
       </c>
       <c r="B264" t="s">
-        <v>413</v>
+        <v>477</v>
       </c>
       <c r="C264" t="s">
-        <v>414</v>
+        <v>478</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>396</v>
+        <v>552</v>
       </c>
       <c r="B265" t="s">
-        <v>415</v>
+        <v>479</v>
       </c>
       <c r="C265" t="s">
-        <v>416</v>
+        <v>480</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>396</v>
+        <v>552</v>
       </c>
       <c r="B266" t="s">
-        <v>417</v>
+        <v>481</v>
       </c>
       <c r="C266" t="s">
-        <v>418</v>
+        <v>482</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>396</v>
+        <v>552</v>
       </c>
       <c r="B267" t="s">
-        <v>419</v>
+        <v>483</v>
       </c>
       <c r="C267" t="s">
-        <v>420</v>
+        <v>484</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>396</v>
+        <v>225</v>
       </c>
       <c r="B268" t="s">
-        <v>421</v>
+        <v>222</v>
       </c>
       <c r="C268" t="s">
-        <v>422</v>
+        <v>223</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>396</v>
+        <v>225</v>
       </c>
       <c r="B269" t="s">
-        <v>423</v>
+        <v>222</v>
       </c>
       <c r="C269" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>396</v>
+        <v>138</v>
       </c>
       <c r="B270" t="s">
-        <v>425</v>
+        <v>139</v>
       </c>
       <c r="C270" t="s">
-        <v>426</v>
+        <v>226</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>396</v>
+        <v>138</v>
       </c>
       <c r="B271" t="s">
-        <v>427</v>
+        <v>139</v>
       </c>
       <c r="C271" t="s">
-        <v>428</v>
+        <v>140</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>396</v>
+        <v>553</v>
       </c>
       <c r="B272" t="s">
-        <v>429</v>
+        <v>485</v>
       </c>
       <c r="C272" t="s">
-        <v>430</v>
+        <v>486</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>396</v>
+        <v>553</v>
       </c>
       <c r="B273" t="s">
-        <v>429</v>
+        <v>485</v>
       </c>
       <c r="C273" t="s">
-        <v>431</v>
+        <v>487</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>396</v>
+        <v>554</v>
       </c>
       <c r="B274" t="s">
-        <v>429</v>
+        <v>488</v>
       </c>
       <c r="C274" t="s">
-        <v>432</v>
+        <v>489</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>396</v>
+        <v>554</v>
       </c>
       <c r="B275" t="s">
-        <v>433</v>
+        <v>490</v>
       </c>
       <c r="C275" t="s">
-        <v>434</v>
+        <v>491</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>396</v>
+        <v>555</v>
       </c>
       <c r="B276" t="s">
-        <v>435</v>
+        <v>492</v>
       </c>
       <c r="C276" t="s">
-        <v>436</v>
+        <v>493</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>396</v>
+        <v>38</v>
       </c>
       <c r="B277" t="s">
-        <v>437</v>
+        <v>41</v>
       </c>
       <c r="C277" t="s">
-        <v>438</v>
+        <v>41</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>439</v>
+        <v>59</v>
       </c>
       <c r="B278" t="s">
-        <v>440</v>
+        <v>70</v>
       </c>
       <c r="C278" t="s">
-        <v>440</v>
+        <v>70</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>439</v>
+        <v>144</v>
       </c>
       <c r="B279" t="s">
-        <v>441</v>
+        <v>144</v>
       </c>
       <c r="C279" t="s">
-        <v>440</v>
+        <v>144</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>439</v>
+        <v>556</v>
       </c>
       <c r="B280" t="s">
-        <v>281</v>
+        <v>494</v>
       </c>
       <c r="C280" t="s">
-        <v>442</v>
+        <v>495</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>439</v>
+        <v>556</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>496</v>
       </c>
       <c r="C281" t="s">
-        <v>443</v>
+        <v>497</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>439</v>
+        <v>556</v>
       </c>
       <c r="B282" t="s">
-        <v>281</v>
+        <v>498</v>
       </c>
       <c r="C282" t="s">
-        <v>444</v>
+        <v>499</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>439</v>
+        <v>557</v>
       </c>
       <c r="B283" t="s">
-        <v>445</v>
+        <v>500</v>
       </c>
       <c r="C283" t="s">
-        <v>444</v>
+        <v>501</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>439</v>
+        <v>558</v>
       </c>
       <c r="B284" t="s">
-        <v>445</v>
+        <v>502</v>
       </c>
       <c r="C284" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>439</v>
+        <v>558</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>504</v>
       </c>
       <c r="C285" t="s">
-        <v>447</v>
+        <v>505</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>439</v>
+        <v>506</v>
       </c>
       <c r="B286" t="s">
-        <v>285</v>
+        <v>506</v>
       </c>
       <c r="C286" t="s">
-        <v>448</v>
+        <v>506</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>439</v>
+        <v>507</v>
       </c>
       <c r="B287" t="s">
-        <v>289</v>
+        <v>507</v>
       </c>
       <c r="C287" t="s">
-        <v>449</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:X186" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:X287">
+      <sortCondition ref="B2:B186"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C179:C1048576 C151:C177 C1:C149">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/预测分析.xlsx
+++ b/预测分析.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forecast\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forecast\预测分析\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E716B92-2D12-4DD6-A0FE-9882B6320998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1920A7A0-5E74-4196-B446-7D91A27557D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$X$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$X$288</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="565">
   <si>
     <t>晶圆</t>
   </si>
@@ -1826,6 +1826,17 @@
   </si>
   <si>
     <t>STC9913D</t>
+  </si>
+  <si>
+    <t>SC1945B1</t>
+  </si>
+  <si>
+    <t>SC1945B1(STC2899AJ)-N13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC2899AJ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2182,7 +2193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X287"/>
+  <dimension ref="A1:X288"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
@@ -5467,12 +5478,19 @@
         <v>507</v>
       </c>
     </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>564</v>
+      </c>
+      <c r="B288" t="s">
+        <v>562</v>
+      </c>
+      <c r="C288" t="s">
+        <v>563</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:X186" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:X287">
-      <sortCondition ref="B2:B186"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A2:X288" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C179:C1048576 C151:C177 C1:C149">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/预测分析.xlsx
+++ b/预测分析.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forecast\预测分析\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1920A7A0-5E74-4196-B446-7D91A27557D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511289BA-245C-4EAF-91E5-C6C454F3391C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$X$288</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$X$286</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="563">
   <si>
     <t>晶圆</t>
   </si>
@@ -486,9 +486,6 @@
     <t>SC2402SO-N-TR</t>
   </si>
   <si>
-    <t>SC2402SO-N-CJ-0XLR-6571</t>
-  </si>
-  <si>
     <t>SC2402SO-N-CJ-90NR-2402</t>
   </si>
   <si>
@@ -1237,12 +1234,6 @@
     <t>SC2242UA-Q-CH-10AK-2242</t>
   </si>
   <si>
-    <t>SC2402SO-N-CJ-00NR-2402</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-CJ-00NR-6571</t>
-  </si>
-  <si>
     <t>SC2413SO-N-TR</t>
   </si>
   <si>
@@ -1837,6 +1828,9 @@
   <si>
     <t>STC2899AJ</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402SO-N-CJ-90NR-6571</t>
   </si>
 </sst>
 </file>
@@ -2193,7 +2187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X288"/>
+  <dimension ref="A1:X286"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
@@ -2203,67 +2197,67 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D1" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M1" s="3" t="s">
+      <c r="P1" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="P1" s="3" t="s">
+      <c r="S1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="T1" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="U1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="V1" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="X1" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
@@ -2364,24 +2358,24 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" t="s">
         <v>163</v>
       </c>
-      <c r="B5" t="s">
-        <v>164</v>
-      </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" t="s">
         <v>177</v>
       </c>
-      <c r="B6" t="s">
-        <v>178</v>
-      </c>
       <c r="C6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -2397,13 +2391,13 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" t="s">
         <v>189</v>
       </c>
-      <c r="B8" t="s">
-        <v>190</v>
-      </c>
       <c r="C8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -2430,24 +2424,24 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12" t="s">
         <v>200</v>
       </c>
-      <c r="B12" t="s">
-        <v>201</v>
-      </c>
       <c r="C12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -2491,172 +2485,172 @@
         <v>125</v>
       </c>
       <c r="C16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B17" t="s">
+        <v>330</v>
+      </c>
+      <c r="C17" t="s">
         <v>331</v>
-      </c>
-      <c r="C17" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B18" t="s">
+        <v>332</v>
+      </c>
+      <c r="C18" t="s">
         <v>333</v>
-      </c>
-      <c r="C18" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B19" t="s">
+        <v>334</v>
+      </c>
+      <c r="C19" t="s">
         <v>335</v>
-      </c>
-      <c r="C19" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B20" t="s">
+        <v>278</v>
+      </c>
+      <c r="C20" t="s">
         <v>279</v>
-      </c>
-      <c r="C20" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" t="s">
         <v>172</v>
-      </c>
-      <c r="C21" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C22" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B23" t="s">
+        <v>337</v>
+      </c>
+      <c r="C23" t="s">
         <v>338</v>
-      </c>
-      <c r="C23" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B24" t="s">
+        <v>164</v>
+      </c>
+      <c r="C24" t="s">
         <v>165</v>
-      </c>
-      <c r="C24" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C27" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B29" t="s">
+        <v>166</v>
+      </c>
+      <c r="C29" t="s">
         <v>167</v>
-      </c>
-      <c r="C29" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B30" t="s">
+        <v>211</v>
+      </c>
+      <c r="C30" t="s">
         <v>212</v>
-      </c>
-      <c r="C30" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B31" t="s">
+        <v>339</v>
+      </c>
+      <c r="C31" t="s">
         <v>340</v>
-      </c>
-      <c r="C31" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2667,7 +2661,7 @@
         <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2741,21 +2735,21 @@
         <v>77</v>
       </c>
       <c r="B39" t="s">
+        <v>235</v>
+      </c>
+      <c r="C39" t="s">
         <v>236</v>
-      </c>
-      <c r="C39" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B40" t="s">
+        <v>341</v>
+      </c>
+      <c r="C40" t="s">
         <v>342</v>
-      </c>
-      <c r="C40" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2777,7 +2771,7 @@
         <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2788,7 +2782,7 @@
         <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2796,21 +2790,21 @@
         <v>119</v>
       </c>
       <c r="B44" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C44" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B45" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C45" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2832,18 +2826,18 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B48" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C48" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2909,128 +2903,128 @@
         <v>132</v>
       </c>
       <c r="C54" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B55" t="s">
+        <v>346</v>
+      </c>
+      <c r="C55" t="s">
         <v>347</v>
-      </c>
-      <c r="C55" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B56" t="s">
+        <v>348</v>
+      </c>
+      <c r="C56" t="s">
         <v>349</v>
-      </c>
-      <c r="C56" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B57" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C57" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B58" t="s">
+        <v>350</v>
+      </c>
+      <c r="C58" t="s">
         <v>351</v>
-      </c>
-      <c r="C58" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B59" t="s">
+        <v>352</v>
+      </c>
+      <c r="C59" t="s">
         <v>353</v>
-      </c>
-      <c r="C59" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B60" t="s">
+        <v>354</v>
+      </c>
+      <c r="C60" t="s">
         <v>355</v>
-      </c>
-      <c r="C60" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B61" t="s">
+        <v>356</v>
+      </c>
+      <c r="C61" t="s">
         <v>357</v>
-      </c>
-      <c r="C61" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B62" t="s">
+        <v>358</v>
+      </c>
+      <c r="C62" t="s">
         <v>359</v>
-      </c>
-      <c r="C62" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B63" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C63" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B64" t="s">
+        <v>361</v>
+      </c>
+      <c r="C64" t="s">
         <v>362</v>
-      </c>
-      <c r="C64" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B65" t="s">
+        <v>363</v>
+      </c>
+      <c r="C65" t="s">
         <v>364</v>
-      </c>
-      <c r="C65" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -3046,13 +3040,13 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B67" t="s">
         <v>148</v>
       </c>
       <c r="C67" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -3063,7 +3057,7 @@
         <v>148</v>
       </c>
       <c r="C68" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -3074,7 +3068,7 @@
         <v>148</v>
       </c>
       <c r="C69" t="s">
-        <v>149</v>
+        <v>306</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3085,337 +3079,337 @@
         <v>148</v>
       </c>
       <c r="C70" t="s">
-        <v>307</v>
+        <v>562</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>144</v>
+        <v>220</v>
       </c>
       <c r="B71" t="s">
-        <v>148</v>
+        <v>213</v>
       </c>
       <c r="C71" t="s">
-        <v>366</v>
+        <v>217</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>144</v>
+        <v>220</v>
       </c>
       <c r="B72" t="s">
-        <v>148</v>
+        <v>213</v>
       </c>
       <c r="C72" t="s">
-        <v>367</v>
+        <v>218</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B73" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C73" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C74" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B75" t="s">
+        <v>213</v>
+      </c>
+      <c r="C75" t="s">
         <v>214</v>
-      </c>
-      <c r="C75" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>221</v>
+        <v>144</v>
       </c>
       <c r="B76" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C76" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>221</v>
+        <v>144</v>
       </c>
       <c r="B77" t="s">
-        <v>214</v>
+        <v>150</v>
       </c>
       <c r="C77" t="s">
-        <v>215</v>
+        <v>151</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>144</v>
+        <v>526</v>
       </c>
       <c r="B78" t="s">
-        <v>214</v>
+        <v>365</v>
       </c>
       <c r="C78" t="s">
-        <v>216</v>
+        <v>366</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="B79" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="C79" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>529</v>
+        <v>188</v>
       </c>
       <c r="B80" t="s">
-        <v>368</v>
+        <v>195</v>
       </c>
       <c r="C80" t="s">
-        <v>369</v>
+        <v>196</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B81" t="s">
-        <v>191</v>
+        <v>271</v>
       </c>
       <c r="C81" t="s">
-        <v>192</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="B82" t="s">
-        <v>196</v>
+        <v>276</v>
       </c>
       <c r="C82" t="s">
-        <v>197</v>
+        <v>277</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="B83" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C83" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B84" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C84" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>259</v>
+        <v>527</v>
       </c>
       <c r="B85" t="s">
-        <v>274</v>
+        <v>367</v>
       </c>
       <c r="C85" t="s">
-        <v>275</v>
+        <v>368</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="B86" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C86" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>530</v>
+        <v>188</v>
       </c>
       <c r="B87" t="s">
-        <v>370</v>
+        <v>268</v>
       </c>
       <c r="C87" t="s">
-        <v>371</v>
+        <v>269</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B88" t="s">
-        <v>269</v>
+        <v>193</v>
       </c>
       <c r="C88" t="s">
-        <v>271</v>
+        <v>194</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="B89" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C89" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B90" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C90" t="s">
-        <v>195</v>
+        <v>255</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B91" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C91" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="B92" t="s">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c r="C92" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>188</v>
+      </c>
+      <c r="B93" t="s">
         <v>259</v>
       </c>
-      <c r="B93" t="s">
-        <v>263</v>
-      </c>
       <c r="C93" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>188</v>
+      </c>
+      <c r="B94" t="s">
         <v>259</v>
       </c>
-      <c r="B94" t="s">
-        <v>264</v>
-      </c>
       <c r="C94" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="B95" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C95" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="B96" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C96" t="s">
-        <v>261</v>
+        <v>290</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>259</v>
+        <v>188</v>
       </c>
       <c r="B97" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="C97" t="s">
-        <v>257</v>
+        <v>198</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>259</v>
+        <v>527</v>
       </c>
       <c r="B98" t="s">
-        <v>258</v>
+        <v>369</v>
       </c>
       <c r="C98" t="s">
-        <v>291</v>
+        <v>370</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="B99" t="s">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="C99" t="s">
-        <v>199</v>
+        <v>76</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>530</v>
+        <v>71</v>
       </c>
       <c r="B100" t="s">
-        <v>372</v>
+        <v>72</v>
       </c>
       <c r="C100" t="s">
-        <v>373</v>
+        <v>74</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3423,502 +3417,502 @@
         <v>71</v>
       </c>
       <c r="B101" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C101" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="B102" t="s">
         <v>72</v>
       </c>
       <c r="C102" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>71</v>
+        <v>253</v>
       </c>
       <c r="B103" t="s">
-        <v>72</v>
+        <v>251</v>
       </c>
       <c r="C103" t="s">
-        <v>73</v>
+        <v>252</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B104" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="C104" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>254</v>
+        <v>71</v>
       </c>
       <c r="B105" t="s">
-        <v>252</v>
+        <v>371</v>
       </c>
       <c r="C105" t="s">
-        <v>253</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
       <c r="B106" t="s">
-        <v>155</v>
+        <v>371</v>
       </c>
       <c r="C106" t="s">
-        <v>156</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="B107" t="s">
-        <v>374</v>
+        <v>248</v>
       </c>
       <c r="C107" t="s">
-        <v>375</v>
+        <v>249</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="B108" t="s">
-        <v>374</v>
+        <v>156</v>
       </c>
       <c r="C108" t="s">
-        <v>376</v>
+        <v>157</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B109" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C109" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>153</v>
+        <v>242</v>
       </c>
       <c r="B110" t="s">
-        <v>157</v>
+        <v>244</v>
       </c>
       <c r="C110" t="s">
-        <v>158</v>
+        <v>245</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>242</v>
+      </c>
+      <c r="B111" t="s">
+        <v>137</v>
+      </c>
+      <c r="C111" t="s">
         <v>243</v>
-      </c>
-      <c r="B111" t="s">
-        <v>247</v>
-      </c>
-      <c r="C111" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>243</v>
+        <v>152</v>
       </c>
       <c r="B112" t="s">
-        <v>245</v>
+        <v>137</v>
       </c>
       <c r="C112" t="s">
-        <v>246</v>
+        <v>374</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B113" t="s">
-        <v>137</v>
+        <v>241</v>
       </c>
       <c r="C113" t="s">
-        <v>244</v>
+        <v>289</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>153</v>
+        <v>528</v>
       </c>
       <c r="B114" t="s">
-        <v>137</v>
+        <v>375</v>
       </c>
       <c r="C114" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>243</v>
+        <v>529</v>
       </c>
       <c r="B115" t="s">
-        <v>242</v>
+        <v>377</v>
       </c>
       <c r="C115" t="s">
-        <v>290</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>531</v>
+        <v>182</v>
       </c>
       <c r="B116" t="s">
-        <v>378</v>
+        <v>318</v>
       </c>
       <c r="C116" t="s">
-        <v>379</v>
+        <v>319</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>532</v>
+        <v>182</v>
       </c>
       <c r="B117" t="s">
-        <v>380</v>
+        <v>239</v>
       </c>
       <c r="C117" t="s">
-        <v>381</v>
+        <v>240</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>182</v>
+      </c>
+      <c r="B118" t="s">
         <v>183</v>
       </c>
-      <c r="B118" t="s">
-        <v>319</v>
-      </c>
       <c r="C118" t="s">
-        <v>320</v>
+        <v>185</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>182</v>
+      </c>
+      <c r="B119" t="s">
         <v>183</v>
       </c>
-      <c r="B119" t="s">
-        <v>240</v>
-      </c>
       <c r="C119" t="s">
-        <v>241</v>
+        <v>184</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B120" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C120" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B121" t="s">
-        <v>184</v>
+        <v>237</v>
       </c>
       <c r="C121" t="s">
-        <v>185</v>
+        <v>238</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>183</v>
+        <v>530</v>
       </c>
       <c r="B122" t="s">
-        <v>187</v>
+        <v>379</v>
       </c>
       <c r="C122" t="s">
-        <v>188</v>
+        <v>380</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="B123" t="s">
-        <v>238</v>
+        <v>161</v>
       </c>
       <c r="C123" t="s">
-        <v>239</v>
+        <v>320</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>533</v>
+        <v>152</v>
       </c>
       <c r="B124" t="s">
-        <v>382</v>
+        <v>161</v>
       </c>
       <c r="C124" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B125" t="s">
-        <v>162</v>
+        <v>382</v>
       </c>
       <c r="C125" t="s">
-        <v>321</v>
+        <v>383</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>153</v>
+        <v>531</v>
       </c>
       <c r="B126" t="s">
-        <v>162</v>
+        <v>384</v>
       </c>
       <c r="C126" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B127" t="s">
-        <v>385</v>
+        <v>158</v>
       </c>
       <c r="C127" t="s">
-        <v>386</v>
+        <v>321</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>534</v>
+        <v>152</v>
       </c>
       <c r="B128" t="s">
-        <v>387</v>
+        <v>158</v>
       </c>
       <c r="C128" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>153</v>
+        <v>532</v>
       </c>
       <c r="B129" t="s">
-        <v>159</v>
+        <v>387</v>
       </c>
       <c r="C129" t="s">
-        <v>322</v>
+        <v>388</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>153</v>
+        <v>532</v>
       </c>
       <c r="B130" t="s">
-        <v>159</v>
+        <v>389</v>
       </c>
       <c r="C130" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B131" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C131" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B132" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C132" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B133" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C135" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>536</v>
+        <v>152</v>
       </c>
       <c r="B136" t="s">
-        <v>400</v>
+        <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>401</v>
+        <v>160</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>536</v>
+        <v>152</v>
       </c>
       <c r="B137" t="s">
+        <v>401</v>
+      </c>
+      <c r="C137" t="s">
         <v>402</v>
-      </c>
-      <c r="C137" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B138" t="s">
-        <v>160</v>
+        <v>403</v>
       </c>
       <c r="C138" t="s">
-        <v>161</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>153</v>
+        <v>516</v>
       </c>
       <c r="B139" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C139" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>153</v>
+        <v>556</v>
       </c>
       <c r="B140" t="s">
-        <v>406</v>
+        <v>505</v>
       </c>
       <c r="C140" t="s">
-        <v>407</v>
+        <v>506</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="B141" t="s">
+        <v>407</v>
+      </c>
+      <c r="C141" t="s">
         <v>408</v>
-      </c>
-      <c r="C141" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>559</v>
+        <v>535</v>
       </c>
       <c r="B142" t="s">
-        <v>508</v>
+        <v>409</v>
       </c>
       <c r="C142" t="s">
-        <v>509</v>
+        <v>410</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B143" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C143" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B144" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C144" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B145" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C145" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B146" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C146" t="s">
         <v>417</v>
@@ -3926,7 +3920,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>538</v>
+        <v>38</v>
       </c>
       <c r="B147" t="s">
         <v>418</v>
@@ -3937,35 +3931,35 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>538</v>
+        <v>38</v>
       </c>
       <c r="B148" t="s">
-        <v>418</v>
+        <v>39</v>
       </c>
       <c r="C148" t="s">
-        <v>420</v>
+        <v>40</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B149" t="s">
-        <v>421</v>
+        <v>60</v>
       </c>
       <c r="C149" t="s">
-        <v>422</v>
+        <v>61</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="B150" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C150" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3973,10 +3967,10 @@
         <v>59</v>
       </c>
       <c r="B151" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C151" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3987,7 +3981,7 @@
         <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3998,7 +3992,7 @@
         <v>62</v>
       </c>
       <c r="C153" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4009,7 +4003,7 @@
         <v>62</v>
       </c>
       <c r="C154" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4020,7 +4014,7 @@
         <v>62</v>
       </c>
       <c r="C155" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4031,106 +4025,106 @@
         <v>62</v>
       </c>
       <c r="C156" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>59</v>
+        <v>536</v>
       </c>
       <c r="B157" t="s">
-        <v>62</v>
+        <v>420</v>
       </c>
       <c r="C157" t="s">
-        <v>64</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>59</v>
+        <v>537</v>
       </c>
       <c r="B158" t="s">
-        <v>62</v>
+        <v>422</v>
       </c>
       <c r="C158" t="s">
-        <v>63</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B159" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C159" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B160" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C160" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B161" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C161" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B162" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C162" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B163" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C163" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>543</v>
+        <v>3</v>
       </c>
       <c r="B164" t="s">
-        <v>433</v>
+        <v>5</v>
       </c>
       <c r="C164" t="s">
-        <v>434</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>543</v>
+        <v>3</v>
       </c>
       <c r="B165" t="s">
-        <v>435</v>
+        <v>5</v>
       </c>
       <c r="C165" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4138,10 +4132,10 @@
         <v>3</v>
       </c>
       <c r="B166" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C166" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4149,10 +4143,10 @@
         <v>3</v>
       </c>
       <c r="B167" t="s">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="C167" t="s">
-        <v>437</v>
+        <v>208</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4160,10 +4154,10 @@
         <v>3</v>
       </c>
       <c r="B168" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4171,10 +4165,10 @@
         <v>3</v>
       </c>
       <c r="B169" t="s">
-        <v>208</v>
+        <v>9</v>
       </c>
       <c r="C169" t="s">
-        <v>209</v>
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4182,10 +4176,10 @@
         <v>3</v>
       </c>
       <c r="B170" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4193,10 +4187,10 @@
         <v>3</v>
       </c>
       <c r="B171" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C171" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4204,10 +4198,10 @@
         <v>3</v>
       </c>
       <c r="B172" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4215,10 +4209,10 @@
         <v>3</v>
       </c>
       <c r="B173" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C173" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4226,10 +4220,10 @@
         <v>3</v>
       </c>
       <c r="B174" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C174" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4237,10 +4231,10 @@
         <v>3</v>
       </c>
       <c r="B175" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C175" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4248,10 +4242,10 @@
         <v>3</v>
       </c>
       <c r="B176" t="s">
-        <v>16</v>
+        <v>298</v>
       </c>
       <c r="C176" t="s">
-        <v>17</v>
+        <v>299</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4259,54 +4253,54 @@
         <v>3</v>
       </c>
       <c r="B177" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C177" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="B178" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C178" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>3</v>
+        <v>303</v>
       </c>
       <c r="B179" t="s">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="C179" t="s">
-        <v>21</v>
+        <v>305</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>301</v>
+        <v>42</v>
       </c>
       <c r="B180" t="s">
-        <v>302</v>
+        <v>48</v>
       </c>
       <c r="C180" t="s">
-        <v>303</v>
+        <v>49</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>304</v>
+        <v>42</v>
       </c>
       <c r="B181" t="s">
-        <v>305</v>
+        <v>43</v>
       </c>
       <c r="C181" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -4314,10 +4308,10 @@
         <v>42</v>
       </c>
       <c r="B182" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C182" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4325,10 +4319,10 @@
         <v>42</v>
       </c>
       <c r="B183" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C183" t="s">
-        <v>318</v>
+        <v>47</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4336,87 +4330,87 @@
         <v>42</v>
       </c>
       <c r="B184" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C184" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>42</v>
+        <v>541</v>
       </c>
       <c r="B185" t="s">
-        <v>45</v>
+        <v>435</v>
       </c>
       <c r="C185" t="s">
-        <v>47</v>
+        <v>436</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>42</v>
+        <v>542</v>
       </c>
       <c r="B186" t="s">
-        <v>45</v>
+        <v>437</v>
       </c>
       <c r="C186" t="s">
-        <v>46</v>
+        <v>438</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B187" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C187" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B188" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C188" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B189" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C189" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>547</v>
+        <v>91</v>
       </c>
       <c r="B190" t="s">
-        <v>444</v>
+        <v>93</v>
       </c>
       <c r="C190" t="s">
-        <v>445</v>
+        <v>94</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>548</v>
+        <v>91</v>
       </c>
       <c r="B191" t="s">
-        <v>446</v>
+        <v>95</v>
       </c>
       <c r="C191" t="s">
-        <v>447</v>
+        <v>96</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4424,10 +4418,10 @@
         <v>91</v>
       </c>
       <c r="B192" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C192" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4435,10 +4429,10 @@
         <v>91</v>
       </c>
       <c r="B193" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C193" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4446,10 +4440,10 @@
         <v>91</v>
       </c>
       <c r="B194" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C194" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4457,10 +4451,10 @@
         <v>91</v>
       </c>
       <c r="B195" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C195" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4468,10 +4462,10 @@
         <v>91</v>
       </c>
       <c r="B196" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C196" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4479,10 +4473,10 @@
         <v>91</v>
       </c>
       <c r="B197" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C197" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4490,10 +4484,10 @@
         <v>91</v>
       </c>
       <c r="B198" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C198" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4501,10 +4495,10 @@
         <v>91</v>
       </c>
       <c r="B199" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C199" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4512,10 +4506,10 @@
         <v>91</v>
       </c>
       <c r="B200" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C200" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4523,10 +4517,10 @@
         <v>91</v>
       </c>
       <c r="B201" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C201" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4534,10 +4528,10 @@
         <v>91</v>
       </c>
       <c r="B202" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C202" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4545,10 +4539,10 @@
         <v>91</v>
       </c>
       <c r="B203" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C203" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4556,10 +4550,10 @@
         <v>91</v>
       </c>
       <c r="B204" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C204" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4567,10 +4561,10 @@
         <v>91</v>
       </c>
       <c r="B205" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C205" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4578,10 +4572,10 @@
         <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C206" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4589,10 +4583,10 @@
         <v>91</v>
       </c>
       <c r="B207" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C207" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4600,10 +4594,10 @@
         <v>91</v>
       </c>
       <c r="B208" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C208" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4611,10 +4605,10 @@
         <v>91</v>
       </c>
       <c r="B209" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C209" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4622,10 +4616,10 @@
         <v>91</v>
       </c>
       <c r="B210" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C210" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4633,10 +4627,10 @@
         <v>91</v>
       </c>
       <c r="B211" t="s">
-        <v>114</v>
+        <v>233</v>
       </c>
       <c r="C211" t="s">
-        <v>114</v>
+        <v>234</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4644,10 +4638,10 @@
         <v>91</v>
       </c>
       <c r="B212" t="s">
-        <v>115</v>
+        <v>445</v>
       </c>
       <c r="C212" t="s">
-        <v>115</v>
+        <v>446</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4655,10 +4649,10 @@
         <v>91</v>
       </c>
       <c r="B213" t="s">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="C213" t="s">
-        <v>235</v>
+        <v>118</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4666,277 +4660,277 @@
         <v>91</v>
       </c>
       <c r="B214" t="s">
-        <v>448</v>
+        <v>116</v>
       </c>
       <c r="C214" t="s">
-        <v>449</v>
+        <v>117</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>91</v>
+        <v>546</v>
       </c>
       <c r="B215" t="s">
-        <v>116</v>
+        <v>447</v>
       </c>
       <c r="C215" t="s">
-        <v>118</v>
+        <v>448</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>91</v>
+        <v>547</v>
       </c>
       <c r="B216" t="s">
-        <v>116</v>
+        <v>449</v>
       </c>
       <c r="C216" t="s">
-        <v>117</v>
+        <v>450</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B217" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C217" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B218" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C218" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B219" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C219" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B220" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C220" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B221" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C221" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B222" t="s">
-        <v>460</v>
+        <v>509</v>
       </c>
       <c r="C222" t="s">
-        <v>461</v>
+        <v>510</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>550</v>
+        <v>176</v>
       </c>
       <c r="B223" t="s">
-        <v>462</v>
+        <v>178</v>
       </c>
       <c r="C223" t="s">
-        <v>463</v>
+        <v>180</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>561</v>
+        <v>176</v>
       </c>
       <c r="B224" t="s">
-        <v>512</v>
+        <v>178</v>
       </c>
       <c r="C224" t="s">
-        <v>513</v>
+        <v>229</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B225" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C225" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B226" t="s">
+        <v>178</v>
+      </c>
+      <c r="C226" t="s">
         <v>179</v>
-      </c>
-      <c r="C226" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B227" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C227" t="s">
-        <v>229</v>
+        <v>181</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B228" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C228" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B229" t="s">
-        <v>179</v>
+        <v>232</v>
       </c>
       <c r="C229" t="s">
-        <v>182</v>
+        <v>231</v>
+      </c>
+      <c r="G229" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
       <c r="B230" t="s">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="C230" t="s">
-        <v>231</v>
+        <v>324</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>177</v>
+        <v>322</v>
       </c>
       <c r="B231" t="s">
-        <v>233</v>
+        <v>325</v>
       </c>
       <c r="C231" t="s">
-        <v>232</v>
-      </c>
-      <c r="G231" t="s">
-        <v>207</v>
+        <v>326</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>323</v>
+        <v>173</v>
       </c>
       <c r="B232" t="s">
-        <v>324</v>
+        <v>174</v>
       </c>
       <c r="C232" t="s">
-        <v>325</v>
+        <v>175</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>323</v>
+        <v>173</v>
       </c>
       <c r="B233" t="s">
-        <v>326</v>
+        <v>209</v>
       </c>
       <c r="C233" t="s">
-        <v>327</v>
+        <v>210</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B234" t="s">
-        <v>175</v>
+        <v>285</v>
       </c>
       <c r="C234" t="s">
-        <v>176</v>
+        <v>286</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B235" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="C235" t="s">
-        <v>211</v>
+        <v>315</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B236" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C236" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="B237" t="s">
-        <v>317</v>
+        <v>142</v>
       </c>
       <c r="C237" t="s">
-        <v>316</v>
+        <v>143</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="B238" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C238" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -4944,10 +4938,10 @@
         <v>141</v>
       </c>
       <c r="B239" t="s">
-        <v>142</v>
+        <v>281</v>
       </c>
       <c r="C239" t="s">
-        <v>143</v>
+        <v>284</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -4963,24 +4957,24 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="B241" t="s">
-        <v>282</v>
+        <v>27</v>
       </c>
       <c r="C241" t="s">
-        <v>285</v>
+        <v>28</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="B242" t="s">
-        <v>282</v>
+        <v>29</v>
       </c>
       <c r="C242" t="s">
-        <v>284</v>
+        <v>30</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4988,10 +4982,10 @@
         <v>26</v>
       </c>
       <c r="B243" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C243" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -4999,10 +4993,10 @@
         <v>26</v>
       </c>
       <c r="B244" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C244" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -5010,10 +5004,10 @@
         <v>26</v>
       </c>
       <c r="B245" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C245" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -5024,7 +5018,7 @@
         <v>33</v>
       </c>
       <c r="C246" t="s">
-        <v>34</v>
+        <v>461</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -5032,54 +5026,54 @@
         <v>26</v>
       </c>
       <c r="B247" t="s">
-        <v>33</v>
+        <v>313</v>
       </c>
       <c r="C247" t="s">
-        <v>35</v>
+        <v>314</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B248" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C248" t="s">
-        <v>464</v>
+        <v>54</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B249" t="s">
-        <v>314</v>
+        <v>53</v>
       </c>
       <c r="C249" t="s">
-        <v>315</v>
+        <v>55</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B250" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C250" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B251" t="s">
-        <v>53</v>
+        <v>462</v>
       </c>
       <c r="C251" t="s">
-        <v>55</v>
+        <v>463</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -5087,10 +5081,10 @@
         <v>56</v>
       </c>
       <c r="B252" t="s">
-        <v>57</v>
+        <v>310</v>
       </c>
       <c r="C252" t="s">
-        <v>58</v>
+        <v>311</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -5098,213 +5092,213 @@
         <v>56</v>
       </c>
       <c r="B253" t="s">
-        <v>465</v>
+        <v>310</v>
       </c>
       <c r="C253" t="s">
-        <v>466</v>
+        <v>312</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>56</v>
+        <v>307</v>
       </c>
       <c r="B254" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C254" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="B255" t="s">
-        <v>311</v>
+        <v>226</v>
       </c>
       <c r="C255" t="s">
-        <v>313</v>
+        <v>227</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>308</v>
+        <v>26</v>
       </c>
       <c r="B256" t="s">
-        <v>309</v>
+        <v>36</v>
       </c>
       <c r="C256" t="s">
-        <v>310</v>
+        <v>37</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>26</v>
+        <v>548</v>
       </c>
       <c r="B257" t="s">
-        <v>227</v>
+        <v>464</v>
       </c>
       <c r="C257" t="s">
-        <v>228</v>
+        <v>465</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>26</v>
+        <v>548</v>
       </c>
       <c r="B258" t="s">
-        <v>36</v>
+        <v>466</v>
       </c>
       <c r="C258" t="s">
-        <v>37</v>
+        <v>467</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B259" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C259" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B260" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C260" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B261" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C261" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B262" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C262" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B263" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C263" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B264" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C264" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B265" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C265" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>552</v>
+        <v>224</v>
       </c>
       <c r="B266" t="s">
-        <v>481</v>
+        <v>221</v>
       </c>
       <c r="C266" t="s">
-        <v>482</v>
+        <v>222</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>552</v>
+        <v>224</v>
       </c>
       <c r="B267" t="s">
-        <v>483</v>
+        <v>221</v>
       </c>
       <c r="C267" t="s">
-        <v>484</v>
+        <v>223</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>138</v>
+      </c>
+      <c r="B268" t="s">
+        <v>139</v>
+      </c>
+      <c r="C268" t="s">
         <v>225</v>
-      </c>
-      <c r="B268" t="s">
-        <v>222</v>
-      </c>
-      <c r="C268" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>225</v>
+        <v>138</v>
       </c>
       <c r="B269" t="s">
-        <v>222</v>
+        <v>139</v>
       </c>
       <c r="C269" t="s">
-        <v>224</v>
+        <v>140</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>138</v>
+        <v>550</v>
       </c>
       <c r="B270" t="s">
-        <v>139</v>
+        <v>482</v>
       </c>
       <c r="C270" t="s">
-        <v>226</v>
+        <v>483</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>138</v>
+        <v>550</v>
       </c>
       <c r="B271" t="s">
-        <v>139</v>
+        <v>482</v>
       </c>
       <c r="C271" t="s">
-        <v>140</v>
+        <v>484</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B272" t="s">
         <v>485</v>
@@ -5315,131 +5309,131 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B273" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C273" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B274" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C274" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>554</v>
+        <v>38</v>
       </c>
       <c r="B275" t="s">
-        <v>490</v>
+        <v>41</v>
       </c>
       <c r="C275" t="s">
-        <v>491</v>
+        <v>41</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>555</v>
+        <v>59</v>
       </c>
       <c r="B276" t="s">
-        <v>492</v>
+        <v>70</v>
       </c>
       <c r="C276" t="s">
-        <v>493</v>
+        <v>70</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="B277" t="s">
-        <v>41</v>
+        <v>144</v>
       </c>
       <c r="C277" t="s">
-        <v>41</v>
+        <v>144</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>59</v>
+        <v>553</v>
       </c>
       <c r="B278" t="s">
-        <v>70</v>
+        <v>491</v>
       </c>
       <c r="C278" t="s">
-        <v>70</v>
+        <v>492</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>144</v>
+        <v>553</v>
       </c>
       <c r="B279" t="s">
-        <v>144</v>
+        <v>493</v>
       </c>
       <c r="C279" t="s">
-        <v>144</v>
+        <v>494</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B280" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C280" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B281" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C281" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B282" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C282" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B283" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C283" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>558</v>
+        <v>503</v>
       </c>
       <c r="B284" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C284" t="s">
         <v>503</v>
@@ -5447,52 +5441,30 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>558</v>
+        <v>504</v>
       </c>
       <c r="B285" t="s">
         <v>504</v>
       </c>
       <c r="C285" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>506</v>
+        <v>561</v>
       </c>
       <c r="B286" t="s">
-        <v>506</v>
+        <v>559</v>
       </c>
       <c r="C286" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287" t="s">
-        <v>507</v>
-      </c>
-      <c r="B287" t="s">
-        <v>507</v>
-      </c>
-      <c r="C287" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
-        <v>564</v>
-      </c>
-      <c r="B288" t="s">
-        <v>562</v>
-      </c>
-      <c r="C288" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:X288" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:X286" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C179:C1048576 C151:C177 C1:C149">
+  <conditionalFormatting sqref="C177:C1048576 C149:C175 C1:C147">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/预测分析.xlsx
+++ b/预测分析.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forecast\预测分析\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511289BA-245C-4EAF-91E5-C6C454F3391C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEEA6CD-22B1-4AC8-BFB0-C34F165F1055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="864" yWindow="804" windowWidth="17280" windowHeight="10044" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="576">
   <si>
     <t>晶圆</t>
   </si>
@@ -1831,13 +1831,65 @@
   </si>
   <si>
     <t>SC2402SO-N-CJ-90NR-6571</t>
+  </si>
+  <si>
+    <t>SC1002N2W-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1002N2W-CL-00AK-N41F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1919UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1919UA-CD-90AK-919H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4001UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM.SC4001UA-CB-90AK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYLM358DC-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYLM358DC-GC-90AR-LM358</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYLM358DC-GC-90AR-NM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC1002AL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9913D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC4001AB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9G005C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1851,6 +1903,20 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1879,7 +1945,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1887,18 +1953,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2 4 2 2" xfId="1" xr:uid="{9C7ED766-84C1-4343-B919-15B8593B06F8}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2187,7 +2285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X286"/>
+  <dimension ref="A1:X291"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
@@ -2260,77 +2358,77 @@
         <v>204</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="5">
         <v>7</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="6">
         <v>7</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="7">
         <v>7</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="5">
         <v>8</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="6">
         <v>8</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="7">
         <v>8</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="5">
         <v>9</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="6">
         <v>9</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="7">
         <v>9</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="5">
         <v>10</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="6">
         <v>10</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="7">
         <v>10</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="5">
         <v>11</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="6">
         <v>11</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="7">
         <v>11</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="6">
         <v>12</v>
       </c>
-      <c r="T2" s="3">
+      <c r="T2" s="5">
         <v>12</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U2" s="7">
         <v>12</v>
       </c>
-      <c r="V2" s="3">
+      <c r="V2" s="5">
         <v>1</v>
       </c>
-      <c r="W2" s="1">
+      <c r="W2" s="6">
         <v>1</v>
       </c>
-      <c r="X2" s="2">
+      <c r="X2" s="7">
         <v>1</v>
       </c>
     </row>
@@ -5459,6 +5557,61 @@
       </c>
       <c r="C286" t="s">
         <v>560</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>572</v>
+      </c>
+      <c r="B287" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="C287" s="8" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>573</v>
+      </c>
+      <c r="B288" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="C288" s="8" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>574</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="C289" s="8" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>575</v>
+      </c>
+      <c r="B290" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="C290" s="8" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>575</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="C291" s="8" t="s">
+        <v>571</v>
       </c>
     </row>
   </sheetData>

--- a/预测分析.xlsx
+++ b/预测分析.xlsx
@@ -1,43 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forecast\预测分析\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEEA6CD-22B1-4AC8-BFB0-C34F165F1055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE35E5B-AFC9-4B5C-86D6-1A32F9A184B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="864" yWindow="804" windowWidth="17280" windowHeight="10044" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$X$286</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$C$2</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="455">
   <si>
     <t>晶圆</t>
   </si>
@@ -51,21 +42,66 @@
     <t>STC9D03E</t>
   </si>
   <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>2100-A-2100</t>
+  </si>
+  <si>
+    <t>2100HBL</t>
+  </si>
+  <si>
+    <t>NR.2100HBL-2100</t>
+  </si>
+  <si>
+    <t>2100S</t>
+  </si>
+  <si>
+    <t>2100S-2100</t>
+  </si>
+  <si>
+    <t>PSTC9D03E</t>
+  </si>
+  <si>
     <t>PSTC9D03E-4</t>
   </si>
   <si>
+    <t>SC4643SA-A</t>
+  </si>
+  <si>
+    <t>SC4643SA-A-4643</t>
+  </si>
+  <si>
     <t>SC4643SA-BK-Q</t>
   </si>
   <si>
     <t>SC4643SA-Q-DE-40HK-2100</t>
   </si>
   <si>
+    <t>SC4643VB</t>
+  </si>
+  <si>
+    <t>NR.SC4643VB-A-4643</t>
+  </si>
+  <si>
+    <t>SC4643VB-A-4643</t>
+  </si>
+  <si>
     <t>SC4643VB-2.5S</t>
   </si>
   <si>
     <t>SC4643VB-A-4643-2.5S</t>
   </si>
   <si>
+    <t>SC4643VB-A</t>
+  </si>
+  <si>
+    <t>NR.SC4643VB-A-FFH-L43</t>
+  </si>
+  <si>
+    <t>SC4643VB-A-FFH-L43</t>
+  </si>
+  <si>
     <t>SC4643VB-BK-Q</t>
   </si>
   <si>
@@ -75,12 +111,27 @@
     <t>SC4643VB-Q-DE-40CK-4643</t>
   </si>
   <si>
+    <t>SC4643VB-G</t>
+  </si>
+  <si>
+    <t>SC4643VB-G(STC9D03E)-4643</t>
+  </si>
+  <si>
     <t>SC4643VB-G-BK-Q</t>
   </si>
   <si>
     <t>SC4643VB-G-Q-DE-40CK-4643</t>
   </si>
   <si>
+    <t>SC4643VB-P</t>
+  </si>
+  <si>
+    <t>NR.SC4643VB-P(STC9D03E)-4643</t>
+  </si>
+  <si>
+    <t>SC4643VB-P(STC9D03E)-4643</t>
+  </si>
+  <si>
     <t>SC4643VB-P-2.5S</t>
   </si>
   <si>
@@ -93,6 +144,12 @@
     <t>SC4643VB-P-Q-DE-40CR-4643</t>
   </si>
   <si>
+    <t>SC4643VB-S</t>
+  </si>
+  <si>
+    <t>SC4643VB-S(STC9D03E)-4643</t>
+  </si>
+  <si>
     <t>SC4643VB-S-BK-Q</t>
   </si>
   <si>
@@ -120,12 +177,36 @@
     <t>STC9A001I</t>
   </si>
   <si>
+    <t>PSTC9A001I-1</t>
+  </si>
+  <si>
+    <t>SC9641TS-P</t>
+  </si>
+  <si>
+    <t>NR.SC9641TS-P-I(STC9A001I)-41CPA</t>
+  </si>
+  <si>
+    <t>SC9641TS-P-I(STC9A001I)-41CPA</t>
+  </si>
+  <si>
+    <t>SC9641TS-P-I（STC9A001I)-41CPA</t>
+  </si>
+  <si>
     <t>SC9641TS-P-BK</t>
   </si>
   <si>
     <t>SC9641TS-P-AI-10AK-41CPA</t>
   </si>
   <si>
+    <t>SC9641TS-PC</t>
+  </si>
+  <si>
+    <t>NR.SC9641TS-PC(STC9A001I)-41CPA</t>
+  </si>
+  <si>
+    <t>SC9641TS-PC(STC9A001I)-41CPA</t>
+  </si>
+  <si>
     <t>SC9641TS-PC-BK-Q</t>
   </si>
   <si>
@@ -138,15 +219,39 @@
     <t>SC9641TS-PC-Q-AI-10LR-9641PC</t>
   </si>
   <si>
+    <t>SC9641TS-PC-Q-AI-10AR-9641PC</t>
+  </si>
+  <si>
     <t>SC9641TS-P-TR</t>
   </si>
   <si>
     <t>SC9641TS-P-AI-10AR-G1630</t>
   </si>
   <si>
+    <t>SC9641TS-P-AI-10LR-41CPA</t>
+  </si>
+  <si>
     <t>SC9641TS-P-AI-10AR-41CPA</t>
   </si>
   <si>
+    <t>SC9648TS-P</t>
+  </si>
+  <si>
+    <t>NR.SC9648TS-P(STC9A001I)-41CPA</t>
+  </si>
+  <si>
+    <t>SC9648TS-P(STC9A001I)-41CPA</t>
+  </si>
+  <si>
+    <t>SC9648TS-P(STC9A001I)-9648</t>
+  </si>
+  <si>
+    <t>SC9648TS-P-9A001I(STC9A001I)-41CPA</t>
+  </si>
+  <si>
+    <t>SC9648TS-P-9A001I(STC9A001I)-9648</t>
+  </si>
+  <si>
     <t>SC9648TS-TR</t>
   </si>
   <si>
@@ -168,12 +273,48 @@
     <t>STC9D01C</t>
   </si>
   <si>
+    <t>SC4688DA</t>
+  </si>
+  <si>
+    <t>SC4688DA(STC9D01C)-4688D</t>
+  </si>
+  <si>
+    <t>SC4688DC</t>
+  </si>
+  <si>
+    <t>SC4688DC-4688</t>
+  </si>
+  <si>
     <t>SC4688DC-TR-Q</t>
   </si>
   <si>
+    <t>SC4688DC-Q-DC-40AR-4688</t>
+  </si>
+  <si>
+    <t>SC4688DC-Q-DC-40CR-6388</t>
+  </si>
+  <si>
     <t>SC4688DC-Q-DC-40CR-4688</t>
   </si>
   <si>
+    <t>SC4688DC-DU-Q-DC-40AR-2425</t>
+  </si>
+  <si>
+    <t>SC4688SA</t>
+  </si>
+  <si>
+    <t>NP.SC4688SA-4688</t>
+  </si>
+  <si>
+    <t>NP.SC4688SA-888K</t>
+  </si>
+  <si>
+    <t>SC4688SA-A</t>
+  </si>
+  <si>
+    <t>SC4688SA-A(STC9D01C)-4688</t>
+  </si>
+  <si>
     <t>SC4688SA-BK-Q</t>
   </si>
   <si>
@@ -183,21 +324,87 @@
     <t>SC4688SA-Q-DC-40CK-888K</t>
   </si>
   <si>
+    <t>SC4695DC</t>
+  </si>
+  <si>
+    <t>SC4695DC-2425</t>
+  </si>
+  <si>
     <t>SC4688DC-TR</t>
   </si>
   <si>
     <t>SC4688DC-DC-40AR-2425</t>
   </si>
   <si>
+    <t>STC2899AE</t>
+  </si>
+  <si>
+    <t>SC1645A1</t>
+  </si>
+  <si>
+    <t>SC1645A1-1466</t>
+  </si>
+  <si>
+    <t>SC1645A1-4601H</t>
+  </si>
+  <si>
+    <t>SC1645A1-61H</t>
+  </si>
+  <si>
+    <t>SC1645A1-65HA</t>
+  </si>
+  <si>
     <t>SC1645A1-BK</t>
   </si>
   <si>
+    <t>SC1645A1-AE-00HK-4601H</t>
+  </si>
+  <si>
+    <t>SC1645A1-AE-00HK-65HA</t>
+  </si>
+  <si>
+    <t>SC1645A1-AE-00HK-1466</t>
+  </si>
+  <si>
+    <t>SC1645A1R12</t>
+  </si>
+  <si>
+    <t>SC1645A1R12-4601H</t>
+  </si>
+  <si>
+    <t>SC1645A2</t>
+  </si>
+  <si>
+    <t>SC1645A2-601HL</t>
+  </si>
+  <si>
+    <t>SC1645B1</t>
+  </si>
+  <si>
+    <t>SC1645B1-4601</t>
+  </si>
+  <si>
+    <t>SC1645B1-615HA</t>
+  </si>
+  <si>
+    <t>SC1645B1-65HA</t>
+  </si>
+  <si>
     <t>SC1645B1-BK</t>
   </si>
   <si>
+    <t>SC1645B1-AE-00HK-615HA</t>
+  </si>
+  <si>
     <t>STC9910BN</t>
   </si>
   <si>
+    <t>SC9641TS</t>
+  </si>
+  <si>
+    <t>SC9641TS-9641</t>
+  </si>
+  <si>
     <t>SC9641TS-TR-Q</t>
   </si>
   <si>
@@ -207,15 +414,45 @@
     <t>SC9641TS-362-Q-CB-10LR-9641</t>
   </si>
   <si>
+    <t>STC9A001G</t>
+  </si>
+  <si>
+    <t>SC9642TS</t>
+  </si>
+  <si>
+    <t>SC9642TS(9A001G)-9642</t>
+  </si>
+  <si>
     <t>STC9A001H</t>
   </si>
   <si>
+    <t>SC9642TS-E</t>
+  </si>
+  <si>
+    <t>SC9642TS(9A001H)-E-9642</t>
+  </si>
+  <si>
+    <t>SC9642TS(STC9A001H)-E-9642</t>
+  </si>
+  <si>
+    <t>SC9642TS(STC9A001H)-E-白板</t>
+  </si>
+  <si>
+    <t>SC9642TS-EC</t>
+  </si>
+  <si>
+    <t>SC9642TS(STC9A001H)-EC-9642</t>
+  </si>
+  <si>
     <t>SC9642TS-EC-TR-Q</t>
   </si>
   <si>
     <t>SC9642TS-EC-Q-AH-4XLR-9642</t>
   </si>
   <si>
+    <t>SC9642TS-EC-Q-AH-4XAR-9642</t>
+  </si>
+  <si>
     <t>STC4011E</t>
   </si>
   <si>
@@ -255,6 +492,21 @@
     <t>STC9906P</t>
   </si>
   <si>
+    <t>SC2442SE</t>
+  </si>
+  <si>
+    <t>SC2442SE-2442</t>
+  </si>
+  <si>
+    <t>SC2442SO-N</t>
+  </si>
+  <si>
+    <t>SC2442SO-N(STC9906P)-2442</t>
+  </si>
+  <si>
+    <t>SC2442SO-N-2442</t>
+  </si>
+  <si>
     <t>SC2442SO-N-TR-Q</t>
   </si>
   <si>
@@ -264,6 +516,21 @@
     <t>SC2442SO-N-Q-CP-10CR-2662</t>
   </si>
   <si>
+    <t>SC2442UA</t>
+  </si>
+  <si>
+    <t>SC2442UA-2442</t>
+  </si>
+  <si>
+    <t>SC2442UA-U18</t>
+  </si>
+  <si>
+    <t>SC2662SO-N</t>
+  </si>
+  <si>
+    <t>SC2662SO-N-2662</t>
+  </si>
+  <si>
     <t>SC2442SO-N-TR</t>
   </si>
   <si>
@@ -285,6 +552,9 @@
     <t>SC1245A1-41F</t>
   </si>
   <si>
+    <t>SC1245A1-61HA</t>
+  </si>
+  <si>
     <t>SC1245B1</t>
   </si>
   <si>
@@ -294,12 +564,36 @@
     <t>SC1245B1-613HA</t>
   </si>
   <si>
+    <t>SC1245SO-N</t>
+  </si>
+  <si>
+    <t>SC1245SO-N-1245</t>
+  </si>
+  <si>
     <t>SC1245SO-N-TR</t>
   </si>
   <si>
     <t>SC1245SO-N-CD-00NR-1245</t>
   </si>
   <si>
+    <t>SC1245UA</t>
+  </si>
+  <si>
+    <t>SC1245A3(STC1898AD)-41F</t>
+  </si>
+  <si>
+    <t>SC1245UA-1245</t>
+  </si>
+  <si>
+    <t>SC1245UA-41F</t>
+  </si>
+  <si>
+    <t>SC41HL-A2</t>
+  </si>
+  <si>
+    <t>SC41HL-A2-41HL</t>
+  </si>
+  <si>
     <t>SC1245A3-BK</t>
   </si>
   <si>
@@ -318,6 +612,15 @@
     <t>PSTC9D04C</t>
   </si>
   <si>
+    <t>SC60220</t>
+  </si>
+  <si>
+    <t>NP.SC60220-60220</t>
+  </si>
+  <si>
+    <t>SC60220-60220</t>
+  </si>
+  <si>
     <t>SC60220SS-TB</t>
   </si>
   <si>
@@ -387,6 +690,30 @@
     <t>SC60224-U-P4-1024</t>
   </si>
   <si>
+    <t>SC60226</t>
+  </si>
+  <si>
+    <t>NA.SC60226</t>
+  </si>
+  <si>
+    <t>NM.SC60226</t>
+  </si>
+  <si>
+    <t>NP.SC60226-60226</t>
+  </si>
+  <si>
+    <t>SC60228DC</t>
+  </si>
+  <si>
+    <t>NR.SC60228DC-60228</t>
+  </si>
+  <si>
+    <t>SC60228DC-60228</t>
+  </si>
+  <si>
+    <t>SC60228DC-白板</t>
+  </si>
+  <si>
     <t>SC60228DC-TR</t>
   </si>
   <si>
@@ -417,9 +744,27 @@
     <t>S41H-A2</t>
   </si>
   <si>
+    <t>S41H-A2-S41H</t>
+  </si>
+  <si>
+    <t>SC1645A1(STC2899AI)-65HA</t>
+  </si>
+  <si>
     <t>SC1645A1-AI-00HK-4601H</t>
   </si>
   <si>
+    <t>SC1645A2(STC2899AI)-601HL</t>
+  </si>
+  <si>
+    <t>SC1645B1(STC2899AI)-4601</t>
+  </si>
+  <si>
+    <t>SC1645B2</t>
+  </si>
+  <si>
+    <t>SC1645B2(STC2899AI)-4601</t>
+  </si>
+  <si>
     <t>SC1645S1-BK</t>
   </si>
   <si>
@@ -450,21 +795,72 @@
     <t>SC1645B1-AI-00HK-4601</t>
   </si>
   <si>
+    <t>STC9906S</t>
+  </si>
+  <si>
+    <t>SC2448SO</t>
+  </si>
+  <si>
+    <t>SC2448SO-2448</t>
+  </si>
+  <si>
+    <t>SC2448UA-N</t>
+  </si>
+  <si>
+    <t>NM.SC2448UA-N</t>
+  </si>
+  <si>
+    <t>SC2448UA-N-2448</t>
+  </si>
+  <si>
     <t>SC2448SO-TR-Q</t>
   </si>
   <si>
+    <t>SC2448SO-Q-CS-10CR-2448</t>
+  </si>
+  <si>
     <t>FD1014A</t>
   </si>
   <si>
+    <t>KH276</t>
+  </si>
+  <si>
+    <t>SD2276(FD1014A)-KH276</t>
+  </si>
+  <si>
+    <t>PFD1014A</t>
+  </si>
+  <si>
+    <t>PFD1014A-0</t>
+  </si>
+  <si>
+    <t>SD2276</t>
+  </si>
+  <si>
+    <t>SD2276(FD1014A)-276</t>
+  </si>
+  <si>
     <t>SD2276VB-BK</t>
   </si>
   <si>
+    <t>SD2276VB-CA-00AK-276</t>
+  </si>
+  <si>
+    <t>SD2276VB-CA-00AK-KH276</t>
+  </si>
+  <si>
     <t>SD2276VB-CA-90AK-276</t>
   </si>
   <si>
     <t>STC9905E</t>
   </si>
   <si>
+    <t>SC9632VB</t>
+  </si>
+  <si>
+    <t>SC9632VB-9632</t>
+  </si>
+  <si>
     <t>SC9632VB-BK</t>
   </si>
   <si>
@@ -480,15 +876,39 @@
     <t>SC2402SO-N</t>
   </si>
   <si>
+    <t>SC2402SO-N-2402</t>
+  </si>
+  <si>
     <t>SC2402SO-N-Ag0.8-2402</t>
   </si>
   <si>
+    <t>SC2402SO-N-C(STC9902J)-2448</t>
+  </si>
+  <si>
     <t>SC2402SO-N-TR</t>
   </si>
   <si>
+    <t>SC2402SO-N-CJ-00NR-2402</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-CJ-0XLR-6571</t>
+  </si>
+  <si>
     <t>SC2402SO-N-CJ-90NR-2402</t>
   </si>
   <si>
+    <t>SC2402UA</t>
+  </si>
+  <si>
+    <t>NM.SC2402UA</t>
+  </si>
+  <si>
+    <t>SC2402UA-2402</t>
+  </si>
+  <si>
+    <t>SC2402UA-U18</t>
+  </si>
+  <si>
     <t>SC2402UA-BK</t>
   </si>
   <si>
@@ -498,6 +918,18 @@
     <t>STC11102B</t>
   </si>
   <si>
+    <t>SC2442SO</t>
+  </si>
+  <si>
+    <t>NM.SC2442SO(2943N1-1)</t>
+  </si>
+  <si>
+    <t>SC2442SO(2943N1-1)-2442</t>
+  </si>
+  <si>
+    <t>SC2442SO-N(2943S1)-2442</t>
+  </si>
+  <si>
     <t>SC2442SO-N-Q-DB-60CR-2442</t>
   </si>
   <si>
@@ -507,15 +939,33 @@
     <t>SC2442SO-Q-DB-60CR-2442</t>
   </si>
   <si>
+    <t>SC2442UA(2943S1-1)-2442</t>
+  </si>
+  <si>
+    <t>SC2442UA(2943S1-1)-U18</t>
+  </si>
+  <si>
     <t>SC2442UA-BK-Q</t>
   </si>
   <si>
     <t>SC2442UA-Q-DB-60AK-2442</t>
   </si>
   <si>
+    <t>SC2448SO(2948N1)-2448</t>
+  </si>
+  <si>
+    <t>SC2448SO(2948N1-1)-2448</t>
+  </si>
+  <si>
     <t>SC2498UA-N-BK-Q</t>
   </si>
   <si>
+    <t>SC2498UA-N-Q-DB-60CK-2498</t>
+  </si>
+  <si>
+    <t>SC2498UA-N-Q-DB-60AK-2498</t>
+  </si>
+  <si>
     <t>SC2943A2-BK</t>
   </si>
   <si>
@@ -525,18 +975,81 @@
     <t>SC2498CUA-N-BK-Q</t>
   </si>
   <si>
+    <t>SC2498CUA-N-Q-DB-60AK-2498C</t>
+  </si>
+  <si>
+    <t>STC9906W</t>
+  </si>
+  <si>
+    <t>SC2443UA</t>
+  </si>
+  <si>
+    <t>SC2443UA-W(STC9906W)-2443</t>
+  </si>
+  <si>
     <t>STC1898AI</t>
   </si>
   <si>
     <t>PSTC1898AI</t>
   </si>
   <si>
+    <t>SC1134B1</t>
+  </si>
+  <si>
+    <t>SC1134B1-43F</t>
+  </si>
+  <si>
+    <t>SC1134BU</t>
+  </si>
+  <si>
+    <t>SC1134BU-1134</t>
+  </si>
+  <si>
+    <t>SC1134S2-BK</t>
+  </si>
+  <si>
+    <t>NM.SC1134S2-CI-00AK</t>
+  </si>
+  <si>
+    <t>SC1134S2-CI-00AK-44E</t>
+  </si>
+  <si>
+    <t>SC1134SO-N</t>
+  </si>
+  <si>
+    <t>SC1134SO-N-1134</t>
+  </si>
+  <si>
     <t>SC1134SO-N-TR-Q</t>
   </si>
   <si>
     <t>SC1134SO-N-Q-CI-00LR-1134</t>
   </si>
   <si>
+    <t>SC1134UA</t>
+  </si>
+  <si>
+    <t>NM.SC1134UA</t>
+  </si>
+  <si>
+    <t>SC1134UA-04E</t>
+  </si>
+  <si>
+    <t>SC1134UA-1134</t>
+  </si>
+  <si>
+    <t>SC1134UA-3144</t>
+  </si>
+  <si>
+    <t>SC1134UA-43F</t>
+  </si>
+  <si>
+    <t>SC1134UA-44E</t>
+  </si>
+  <si>
+    <t>SC1134UA-44L</t>
+  </si>
+  <si>
     <t>SC1134UA-BK</t>
   </si>
   <si>
@@ -555,24 +1068,90 @@
     <t>SC1134BU-TR</t>
   </si>
   <si>
+    <t>SC1134BU-CI-00AR-1134</t>
+  </si>
+  <si>
     <t>SC1134BU-CI-00CR-1134</t>
   </si>
   <si>
+    <t>SC1134S1-BK</t>
+  </si>
+  <si>
+    <t>SC1134S1-CI-00AK-43F</t>
+  </si>
+  <si>
     <t>STC9910E</t>
   </si>
   <si>
+    <t>SC9625VB</t>
+  </si>
+  <si>
+    <t>NM.SC9625VB(STC9910E)</t>
+  </si>
+  <si>
+    <t>NR.SC9625VB(STC9910E)-9625</t>
+  </si>
+  <si>
+    <t>SC9625VB-L</t>
+  </si>
+  <si>
+    <t>NR.SC9625VB-L-9625L</t>
+  </si>
+  <si>
+    <t>SC9625VB-L-9625L</t>
+  </si>
+  <si>
     <t>SC9625VB-BK</t>
   </si>
   <si>
     <t>SC9625VB-CE-00CK-9625L</t>
   </si>
   <si>
+    <t>STC9A001F</t>
+  </si>
+  <si>
+    <t>AS04</t>
+  </si>
+  <si>
+    <t>SC9641TS-P(9A001F)-AS04</t>
+  </si>
+  <si>
+    <t>NR.SC9641TS-P（9A001F)-41CPA</t>
+  </si>
+  <si>
+    <t>SC9641TS-P(9A001F)-41CPA</t>
+  </si>
+  <si>
+    <t>SC9641TS-P（9A001F)-41CPA</t>
+  </si>
+  <si>
     <t>STC9901AF</t>
   </si>
   <si>
     <t>PSTC9901AF</t>
   </si>
   <si>
+    <t>SC9314UA</t>
+  </si>
+  <si>
+    <t>NM.SC9314UA</t>
+  </si>
+  <si>
+    <t>SC9314UA-17CA</t>
+  </si>
+  <si>
+    <t>SC9314UA-2414</t>
+  </si>
+  <si>
+    <t>SC9314UA-9201L</t>
+  </si>
+  <si>
+    <t>SC9314UA-9209</t>
+  </si>
+  <si>
+    <t>SC9314UA-94M</t>
+  </si>
+  <si>
     <t>SC9314UA-BK</t>
   </si>
   <si>
@@ -588,6 +1167,21 @@
     <t>STC9906J</t>
   </si>
   <si>
+    <t>SC2462SO</t>
+  </si>
+  <si>
+    <t>SC2462SO-2462</t>
+  </si>
+  <si>
+    <t>SC2462SO-6472</t>
+  </si>
+  <si>
+    <t>SC2462UA</t>
+  </si>
+  <si>
+    <t>SC2462UA-2462</t>
+  </si>
+  <si>
     <t>SC2462UA-BK</t>
   </si>
   <si>
@@ -597,6 +1191,27 @@
     <t>SC2462UA-CJ-10AK-6472</t>
   </si>
   <si>
+    <t>SC2462UA-CJ-10HK-6472</t>
+  </si>
+  <si>
+    <t>SC2464SO</t>
+  </si>
+  <si>
+    <t>SC2464SO-2464</t>
+  </si>
+  <si>
+    <t>SC2464UA</t>
+  </si>
+  <si>
+    <t>SC2464UA-2464</t>
+  </si>
+  <si>
+    <t>SC2462SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2462SO-Q-CJ-10CR-2462</t>
+  </si>
+  <si>
     <t>SC2464SO-TR</t>
   </si>
   <si>
@@ -609,15 +1224,111 @@
     <t>PSTC9906I</t>
   </si>
   <si>
+    <t>SC2430UA</t>
+  </si>
+  <si>
+    <t>SC2430UA-2430</t>
+  </si>
+  <si>
     <t>SC2430UA-BK</t>
   </si>
   <si>
     <t>SC2430UA-CI-10AK-2430</t>
   </si>
   <si>
+    <t>SC2432HUA</t>
+  </si>
+  <si>
+    <t>SC2432HUA-2432H</t>
+  </si>
+  <si>
+    <t>SC2432SO</t>
+  </si>
+  <si>
+    <t>NM.SC2432SO</t>
+  </si>
+  <si>
+    <t>SC2432SO-2432</t>
+  </si>
+  <si>
+    <t>SC2432SO-N</t>
+  </si>
+  <si>
+    <t>SC2432SO-N-2432</t>
+  </si>
+  <si>
+    <t>SC2432UA</t>
+  </si>
+  <si>
+    <t>SC2432UA-1101</t>
+  </si>
+  <si>
+    <t>SC2432UA-2432</t>
+  </si>
+  <si>
+    <t>SC2432UA-6232</t>
+  </si>
+  <si>
+    <t>SC2434SO</t>
+  </si>
+  <si>
+    <t>SC2434SO-2434</t>
+  </si>
+  <si>
+    <t>SC2434SO-N</t>
+  </si>
+  <si>
+    <t>SC2434SO-N-2434</t>
+  </si>
+  <si>
+    <t>SC2434UA</t>
+  </si>
+  <si>
+    <t>SC2434UA-2434</t>
+  </si>
+  <si>
     <t>SC2434UA-BK</t>
   </si>
   <si>
+    <t>SC2434UA-CI-10AK-2434</t>
+  </si>
+  <si>
+    <t>SC2436SO</t>
+  </si>
+  <si>
+    <t>SC2436SO-2436</t>
+  </si>
+  <si>
+    <t>SC2436UA</t>
+  </si>
+  <si>
+    <t>SC2436UA-2436</t>
+  </si>
+  <si>
+    <t>SC2438SO</t>
+  </si>
+  <si>
+    <t>SC2438SO-2438</t>
+  </si>
+  <si>
+    <t>SC2438UA</t>
+  </si>
+  <si>
+    <t>SC2438UA-2438</t>
+  </si>
+  <si>
+    <t>SC243XUA</t>
+  </si>
+  <si>
+    <t>NA.SC243XUA</t>
+  </si>
+  <si>
+    <t>NF.SC243XUA-243X</t>
+  </si>
+  <si>
+    <t>SC243XUA-243X</t>
+  </si>
+  <si>
     <t>SC2434SO-N-TR</t>
   </si>
   <si>
@@ -639,10 +1350,34 @@
     <t>STC9G002A</t>
   </si>
   <si>
+    <t>PSTC9G002A</t>
+  </si>
+  <si>
     <t>PSTC9G002A-0</t>
   </si>
   <si>
+    <t>SC2402LSO-N-177</t>
+  </si>
+  <si>
+    <t>SC2402LSO-N-2402</t>
+  </si>
+  <si>
+    <t>SC2402SO-N（STC9G002A)-G-2402</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-G</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-G(STC9G002A)-177</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-GA-00LR-2402</t>
+  </si>
+  <si>
     <t>SC2402SO-N-GA-00NR-2402</t>
+  </si>
+  <si>
+    <t>SC2402LUA-2402</t>
   </si>
   <si>
     <t>预测</t>
@@ -662,1226 +1397,6 @@
   </si>
   <si>
     <t xml:space="preserve">  </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC4643SA-S-TR-Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC4643SA-S-Q-DE-40HR-2100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9625VB-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NM.SC9625VB-CE-00CK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1134UA-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NM.SC1134UA-CI-00AK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2402UA-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NM.SC2402UA-GB-00AK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2402UA-CJ-90AK-2402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2402UA-GB-00AK-177</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2402UA-GB-0XAK-U18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2402UA-GB-0XAK-2402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2402UA-GB-00AK-6501</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC9G002B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SD211VB-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SD211VB-CA-90AK-KH211</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SD211VB-CA-90AK-211</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FD1016A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SD2276VB-CA-90AK-KH276</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9648TS-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9648TS-AI-10AK-9648</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9314UA-CF-0XAK-9201L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9314UA-CF-0XAK-9209</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NM.SC9314UA-CF-0XAK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9314UA-Q-CF-0XAK-94M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9314UA-BK-Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC60226SS-TB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NM.SC60226SS-DC-00CB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1245UA-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1245UA-CD-0XHX-41F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2464UA-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2464UA-CJ-10AK-2464</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2462SO-TR-Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2462SO-Q-CJ-10CR-2462</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2448UA-N-BK-Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC11102B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2448SO-Q-DB-60CR-2448</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2443UA-BK-Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2443UA-Q-DB-60AK-2443</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2443SO-TR-Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2443SO-Q-DB-60CR-2443</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2442UA-BK-Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2442UA-Q-CP-10AK-2442</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC9906P</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2442SO-TR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2442SO-CR-10CR-2442</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC9906R</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2438SO-TR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2434UA-CI-10AK-2434</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2438SO-CM-10CR-2438</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2438SO-TR-Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC9906M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2436UA-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2436UA-CI-10AK-2436</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2436UA-CI-10AK-6210</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2436SO-TR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2436SO-TR-Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2436SO-Q-CM-10CR-2436</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2436SO-CM-10CR-2436</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2434SO-TR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2434SO-CM-10CR-2434</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2432UA-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2432UA-CI-10AK-2432</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2432UA-CI-10AK-6232</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2432SO-N-TR-Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2432SO-N-Q-CI-10CR-2432</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2432SO-TR-Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2432SO-Q-CM-10AR-NM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2432SO-Q-CM-10AR-2432</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2432SO-TR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2432SO-CM-10CR-2432</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1134B1-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1134B1-CI-00HK-43F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9633VB-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9634VB-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9633VB-CF-00CK-9633</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9634VB-CG-00CK-9634</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9634VB-CG-00CK-SZ48</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9625VB-BK-Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9625VB-Q-CE-4XCK-9625L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9625VB-TR-Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9625VB-Q-CE-4XCR-9625L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2448UA-N-Q-DB-60AK-2448</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2438SO-Q-CM-10CR-2438</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1645A2-AE-00HK-601HL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1645A2-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1134UA-CI-00AK-3144</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1245A1-61HA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S41H-A2-S41H</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1645A1-AI-00HK-65HA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1645A1-AI-00HK-1466</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC4643VB-S-TR-Q</t>
-  </si>
-  <si>
-    <t>SC4643VB-S-Q-DE-40CR-4643</t>
-  </si>
-  <si>
-    <t>STC9D06F</t>
-  </si>
-  <si>
-    <t>SC4645VB-BK</t>
-  </si>
-  <si>
-    <t>SC4645VB-DF-00CK-4645</t>
-  </si>
-  <si>
-    <t>STC13103B</t>
-  </si>
-  <si>
-    <t>SC4665VB-BK</t>
-  </si>
-  <si>
-    <t>SC4665VB-HB-33CK-4665</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-CJ-90NR-NM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC9A001G</t>
-  </si>
-  <si>
-    <t>SC9642TS-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9642TS-Q-AG-4XHR-9642</t>
-  </si>
-  <si>
-    <t>SC9642TS-E-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9642TS-E-Q-AH-4XLR-9642</t>
-  </si>
-  <si>
-    <t>SC9642TS-E362-Q-AH-4XLR-9642</t>
-  </si>
-  <si>
-    <t>SC9641TS-P-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9641TS-P-Q-AI-10LR-9641P</t>
-  </si>
-  <si>
-    <t>SC9625VB-CE-00CR-9625L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC9625VB-TR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC4688DC-Q-DC-40AR-6388</t>
-  </si>
-  <si>
-    <t>SC2462SO-TR</t>
-  </si>
-  <si>
-    <t>SC2462SO-CJ-10CR-2462</t>
-  </si>
-  <si>
-    <t>SC2498CUA-N-Q-DB-60CK-2498C</t>
-  </si>
-  <si>
-    <t>SC2498UA-N-Q-DB-60CK-2498</t>
-  </si>
-  <si>
-    <t>STC9910F</t>
-  </si>
-  <si>
-    <t>SC9621VB-BK</t>
-  </si>
-  <si>
-    <t>SC9621VB-CF-00CK-9621</t>
-  </si>
-  <si>
-    <t>SC9621VB-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9621VB-Q-CN-4XCR-9621</t>
-  </si>
-  <si>
-    <t>STC2899AE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1645B1-AI-00HK-615HA</t>
-  </si>
-  <si>
-    <t>PSTC9G001C</t>
-  </si>
-  <si>
-    <t>SC1002N1-BK</t>
-  </si>
-  <si>
-    <t>SC1002N1-CL-00HK-42N</t>
-  </si>
-  <si>
-    <t>SC1002S1-BK</t>
-  </si>
-  <si>
-    <t>SC1002S1-CG-00AK-41F</t>
-  </si>
-  <si>
-    <t>SC1133UA-BK</t>
-  </si>
-  <si>
-    <t>SC1133UA-CJ-00AK-1133</t>
-  </si>
-  <si>
-    <t>SC1134BU-CI-00AR-1134</t>
-  </si>
-  <si>
-    <t>SC1134SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC1134SO-N-CF-00LR-1134</t>
-  </si>
-  <si>
-    <t>SC1138SO-N-TR-Q</t>
-  </si>
-  <si>
-    <t>SC1138SO-N-Q-CC-00LR-1138</t>
-  </si>
-  <si>
-    <t>SC1445A1</t>
-  </si>
-  <si>
-    <t>SC1445A1-41F</t>
-  </si>
-  <si>
-    <t>SC1645A1-AI-00HK-615HA</t>
-  </si>
-  <si>
-    <t>SC1645B1-AE-00HK-4601</t>
-  </si>
-  <si>
-    <t>SC1845S1-AI-00AK-41F</t>
-  </si>
-  <si>
-    <t>SC1945A1-BK</t>
-  </si>
-  <si>
-    <t>SC1945A1-AJ-00HK-N13</t>
-  </si>
-  <si>
-    <t>SC1945B1-BK</t>
-  </si>
-  <si>
-    <t>SC1945B1-AJ-00HK-N603</t>
-  </si>
-  <si>
-    <t>SC2063SO-TR</t>
-  </si>
-  <si>
-    <t>SC2063SO-GC-00NR-2063</t>
-  </si>
-  <si>
-    <t>SC2063UA-BK</t>
-  </si>
-  <si>
-    <t>SC2063UA-GC-00AK-2063</t>
-  </si>
-  <si>
-    <t>SC2064SO-TR</t>
-  </si>
-  <si>
-    <t>SC2064SO-GC-00NR-2064</t>
-  </si>
-  <si>
-    <t>SC2202SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC2202SO-N-CE-00NR-2202</t>
-  </si>
-  <si>
-    <t>SC2242SO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2242SO-Q-CH-10CR-2242</t>
-  </si>
-  <si>
-    <t>SC2242SO-Q-CH-10CR-2642</t>
-  </si>
-  <si>
-    <t>SC2242UA-BK</t>
-  </si>
-  <si>
-    <t>SC2242UA-CE-00AK-2242</t>
-  </si>
-  <si>
-    <t>SC2242UA-BK-Q</t>
-  </si>
-  <si>
-    <t>SC2242UA-Q-CH-10AK-2242</t>
-  </si>
-  <si>
-    <t>SC2413SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC2413SO-N-CD-00LR-44E</t>
-  </si>
-  <si>
-    <t>SC2432SO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2432SO-Q-CM-10CR-2432</t>
-  </si>
-  <si>
-    <t>SC243XSO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC243XSO-Q-CM-10CR-243X</t>
-  </si>
-  <si>
-    <t>SC2442UA-BK</t>
-  </si>
-  <si>
-    <t>SC2442UA-CP-10AK-2442</t>
-  </si>
-  <si>
-    <t>SC2442UA-CP-10AK-U18</t>
-  </si>
-  <si>
-    <t>SC2448SO-Q-DB-40CR-2448</t>
-  </si>
-  <si>
-    <t>SC2452SO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2452SO-Q-DD-60AR-2452</t>
-  </si>
-  <si>
-    <t>SC2455SO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2455SO-Q-CK-10CR-2455</t>
-  </si>
-  <si>
-    <t>SC2466SO-TR</t>
-  </si>
-  <si>
-    <t>SC2466SO-CO-10CR-2466</t>
-  </si>
-  <si>
-    <t>SC2498CUA-N-Q-DB-60AK-2498C</t>
-  </si>
-  <si>
-    <t>SC2498SO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2498SO-Q-DB-60CR-2498</t>
-  </si>
-  <si>
-    <t>SC2498TSO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2498TSO-Q-CC-10CR-2498T</t>
-  </si>
-  <si>
-    <t>SC2498UA-N-Q-DB-60AK-2498</t>
-  </si>
-  <si>
-    <t>SC2527S6-AB-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2527S6-AB-Q-DA-40CR-2527</t>
-  </si>
-  <si>
-    <t>SC2527S6-SD-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2527S6-SD-Q-DA-40CR-2527</t>
-  </si>
-  <si>
-    <t>SC2546VB-AB-BK</t>
-  </si>
-  <si>
-    <t>SC2546VB-AB-DA-00AK-2546</t>
-  </si>
-  <si>
-    <t>SC25791CUA-A-Q</t>
-  </si>
-  <si>
-    <t>SC25791CUA-A(STC11210G-Q)-25791C</t>
-  </si>
-  <si>
-    <t>SC25791SE-TR-Q</t>
-  </si>
-  <si>
-    <t>SC25791SE-Q-CG-40CR-5791</t>
-  </si>
-  <si>
-    <t>SC25891CUA-A-Q</t>
-  </si>
-  <si>
-    <t>SC25891CUA-A-Q(STC11210G-Q)-25891C</t>
-  </si>
-  <si>
-    <t>SC25891SE-TR-Q</t>
-  </si>
-  <si>
-    <t>SC25891SE-Q-CG-40CR-5891</t>
-  </si>
-  <si>
-    <t>SC2943SO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2943SO-Q-DB-60CR-2943</t>
-  </si>
-  <si>
-    <t>SC2948S2-BK</t>
-  </si>
-  <si>
-    <t>SC2948S2-DB-60AK-61H</t>
-  </si>
-  <si>
-    <t>SC2968S1-N-BK</t>
-  </si>
-  <si>
-    <t>SC2968S1-N-DC-4XAK-S21C</t>
-  </si>
-  <si>
-    <t>SC4001SE-TR</t>
-  </si>
-  <si>
-    <t>SC4001SE-CB-90CR-4001</t>
-  </si>
-  <si>
-    <t>SC4002BU-TR</t>
-  </si>
-  <si>
-    <t>SC4002BU-CA-00CR-4002</t>
-  </si>
-  <si>
-    <t>SC4002SO</t>
-  </si>
-  <si>
-    <t>SC4002SO(STC4000AA)-4002</t>
-  </si>
-  <si>
-    <t>SC4002SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC4002SO-N-CA-00NR-4002</t>
-  </si>
-  <si>
-    <t>SC4002UA-BK</t>
-  </si>
-  <si>
-    <t>SC4002UA-CA-00AK-4002</t>
-  </si>
-  <si>
-    <t>SC4002UA-CA-00AK-95A</t>
-  </si>
-  <si>
-    <t>SC4011DN</t>
-  </si>
-  <si>
-    <t>SC4011DN-4011</t>
-  </si>
-  <si>
-    <t>SC4019S7-BK</t>
-  </si>
-  <si>
-    <t>SC4019S7-CC-90AK-49E</t>
-  </si>
-  <si>
-    <t>SC4101DN</t>
-  </si>
-  <si>
-    <t>SC4101DN(STC11201B1)-4101</t>
-  </si>
-  <si>
-    <t>SC4103DN</t>
-  </si>
-  <si>
-    <t>SC4103DN(STC11201B1)-4103</t>
-  </si>
-  <si>
-    <t>SC4251D3-TR</t>
-  </si>
-  <si>
-    <t>SC4251D3-GA-00FR-4251</t>
-  </si>
-  <si>
-    <t>SC4391S6-TR</t>
-  </si>
-  <si>
-    <t>SC4391S6-GB-00NR-4391</t>
-  </si>
-  <si>
-    <t>SC4616BU</t>
-  </si>
-  <si>
-    <t>SC4616BU-4616</t>
-  </si>
-  <si>
-    <t>SC4616UA-10.2NF-BK</t>
-  </si>
-  <si>
-    <t>SC4616UA-10.2NF-CD-90AK-4616</t>
-  </si>
-  <si>
-    <t>SC4643SA-Q-DE-40CK-4643</t>
-  </si>
-  <si>
-    <t>SC4689SA-BK-Q</t>
-  </si>
-  <si>
-    <t>SC4689SA-Q-DF-40CK-4689</t>
-  </si>
-  <si>
-    <t>SC4703SO-TR</t>
-  </si>
-  <si>
-    <t>SC4703SO-GB-00NR-4703</t>
-  </si>
-  <si>
-    <t>SC4823S6-TR</t>
-  </si>
-  <si>
-    <t>SC4823S6-GA-00NR-4823</t>
-  </si>
-  <si>
-    <t>SC4923SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC4923SO-N-CD-00NR-4923</t>
-  </si>
-  <si>
-    <t>SC60104</t>
-  </si>
-  <si>
-    <t>NM.SC60104</t>
-  </si>
-  <si>
-    <t>SC60226SS-TB</t>
-  </si>
-  <si>
-    <t>NA.SC60226SS-DC</t>
-  </si>
-  <si>
-    <t>SC60370</t>
-  </si>
-  <si>
-    <t>SC60370(STC9D05C)-60370</t>
-  </si>
-  <si>
-    <t>SC69401DC-SPI-TR-Q</t>
-  </si>
-  <si>
-    <t>SC69401DC-SPI-Q-HD-4XCR-69401</t>
-  </si>
-  <si>
-    <t>SC69401DC-TR</t>
-  </si>
-  <si>
-    <t>SC69401DC-HD-4XCR-69401</t>
-  </si>
-  <si>
-    <t>SC69401DC-TR-Q</t>
-  </si>
-  <si>
-    <t>SC69401DC-Q-HD-4XCR-69401</t>
-  </si>
-  <si>
-    <t>SC69401HS-SPI-TR-Q</t>
-  </si>
-  <si>
-    <t>SC69401HS-SPI-Q-HD-4XTR-69401</t>
-  </si>
-  <si>
-    <t>SC69401HS-TR</t>
-  </si>
-  <si>
-    <t>SC69401HS-HD-4XTR-69401</t>
-  </si>
-  <si>
-    <t>SC69401HS-TR-Q</t>
-  </si>
-  <si>
-    <t>SC69401HS-Q-HD-4XTR-69401</t>
-  </si>
-  <si>
-    <t>SC9641TS-P-AI-10LR-41CPA</t>
-  </si>
-  <si>
-    <t>SC9642TS-E-TR</t>
-  </si>
-  <si>
-    <t>SC9642TS-E-AH-4XLR-9642</t>
-  </si>
-  <si>
-    <t>SC9675IM-HRF00-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9675IM-HRF00-Q-AB-4XAR-9675</t>
-  </si>
-  <si>
-    <t>SC9675IM-HRF11-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9675IM-HRF11-Q-AB-4XAR-9675</t>
-  </si>
-  <si>
-    <t>SC9675IM-LRF00-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9675IM-LRF00-Q-AB-4XAR-9675</t>
-  </si>
-  <si>
-    <t>SC9675IM-LRF01-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9675IM-LRF01-Q-AB-4XAR-9675</t>
-  </si>
-  <si>
-    <t>SC9675IM-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9675IM-Q-AB-4XAR-9675</t>
-  </si>
-  <si>
-    <t>SC9675T3-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9675T3-Q-AB-4XAR-9675</t>
-  </si>
-  <si>
-    <t>SC9683TS-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9683TS-Q-DB-4XAR-9683</t>
-  </si>
-  <si>
-    <t>SC9684TS-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9684TS-Q-DB-4XAR-9684</t>
-  </si>
-  <si>
-    <t>SC9685TS-RP120-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9685TS-RP120-Q-DB-46AR-96852</t>
-  </si>
-  <si>
-    <t>SD477VB-BK</t>
-  </si>
-  <si>
-    <t>SD477VB-GC-90AK-477S</t>
-  </si>
-  <si>
-    <t>SD477VB-GC-90AK-KH477</t>
-  </si>
-  <si>
-    <t>SL002147DC-TR</t>
-  </si>
-  <si>
-    <t>SL002147DC-GB-00AR-2147</t>
-  </si>
-  <si>
-    <t>SL54123ADC-TR</t>
-  </si>
-  <si>
-    <t>SL54123ADC-GB-00AR-54123A</t>
-  </si>
-  <si>
-    <t>SPD3242</t>
-  </si>
-  <si>
-    <t>SPD3242(STC35301)</t>
-  </si>
-  <si>
-    <t>VE1430Q1BA3R5</t>
-  </si>
-  <si>
-    <t>TRVE1430Q1BA3R5(VA2201D)-1430Q</t>
-  </si>
-  <si>
-    <t>VE1430Q1CA3R33</t>
-  </si>
-  <si>
-    <t>TRVE1430Q1CA3R33(VA2201D)-1430Q</t>
-  </si>
-  <si>
-    <t>VE1430Q1CA3R5</t>
-  </si>
-  <si>
-    <t>TRVE1430Q1CA3R5-1430Q</t>
-  </si>
-  <si>
-    <t>VE1430Q1VA3RADJ</t>
-  </si>
-  <si>
-    <t>TRVE1430Q1VA3RADJ(VA2201E)-1430Q</t>
-  </si>
-  <si>
-    <t>VE8602A5R</t>
-  </si>
-  <si>
-    <t>TRVE8602A5R-8602</t>
-  </si>
-  <si>
-    <t>VE8602AKR</t>
-  </si>
-  <si>
-    <t>VE8602AKR-8602</t>
-  </si>
-  <si>
-    <t>ZH6338</t>
-  </si>
-  <si>
-    <t>ZH6531</t>
-  </si>
-  <si>
-    <t>SC3100VB-BK-Q</t>
-  </si>
-  <si>
-    <t>SC3100VB-DG-00CK-3100</t>
-  </si>
-  <si>
-    <t>SC2033SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC2033SO-N-GD-00NR-2033</t>
-  </si>
-  <si>
-    <t>SC919SO-N-TR-Q</t>
-  </si>
-  <si>
-    <t>SC919SO-N-Q-CD-90CR-919H</t>
-  </si>
-  <si>
-    <t>SC1645B1-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1645A1-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC9G001C</t>
-  </si>
-  <si>
-    <t>STC9G001C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC1002AG</t>
-  </si>
-  <si>
-    <t>STC11102C</t>
-  </si>
-  <si>
-    <t>STC1002AL</t>
-  </si>
-  <si>
-    <t>STC1898AJ</t>
-  </si>
-  <si>
-    <t>STC1002AF</t>
-  </si>
-  <si>
-    <t>STC1898AC</t>
-  </si>
-  <si>
-    <t>STC2899AB</t>
-  </si>
-  <si>
-    <t>STC2899AE</t>
-  </si>
-  <si>
-    <t>STC2899AJ</t>
-  </si>
-  <si>
-    <t>STC9902E</t>
-  </si>
-  <si>
-    <t>STC9906H</t>
-  </si>
-  <si>
-    <t>STC9902D</t>
-  </si>
-  <si>
-    <t>STC9906M</t>
-  </si>
-  <si>
-    <t>STC11103D</t>
-  </si>
-  <si>
-    <t>STC9906K</t>
-  </si>
-  <si>
-    <t>STC9906O</t>
-  </si>
-  <si>
-    <t>STC11300C</t>
-  </si>
-  <si>
-    <t>STC11131A</t>
-  </si>
-  <si>
-    <t>STC11210G-Q</t>
-  </si>
-  <si>
-    <t>STC4001AB</t>
-  </si>
-  <si>
-    <t>STC4000AA</t>
-  </si>
-  <si>
-    <t>STC4011C</t>
-  </si>
-  <si>
-    <t>STC11201B1</t>
-  </si>
-  <si>
-    <t>STC11401A</t>
-  </si>
-  <si>
-    <t>STC11202B</t>
-  </si>
-  <si>
-    <t>STC9907D</t>
-  </si>
-  <si>
-    <t>STC9D01F</t>
-  </si>
-  <si>
-    <t>STC11205B</t>
-  </si>
-  <si>
-    <t>STC11205A_T</t>
-  </si>
-  <si>
-    <t>SC4009D</t>
-  </si>
-  <si>
-    <t>STC9D02C</t>
-  </si>
-  <si>
-    <t>STC9D05C</t>
-  </si>
-  <si>
-    <t>STC9H002DQ</t>
-  </si>
-  <si>
-    <t>STC9A002B</t>
-  </si>
-  <si>
-    <t>STC12100B</t>
-  </si>
-  <si>
-    <t>STC22304C</t>
-  </si>
-  <si>
-    <t>STC16100B</t>
-  </si>
-  <si>
-    <t>STC35301</t>
-  </si>
-  <si>
-    <t>VA2201D</t>
-  </si>
-  <si>
-    <t>VA2201E</t>
-  </si>
-  <si>
-    <t>V2302C</t>
-  </si>
-  <si>
-    <t>STC9D06G</t>
-  </si>
-  <si>
-    <t>STC9G001D</t>
-  </si>
-  <si>
-    <t>STC9913D</t>
-  </si>
-  <si>
-    <t>SC1945B1</t>
-  </si>
-  <si>
-    <t>SC1945B1(STC2899AJ)-N13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC2899AJ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC2402SO-N-CJ-90NR-6571</t>
-  </si>
-  <si>
-    <t>SC1002N2W-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1002N2W-CL-00AK-N41F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1919UA-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC1919UA-CD-90AK-919H</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SC4001UA-BK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NM.SC4001UA-CB-90AK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SYLM358DC-TR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SYLM358DC-GC-90AR-LM358</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SYLM358DC-GC-90AR-NM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC1002AL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC9913D</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC4001AB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STC9G005C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1889,7 +1404,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1903,20 +1418,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1945,7 +1446,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1953,63 +1454,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2 4 2 2" xfId="1" xr:uid="{9C7ED766-84C1-4343-B919-15B8593B06F8}"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2285,7 +1743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X291"/>
+  <dimension ref="A1:X287"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
@@ -2295,207 +1753,207 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D1" s="3" t="s">
-        <v>202</v>
+        <v>450</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>205</v>
+        <v>453</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>204</v>
+        <v>452</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>202</v>
+        <v>450</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>203</v>
+        <v>451</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>204</v>
+        <v>452</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>202</v>
+        <v>450</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>203</v>
+        <v>451</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>204</v>
+        <v>452</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>202</v>
+        <v>450</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>203</v>
+        <v>451</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>204</v>
+        <v>452</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>202</v>
+        <v>450</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>203</v>
+        <v>451</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>204</v>
+        <v>452</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>203</v>
+        <v>451</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>202</v>
+        <v>450</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>204</v>
+        <v>452</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>202</v>
+        <v>450</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>203</v>
+        <v>451</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="3">
         <v>7</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="1">
         <v>7</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="2">
         <v>7</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="3">
         <v>8</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="1">
         <v>8</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="2">
         <v>8</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="3">
         <v>9</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="1">
         <v>9</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="2">
         <v>9</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="3">
         <v>10</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="1">
         <v>10</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="2">
         <v>10</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="3">
         <v>11</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="1">
         <v>11</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="2">
         <v>11</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="1">
         <v>12</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="3">
         <v>12</v>
       </c>
-      <c r="U2" s="7">
+      <c r="U2" s="2">
         <v>12</v>
       </c>
-      <c r="V2" s="5">
+      <c r="V2" s="3">
         <v>1</v>
       </c>
-      <c r="W2" s="6">
+      <c r="W2" s="1">
         <v>1</v>
       </c>
-      <c r="X2" s="7">
+      <c r="X2" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>138</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>163</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>177</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>189</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -2503,3123 +1961,3076 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>514</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>329</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>329</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>199</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>200</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>200</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>119</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>119</v>
+        <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>119</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>295</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>517</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>330</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>331</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>515</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>332</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>333</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>518</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>334</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>335</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>278</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>279</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>171</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>172</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>171</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>336</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>519</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>337</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>338</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>164</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>165</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>170</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>169</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>168</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>162</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>166</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>162</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>166</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>162</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>212</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>520</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>339</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>340</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>294</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>235</v>
+        <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>236</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>521</v>
+        <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>341</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>342</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C42" t="s">
-        <v>296</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C43" t="s">
-        <v>297</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>512</v>
+        <v>68</v>
       </c>
       <c r="C44" t="s">
-        <v>343</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>327</v>
+        <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>292</v>
+        <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>291</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C47" t="s">
-        <v>328</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>522</v>
+        <v>76</v>
       </c>
       <c r="B48" t="s">
-        <v>511</v>
+        <v>79</v>
       </c>
       <c r="C48" t="s">
-        <v>344</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="B49" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="C49" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="B50" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="C50" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="B51" t="s">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="C51" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="C52" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="B53" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="C53" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="B54" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="C54" t="s">
-        <v>345</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>523</v>
+        <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>346</v>
+        <v>90</v>
       </c>
       <c r="C55" t="s">
-        <v>347</v>
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>523</v>
+        <v>80</v>
       </c>
       <c r="B56" t="s">
-        <v>348</v>
+        <v>90</v>
       </c>
       <c r="C56" t="s">
-        <v>349</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>557</v>
+        <v>80</v>
       </c>
       <c r="B57" t="s">
-        <v>507</v>
+        <v>93</v>
       </c>
       <c r="C57" t="s">
-        <v>508</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>513</v>
+        <v>80</v>
       </c>
       <c r="B58" t="s">
-        <v>350</v>
+        <v>95</v>
       </c>
       <c r="C58" t="s">
-        <v>351</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>513</v>
+        <v>80</v>
       </c>
       <c r="B59" t="s">
-        <v>352</v>
+        <v>95</v>
       </c>
       <c r="C59" t="s">
-        <v>353</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>513</v>
+        <v>80</v>
       </c>
       <c r="B60" t="s">
-        <v>354</v>
+        <v>98</v>
       </c>
       <c r="C60" t="s">
-        <v>355</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>524</v>
+        <v>80</v>
       </c>
       <c r="B61" t="s">
-        <v>356</v>
+        <v>100</v>
       </c>
       <c r="C61" t="s">
-        <v>357</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>525</v>
+        <v>102</v>
       </c>
       <c r="B62" t="s">
-        <v>358</v>
+        <v>103</v>
       </c>
       <c r="C62" t="s">
-        <v>359</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>525</v>
+        <v>102</v>
       </c>
       <c r="B63" t="s">
-        <v>358</v>
+        <v>103</v>
       </c>
       <c r="C63" t="s">
-        <v>360</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>524</v>
+        <v>102</v>
       </c>
       <c r="B64" t="s">
-        <v>361</v>
+        <v>103</v>
       </c>
       <c r="C64" t="s">
-        <v>362</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>525</v>
+        <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>363</v>
+        <v>103</v>
       </c>
       <c r="C65" t="s">
-        <v>364</v>
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="B66" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="C66" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>199</v>
+        <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="C67" t="s">
-        <v>201</v>
+        <v>110</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="B68" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="C68" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="B69" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C69" t="s">
-        <v>306</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="C70" t="s">
-        <v>562</v>
+        <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="B71" t="s">
-        <v>213</v>
+        <v>116</v>
       </c>
       <c r="C71" t="s">
-        <v>217</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="B72" t="s">
-        <v>213</v>
+        <v>116</v>
       </c>
       <c r="C72" t="s">
-        <v>218</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="B73" t="s">
-        <v>213</v>
+        <v>116</v>
       </c>
       <c r="C73" t="s">
-        <v>219</v>
+        <v>119</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="B74" t="s">
-        <v>213</v>
+        <v>120</v>
       </c>
       <c r="C74" t="s">
-        <v>216</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>220</v>
+        <v>122</v>
       </c>
       <c r="B75" t="s">
-        <v>213</v>
+        <v>123</v>
       </c>
       <c r="C75" t="s">
-        <v>214</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="B76" t="s">
-        <v>213</v>
+        <v>125</v>
       </c>
       <c r="C76" t="s">
-        <v>215</v>
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="B77" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C77" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>526</v>
+        <v>128</v>
       </c>
       <c r="B78" t="s">
-        <v>365</v>
+        <v>129</v>
       </c>
       <c r="C78" t="s">
-        <v>366</v>
+        <v>130</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>188</v>
+        <v>131</v>
       </c>
       <c r="B79" t="s">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="C79" t="s">
-        <v>191</v>
+        <v>133</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>188</v>
+        <v>131</v>
       </c>
       <c r="B80" t="s">
-        <v>195</v>
+        <v>132</v>
       </c>
       <c r="C80" t="s">
-        <v>196</v>
+        <v>134</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>188</v>
+        <v>131</v>
       </c>
       <c r="B81" t="s">
-        <v>271</v>
+        <v>132</v>
       </c>
       <c r="C81" t="s">
-        <v>272</v>
+        <v>135</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>258</v>
+        <v>131</v>
       </c>
       <c r="B82" t="s">
-        <v>276</v>
+        <v>136</v>
       </c>
       <c r="C82" t="s">
-        <v>277</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>258</v>
+        <v>131</v>
       </c>
       <c r="B83" t="s">
-        <v>273</v>
+        <v>138</v>
       </c>
       <c r="C83" t="s">
-        <v>274</v>
+        <v>139</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>258</v>
+        <v>131</v>
       </c>
       <c r="B84" t="s">
-        <v>273</v>
+        <v>138</v>
       </c>
       <c r="C84" t="s">
-        <v>275</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>527</v>
+        <v>141</v>
       </c>
       <c r="B85" t="s">
-        <v>367</v>
+        <v>142</v>
       </c>
       <c r="C85" t="s">
-        <v>368</v>
+        <v>143</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="B86" t="s">
-        <v>268</v>
+        <v>144</v>
       </c>
       <c r="C86" t="s">
-        <v>270</v>
+        <v>145</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="B87" t="s">
-        <v>268</v>
+        <v>144</v>
       </c>
       <c r="C87" t="s">
-        <v>269</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="B88" t="s">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="C88" t="s">
-        <v>194</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>258</v>
+        <v>141</v>
       </c>
       <c r="B89" t="s">
-        <v>266</v>
+        <v>144</v>
       </c>
       <c r="C89" t="s">
-        <v>267</v>
+        <v>148</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="B90" t="s">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="C90" t="s">
-        <v>255</v>
+        <v>149</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>258</v>
+        <v>141</v>
       </c>
       <c r="B91" t="s">
-        <v>262</v>
+        <v>144</v>
       </c>
       <c r="C91" t="s">
-        <v>265</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>258</v>
+        <v>141</v>
       </c>
       <c r="B92" t="s">
-        <v>263</v>
+        <v>144</v>
       </c>
       <c r="C92" t="s">
-        <v>264</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="B93" t="s">
-        <v>259</v>
+        <v>152</v>
       </c>
       <c r="C93" t="s">
-        <v>261</v>
+        <v>152</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="B94" t="s">
-        <v>259</v>
+        <v>154</v>
       </c>
       <c r="C94" t="s">
-        <v>260</v>
+        <v>155</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>258</v>
+        <v>153</v>
       </c>
       <c r="B95" t="s">
-        <v>254</v>
+        <v>156</v>
       </c>
       <c r="C95" t="s">
-        <v>256</v>
+        <v>157</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>258</v>
+        <v>153</v>
       </c>
       <c r="B96" t="s">
-        <v>257</v>
+        <v>156</v>
       </c>
       <c r="C96" t="s">
-        <v>290</v>
+        <v>158</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="B97" t="s">
-        <v>197</v>
+        <v>159</v>
       </c>
       <c r="C97" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>527</v>
+        <v>153</v>
       </c>
       <c r="B98" t="s">
-        <v>369</v>
+        <v>159</v>
       </c>
       <c r="C98" t="s">
-        <v>370</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="B99" t="s">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="C99" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="B100" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="C100" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="C101" t="s">
-        <v>73</v>
+        <v>166</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B102" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="C102" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>253</v>
+        <v>169</v>
       </c>
       <c r="B103" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="C103" t="s">
-        <v>252</v>
+        <v>171</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B104" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C104" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="B105" t="s">
-        <v>371</v>
+        <v>172</v>
       </c>
       <c r="C105" t="s">
-        <v>372</v>
+        <v>174</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="B106" t="s">
-        <v>371</v>
+        <v>175</v>
       </c>
       <c r="C106" t="s">
-        <v>373</v>
+        <v>176</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>250</v>
+        <v>169</v>
       </c>
       <c r="B107" t="s">
-        <v>248</v>
+        <v>175</v>
       </c>
       <c r="C107" t="s">
-        <v>249</v>
+        <v>177</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B108" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C108" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
       <c r="B109" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="C109" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
       <c r="B110" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
       <c r="C110" t="s">
-        <v>245</v>
+        <v>183</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
       <c r="B111" t="s">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="C111" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B112" t="s">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="C112" t="s">
-        <v>374</v>
+        <v>185</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
       <c r="B113" t="s">
-        <v>241</v>
+        <v>186</v>
       </c>
       <c r="C113" t="s">
-        <v>289</v>
+        <v>187</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>528</v>
+        <v>169</v>
       </c>
       <c r="B114" t="s">
-        <v>375</v>
+        <v>188</v>
       </c>
       <c r="C114" t="s">
-        <v>376</v>
+        <v>189</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>529</v>
+        <v>169</v>
       </c>
       <c r="B115" t="s">
-        <v>377</v>
+        <v>190</v>
       </c>
       <c r="C115" t="s">
-        <v>378</v>
+        <v>191</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B116" t="s">
-        <v>318</v>
+        <v>193</v>
       </c>
       <c r="C116" t="s">
-        <v>319</v>
+        <v>193</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B117" t="s">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="C117" t="s">
-        <v>240</v>
+        <v>195</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B118" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="C118" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B119" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="C119" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B120" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="C120" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B121" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="C121" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>530</v>
+        <v>192</v>
       </c>
       <c r="B122" t="s">
-        <v>379</v>
+        <v>202</v>
       </c>
       <c r="C122" t="s">
-        <v>380</v>
+        <v>202</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="B123" t="s">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="C123" t="s">
-        <v>320</v>
+        <v>203</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="B124" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="C124" t="s">
-        <v>381</v>
+        <v>204</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="B125" t="s">
-        <v>382</v>
+        <v>205</v>
       </c>
       <c r="C125" t="s">
-        <v>383</v>
+        <v>205</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>531</v>
+        <v>192</v>
       </c>
       <c r="B126" t="s">
-        <v>384</v>
+        <v>206</v>
       </c>
       <c r="C126" t="s">
-        <v>385</v>
+        <v>206</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="B127" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="C127" t="s">
-        <v>321</v>
+        <v>207</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="B128" t="s">
-        <v>158</v>
+        <v>208</v>
       </c>
       <c r="C128" t="s">
-        <v>386</v>
+        <v>208</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>532</v>
+        <v>192</v>
       </c>
       <c r="B129" t="s">
-        <v>387</v>
+        <v>209</v>
       </c>
       <c r="C129" t="s">
-        <v>388</v>
+        <v>209</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>532</v>
+        <v>192</v>
       </c>
       <c r="B130" t="s">
-        <v>389</v>
+        <v>210</v>
       </c>
       <c r="C130" t="s">
-        <v>390</v>
+        <v>210</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>532</v>
+        <v>192</v>
       </c>
       <c r="B131" t="s">
-        <v>391</v>
+        <v>211</v>
       </c>
       <c r="C131" t="s">
-        <v>392</v>
+        <v>211</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>533</v>
+        <v>192</v>
       </c>
       <c r="B132" t="s">
-        <v>393</v>
+        <v>212</v>
       </c>
       <c r="C132" t="s">
-        <v>394</v>
+        <v>212</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>533</v>
+        <v>192</v>
       </c>
       <c r="B133" t="s">
-        <v>395</v>
+        <v>213</v>
       </c>
       <c r="C133" t="s">
-        <v>396</v>
+        <v>213</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>533</v>
+        <v>192</v>
       </c>
       <c r="B134" t="s">
-        <v>397</v>
+        <v>214</v>
       </c>
       <c r="C134" t="s">
-        <v>398</v>
+        <v>214</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>533</v>
+        <v>192</v>
       </c>
       <c r="B135" t="s">
-        <v>399</v>
+        <v>215</v>
       </c>
       <c r="C135" t="s">
-        <v>400</v>
+        <v>215</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="B136" t="s">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="C136" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="B137" t="s">
-        <v>401</v>
+        <v>217</v>
       </c>
       <c r="C137" t="s">
-        <v>402</v>
+        <v>217</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="B138" t="s">
-        <v>403</v>
+        <v>218</v>
       </c>
       <c r="C138" t="s">
-        <v>404</v>
+        <v>218</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>516</v>
+        <v>192</v>
       </c>
       <c r="B139" t="s">
-        <v>405</v>
+        <v>219</v>
       </c>
       <c r="C139" t="s">
-        <v>406</v>
+        <v>219</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>556</v>
+        <v>192</v>
       </c>
       <c r="B140" t="s">
-        <v>505</v>
+        <v>220</v>
       </c>
       <c r="C140" t="s">
-        <v>506</v>
+        <v>221</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>534</v>
+        <v>192</v>
       </c>
       <c r="B141" t="s">
-        <v>407</v>
+        <v>220</v>
       </c>
       <c r="C141" t="s">
-        <v>408</v>
+        <v>222</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>535</v>
+        <v>192</v>
       </c>
       <c r="B142" t="s">
-        <v>409</v>
+        <v>220</v>
       </c>
       <c r="C142" t="s">
-        <v>410</v>
+        <v>223</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>535</v>
+        <v>192</v>
       </c>
       <c r="B143" t="s">
-        <v>411</v>
+        <v>224</v>
       </c>
       <c r="C143" t="s">
-        <v>412</v>
+        <v>225</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>535</v>
+        <v>192</v>
       </c>
       <c r="B144" t="s">
-        <v>413</v>
+        <v>224</v>
       </c>
       <c r="C144" t="s">
-        <v>414</v>
+        <v>226</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>535</v>
+        <v>192</v>
       </c>
       <c r="B145" t="s">
-        <v>415</v>
+        <v>224</v>
       </c>
       <c r="C145" t="s">
-        <v>416</v>
+        <v>227</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>535</v>
+        <v>192</v>
       </c>
       <c r="B146" t="s">
-        <v>415</v>
+        <v>228</v>
       </c>
       <c r="C146" t="s">
-        <v>417</v>
+        <v>229</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>38</v>
+        <v>192</v>
       </c>
       <c r="B147" t="s">
-        <v>418</v>
+        <v>228</v>
       </c>
       <c r="C147" t="s">
-        <v>419</v>
+        <v>230</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>38</v>
+        <v>231</v>
       </c>
       <c r="B148" t="s">
-        <v>39</v>
+        <v>232</v>
       </c>
       <c r="C148" t="s">
-        <v>40</v>
+        <v>233</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="B149" t="s">
-        <v>60</v>
+        <v>232</v>
       </c>
       <c r="C149" t="s">
-        <v>61</v>
+        <v>234</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="B150" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
       <c r="C150" t="s">
-        <v>68</v>
+        <v>236</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="B151" t="s">
-        <v>62</v>
+        <v>237</v>
       </c>
       <c r="C151" t="s">
-        <v>69</v>
+        <v>238</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="B152" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="C152" t="s">
-        <v>67</v>
+        <v>239</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="B153" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="C153" t="s">
-        <v>66</v>
+        <v>240</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="B154" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="C154" t="s">
-        <v>65</v>
+        <v>241</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="B155" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="C155" t="s">
-        <v>64</v>
+        <v>242</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="B156" t="s">
-        <v>62</v>
+        <v>243</v>
       </c>
       <c r="C156" t="s">
-        <v>63</v>
+        <v>244</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>536</v>
+        <v>231</v>
       </c>
       <c r="B157" t="s">
-        <v>420</v>
+        <v>245</v>
       </c>
       <c r="C157" t="s">
-        <v>421</v>
+        <v>246</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>537</v>
+        <v>231</v>
       </c>
       <c r="B158" t="s">
-        <v>422</v>
+        <v>247</v>
       </c>
       <c r="C158" t="s">
-        <v>423</v>
+        <v>248</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>537</v>
+        <v>231</v>
       </c>
       <c r="B159" t="s">
-        <v>424</v>
+        <v>247</v>
       </c>
       <c r="C159" t="s">
-        <v>425</v>
+        <v>249</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>538</v>
+        <v>231</v>
       </c>
       <c r="B160" t="s">
-        <v>426</v>
+        <v>250</v>
       </c>
       <c r="C160" t="s">
-        <v>427</v>
+        <v>251</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>539</v>
+        <v>231</v>
       </c>
       <c r="B161" t="s">
-        <v>428</v>
+        <v>252</v>
       </c>
       <c r="C161" t="s">
-        <v>429</v>
+        <v>253</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>540</v>
+        <v>231</v>
       </c>
       <c r="B162" t="s">
-        <v>430</v>
+        <v>120</v>
       </c>
       <c r="C162" t="s">
-        <v>431</v>
+        <v>254</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>540</v>
+        <v>255</v>
       </c>
       <c r="B163" t="s">
-        <v>432</v>
+        <v>256</v>
       </c>
       <c r="C163" t="s">
-        <v>433</v>
+        <v>257</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>3</v>
+        <v>255</v>
       </c>
       <c r="B164" t="s">
-        <v>5</v>
+        <v>258</v>
       </c>
       <c r="C164" t="s">
-        <v>6</v>
+        <v>259</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>3</v>
+        <v>255</v>
       </c>
       <c r="B165" t="s">
-        <v>5</v>
+        <v>258</v>
       </c>
       <c r="C165" t="s">
-        <v>434</v>
+        <v>260</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>3</v>
+        <v>255</v>
       </c>
       <c r="B166" t="s">
-        <v>24</v>
+        <v>261</v>
       </c>
       <c r="C166" t="s">
-        <v>25</v>
+        <v>262</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>3</v>
+        <v>263</v>
       </c>
       <c r="B167" t="s">
-        <v>207</v>
+        <v>264</v>
       </c>
       <c r="C167" t="s">
-        <v>208</v>
+        <v>265</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>3</v>
+        <v>263</v>
       </c>
       <c r="B168" t="s">
-        <v>7</v>
+        <v>266</v>
       </c>
       <c r="C168" t="s">
-        <v>8</v>
+        <v>266</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>3</v>
+        <v>263</v>
       </c>
       <c r="B169" t="s">
-        <v>9</v>
+        <v>267</v>
       </c>
       <c r="C169" t="s">
-        <v>10</v>
+        <v>267</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>3</v>
+        <v>263</v>
       </c>
       <c r="B170" t="s">
-        <v>9</v>
+        <v>268</v>
       </c>
       <c r="C170" t="s">
-        <v>11</v>
+        <v>269</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>3</v>
+        <v>263</v>
       </c>
       <c r="B171" t="s">
-        <v>12</v>
+        <v>270</v>
       </c>
       <c r="C171" t="s">
-        <v>13</v>
+        <v>271</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>3</v>
+        <v>263</v>
       </c>
       <c r="B172" t="s">
-        <v>14</v>
+        <v>270</v>
       </c>
       <c r="C172" t="s">
-        <v>15</v>
+        <v>272</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>3</v>
+        <v>263</v>
       </c>
       <c r="B173" t="s">
-        <v>22</v>
+        <v>270</v>
       </c>
       <c r="C173" t="s">
-        <v>23</v>
+        <v>273</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>3</v>
+        <v>263</v>
       </c>
       <c r="B174" t="s">
-        <v>16</v>
+        <v>263</v>
       </c>
       <c r="C174" t="s">
-        <v>17</v>
+        <v>263</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>3</v>
+        <v>274</v>
       </c>
       <c r="B175" t="s">
-        <v>18</v>
+        <v>275</v>
       </c>
       <c r="C175" t="s">
-        <v>19</v>
+        <v>276</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>3</v>
+        <v>274</v>
       </c>
       <c r="B176" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="C176" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>3</v>
+        <v>279</v>
       </c>
       <c r="B177" t="s">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="C177" t="s">
-        <v>21</v>
+        <v>280</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="B178" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="C178" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="B179" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="C179" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>42</v>
+        <v>279</v>
       </c>
       <c r="B180" t="s">
-        <v>48</v>
+        <v>281</v>
       </c>
       <c r="C180" t="s">
-        <v>49</v>
+        <v>284</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>42</v>
+        <v>279</v>
       </c>
       <c r="B181" t="s">
-        <v>43</v>
+        <v>285</v>
       </c>
       <c r="C181" t="s">
-        <v>317</v>
+        <v>286</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>42</v>
+        <v>279</v>
       </c>
       <c r="B182" t="s">
-        <v>43</v>
+        <v>285</v>
       </c>
       <c r="C182" t="s">
-        <v>44</v>
+        <v>287</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>42</v>
+        <v>279</v>
       </c>
       <c r="B183" t="s">
-        <v>45</v>
+        <v>285</v>
       </c>
       <c r="C183" t="s">
-        <v>47</v>
+        <v>288</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>42</v>
+        <v>279</v>
       </c>
       <c r="B184" t="s">
-        <v>45</v>
+        <v>289</v>
       </c>
       <c r="C184" t="s">
-        <v>46</v>
+        <v>290</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>541</v>
+        <v>279</v>
       </c>
       <c r="B185" t="s">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="C185" t="s">
-        <v>436</v>
+        <v>291</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>542</v>
+        <v>279</v>
       </c>
       <c r="B186" t="s">
-        <v>437</v>
+        <v>289</v>
       </c>
       <c r="C186" t="s">
-        <v>438</v>
+        <v>292</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>543</v>
+        <v>279</v>
       </c>
       <c r="B187" t="s">
-        <v>439</v>
+        <v>293</v>
       </c>
       <c r="C187" t="s">
-        <v>440</v>
+        <v>294</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>544</v>
+        <v>279</v>
       </c>
       <c r="B188" t="s">
-        <v>441</v>
+        <v>279</v>
       </c>
       <c r="C188" t="s">
-        <v>442</v>
+        <v>279</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>545</v>
+        <v>295</v>
       </c>
       <c r="B189" t="s">
-        <v>443</v>
+        <v>296</v>
       </c>
       <c r="C189" t="s">
-        <v>444</v>
+        <v>297</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="B190" t="s">
-        <v>93</v>
+        <v>296</v>
       </c>
       <c r="C190" t="s">
-        <v>94</v>
+        <v>298</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="B191" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="C191" t="s">
-        <v>96</v>
+        <v>299</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="B192" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="C192" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="B193" t="s">
-        <v>98</v>
+        <v>301</v>
       </c>
       <c r="C193" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="B194" t="s">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="C194" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="B195" t="s">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="C195" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="B196" t="s">
-        <v>101</v>
+        <v>305</v>
       </c>
       <c r="C196" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="B197" t="s">
-        <v>102</v>
+        <v>256</v>
       </c>
       <c r="C197" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="B198" t="s">
-        <v>103</v>
+        <v>256</v>
       </c>
       <c r="C198" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="B199" t="s">
-        <v>104</v>
+        <v>309</v>
       </c>
       <c r="C199" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="B200" t="s">
-        <v>105</v>
+        <v>309</v>
       </c>
       <c r="C200" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+      <c r="G200" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="B201" t="s">
-        <v>106</v>
+        <v>312</v>
       </c>
       <c r="C201" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="B202" t="s">
-        <v>107</v>
+        <v>314</v>
       </c>
       <c r="C202" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>91</v>
+        <v>316</v>
       </c>
       <c r="B203" t="s">
-        <v>108</v>
+        <v>317</v>
       </c>
       <c r="C203" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="B204" t="s">
-        <v>109</v>
+        <v>320</v>
       </c>
       <c r="C204" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="B205" t="s">
-        <v>110</v>
+        <v>321</v>
       </c>
       <c r="C205" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="B206" t="s">
-        <v>111</v>
+        <v>323</v>
       </c>
       <c r="C206" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="B207" t="s">
-        <v>112</v>
+        <v>325</v>
       </c>
       <c r="C207" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="B208" t="s">
-        <v>113</v>
+        <v>325</v>
       </c>
       <c r="C208" t="s">
-        <v>113</v>
+        <v>327</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="B209" t="s">
-        <v>114</v>
+        <v>328</v>
       </c>
       <c r="C209" t="s">
-        <v>114</v>
+        <v>329</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="B210" t="s">
-        <v>115</v>
+        <v>330</v>
       </c>
       <c r="C210" t="s">
-        <v>115</v>
+        <v>331</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="B211" t="s">
-        <v>233</v>
+        <v>332</v>
       </c>
       <c r="C211" t="s">
-        <v>234</v>
+        <v>333</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="B212" t="s">
-        <v>445</v>
+        <v>332</v>
       </c>
       <c r="C212" t="s">
-        <v>446</v>
+        <v>334</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="B213" t="s">
-        <v>116</v>
+        <v>332</v>
       </c>
       <c r="C213" t="s">
-        <v>118</v>
+        <v>335</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>91</v>
+        <v>319</v>
       </c>
       <c r="B214" t="s">
-        <v>116</v>
+        <v>332</v>
       </c>
       <c r="C214" t="s">
-        <v>117</v>
+        <v>336</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>546</v>
+        <v>319</v>
       </c>
       <c r="B215" t="s">
-        <v>447</v>
+        <v>332</v>
       </c>
       <c r="C215" t="s">
-        <v>448</v>
+        <v>337</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>547</v>
+        <v>319</v>
       </c>
       <c r="B216" t="s">
-        <v>449</v>
+        <v>332</v>
       </c>
       <c r="C216" t="s">
-        <v>450</v>
+        <v>338</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>547</v>
+        <v>319</v>
       </c>
       <c r="B217" t="s">
-        <v>451</v>
+        <v>332</v>
       </c>
       <c r="C217" t="s">
-        <v>452</v>
+        <v>339</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>547</v>
+        <v>319</v>
       </c>
       <c r="B218" t="s">
-        <v>453</v>
+        <v>340</v>
       </c>
       <c r="C218" t="s">
-        <v>454</v>
+        <v>341</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>547</v>
+        <v>319</v>
       </c>
       <c r="B219" t="s">
-        <v>455</v>
+        <v>340</v>
       </c>
       <c r="C219" t="s">
-        <v>456</v>
+        <v>342</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>547</v>
+        <v>319</v>
       </c>
       <c r="B220" t="s">
-        <v>457</v>
+        <v>340</v>
       </c>
       <c r="C220" t="s">
-        <v>458</v>
+        <v>343</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>547</v>
+        <v>319</v>
       </c>
       <c r="B221" t="s">
-        <v>459</v>
+        <v>340</v>
       </c>
       <c r="C221" t="s">
-        <v>460</v>
+        <v>344</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>558</v>
+        <v>319</v>
       </c>
       <c r="B222" t="s">
-        <v>509</v>
+        <v>345</v>
       </c>
       <c r="C222" t="s">
-        <v>510</v>
+        <v>346</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>176</v>
+        <v>319</v>
       </c>
       <c r="B223" t="s">
-        <v>178</v>
+        <v>345</v>
       </c>
       <c r="C223" t="s">
-        <v>180</v>
+        <v>347</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>176</v>
+        <v>319</v>
       </c>
       <c r="B224" t="s">
-        <v>178</v>
+        <v>348</v>
       </c>
       <c r="C224" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>176</v>
+        <v>350</v>
       </c>
       <c r="B225" t="s">
-        <v>178</v>
+        <v>351</v>
       </c>
       <c r="C225" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>176</v>
+        <v>350</v>
       </c>
       <c r="B226" t="s">
-        <v>178</v>
+        <v>351</v>
       </c>
       <c r="C226" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>176</v>
+        <v>350</v>
       </c>
       <c r="B227" t="s">
-        <v>178</v>
+        <v>354</v>
       </c>
       <c r="C227" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>176</v>
+        <v>350</v>
       </c>
       <c r="B228" t="s">
-        <v>178</v>
+        <v>354</v>
       </c>
       <c r="C228" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>176</v>
+        <v>350</v>
       </c>
       <c r="B229" t="s">
-        <v>232</v>
+        <v>357</v>
       </c>
       <c r="C229" t="s">
-        <v>231</v>
-      </c>
-      <c r="G229" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>322</v>
+        <v>359</v>
       </c>
       <c r="B230" t="s">
-        <v>323</v>
+        <v>360</v>
       </c>
       <c r="C230" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>322</v>
+        <v>359</v>
       </c>
       <c r="B231" t="s">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="C231" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>173</v>
+        <v>359</v>
       </c>
       <c r="B232" t="s">
-        <v>174</v>
+        <v>50</v>
       </c>
       <c r="C232" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>173</v>
+        <v>359</v>
       </c>
       <c r="B233" t="s">
-        <v>209</v>
+        <v>50</v>
       </c>
       <c r="C233" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>173</v>
+        <v>365</v>
       </c>
       <c r="B234" t="s">
-        <v>285</v>
+        <v>366</v>
       </c>
       <c r="C234" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>173</v>
+        <v>365</v>
       </c>
       <c r="B235" t="s">
-        <v>316</v>
+        <v>367</v>
       </c>
       <c r="C235" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>173</v>
+        <v>365</v>
       </c>
       <c r="B236" t="s">
-        <v>287</v>
+        <v>367</v>
       </c>
       <c r="C236" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>141</v>
+        <v>365</v>
       </c>
       <c r="B237" t="s">
-        <v>142</v>
+        <v>367</v>
       </c>
       <c r="C237" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>141</v>
+        <v>365</v>
       </c>
       <c r="B238" t="s">
-        <v>280</v>
+        <v>367</v>
       </c>
       <c r="C238" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>141</v>
+        <v>365</v>
       </c>
       <c r="B239" t="s">
-        <v>281</v>
+        <v>367</v>
       </c>
       <c r="C239" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>141</v>
+        <v>365</v>
       </c>
       <c r="B240" t="s">
-        <v>281</v>
+        <v>367</v>
       </c>
       <c r="C240" t="s">
-        <v>283</v>
+        <v>373</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>26</v>
+        <v>365</v>
       </c>
       <c r="B241" t="s">
-        <v>27</v>
+        <v>374</v>
       </c>
       <c r="C241" t="s">
-        <v>28</v>
+        <v>375</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>26</v>
+        <v>365</v>
       </c>
       <c r="B242" t="s">
-        <v>29</v>
+        <v>374</v>
       </c>
       <c r="C242" t="s">
-        <v>30</v>
+        <v>376</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>26</v>
+        <v>365</v>
       </c>
       <c r="B243" t="s">
-        <v>31</v>
+        <v>374</v>
       </c>
       <c r="C243" t="s">
-        <v>32</v>
+        <v>377</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>26</v>
+        <v>378</v>
       </c>
       <c r="B244" t="s">
-        <v>33</v>
+        <v>379</v>
       </c>
       <c r="C244" t="s">
-        <v>34</v>
+        <v>380</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>26</v>
+        <v>378</v>
       </c>
       <c r="B245" t="s">
-        <v>33</v>
+        <v>379</v>
       </c>
       <c r="C245" t="s">
-        <v>35</v>
+        <v>381</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>26</v>
+        <v>378</v>
       </c>
       <c r="B246" t="s">
-        <v>33</v>
+        <v>382</v>
       </c>
       <c r="C246" t="s">
-        <v>461</v>
+        <v>383</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>26</v>
+        <v>378</v>
       </c>
       <c r="B247" t="s">
-        <v>313</v>
+        <v>384</v>
       </c>
       <c r="C247" t="s">
-        <v>314</v>
+        <v>385</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>52</v>
+        <v>378</v>
       </c>
       <c r="B248" t="s">
-        <v>53</v>
+        <v>384</v>
       </c>
       <c r="C248" t="s">
-        <v>54</v>
+        <v>386</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>52</v>
+        <v>378</v>
       </c>
       <c r="B249" t="s">
-        <v>53</v>
+        <v>384</v>
       </c>
       <c r="C249" t="s">
-        <v>55</v>
+        <v>387</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>56</v>
+        <v>378</v>
       </c>
       <c r="B250" t="s">
-        <v>57</v>
+        <v>388</v>
       </c>
       <c r="C250" t="s">
-        <v>58</v>
+        <v>389</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>56</v>
+        <v>378</v>
       </c>
       <c r="B251" t="s">
-        <v>462</v>
+        <v>390</v>
       </c>
       <c r="C251" t="s">
-        <v>463</v>
+        <v>391</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>56</v>
+        <v>378</v>
       </c>
       <c r="B252" t="s">
-        <v>310</v>
+        <v>392</v>
       </c>
       <c r="C252" t="s">
-        <v>311</v>
+        <v>393</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>56</v>
+        <v>378</v>
       </c>
       <c r="B253" t="s">
-        <v>310</v>
+        <v>394</v>
       </c>
       <c r="C253" t="s">
-        <v>312</v>
+        <v>395</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>307</v>
+        <v>396</v>
       </c>
       <c r="B254" t="s">
-        <v>308</v>
+        <v>397</v>
       </c>
       <c r="C254" t="s">
-        <v>309</v>
+        <v>397</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>26</v>
+        <v>396</v>
       </c>
       <c r="B255" t="s">
-        <v>226</v>
+        <v>398</v>
       </c>
       <c r="C255" t="s">
-        <v>227</v>
+        <v>399</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>26</v>
+        <v>396</v>
       </c>
       <c r="B256" t="s">
-        <v>36</v>
+        <v>400</v>
       </c>
       <c r="C256" t="s">
-        <v>37</v>
+        <v>401</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>548</v>
+        <v>396</v>
       </c>
       <c r="B257" t="s">
-        <v>464</v>
+        <v>402</v>
       </c>
       <c r="C257" t="s">
-        <v>465</v>
+        <v>403</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>548</v>
+        <v>396</v>
       </c>
       <c r="B258" t="s">
-        <v>466</v>
+        <v>404</v>
       </c>
       <c r="C258" t="s">
-        <v>467</v>
+        <v>405</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>548</v>
+        <v>396</v>
       </c>
       <c r="B259" t="s">
-        <v>468</v>
+        <v>404</v>
       </c>
       <c r="C259" t="s">
-        <v>469</v>
+        <v>406</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>548</v>
+        <v>396</v>
       </c>
       <c r="B260" t="s">
-        <v>470</v>
+        <v>407</v>
       </c>
       <c r="C260" t="s">
-        <v>471</v>
+        <v>408</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>548</v>
+        <v>396</v>
       </c>
       <c r="B261" t="s">
-        <v>472</v>
+        <v>409</v>
       </c>
       <c r="C261" t="s">
-        <v>473</v>
+        <v>410</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>548</v>
+        <v>396</v>
       </c>
       <c r="B262" t="s">
-        <v>474</v>
+        <v>409</v>
       </c>
       <c r="C262" t="s">
-        <v>475</v>
+        <v>411</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>549</v>
+        <v>396</v>
       </c>
       <c r="B263" t="s">
-        <v>476</v>
+        <v>409</v>
       </c>
       <c r="C263" t="s">
-        <v>477</v>
+        <v>412</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>549</v>
+        <v>396</v>
       </c>
       <c r="B264" t="s">
-        <v>478</v>
+        <v>413</v>
       </c>
       <c r="C264" t="s">
-        <v>479</v>
+        <v>414</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>549</v>
+        <v>396</v>
       </c>
       <c r="B265" t="s">
-        <v>480</v>
+        <v>415</v>
       </c>
       <c r="C265" t="s">
-        <v>481</v>
+        <v>416</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>224</v>
+        <v>396</v>
       </c>
       <c r="B266" t="s">
-        <v>221</v>
+        <v>417</v>
       </c>
       <c r="C266" t="s">
-        <v>222</v>
+        <v>418</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>224</v>
+        <v>396</v>
       </c>
       <c r="B267" t="s">
-        <v>221</v>
+        <v>419</v>
       </c>
       <c r="C267" t="s">
-        <v>223</v>
+        <v>420</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>138</v>
+        <v>396</v>
       </c>
       <c r="B268" t="s">
-        <v>139</v>
+        <v>421</v>
       </c>
       <c r="C268" t="s">
-        <v>225</v>
+        <v>422</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>138</v>
+        <v>396</v>
       </c>
       <c r="B269" t="s">
-        <v>139</v>
+        <v>423</v>
       </c>
       <c r="C269" t="s">
-        <v>140</v>
+        <v>424</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>550</v>
+        <v>396</v>
       </c>
       <c r="B270" t="s">
-        <v>482</v>
+        <v>425</v>
       </c>
       <c r="C270" t="s">
-        <v>483</v>
+        <v>426</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>550</v>
+        <v>396</v>
       </c>
       <c r="B271" t="s">
-        <v>482</v>
+        <v>427</v>
       </c>
       <c r="C271" t="s">
-        <v>484</v>
+        <v>428</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>551</v>
+        <v>396</v>
       </c>
       <c r="B272" t="s">
-        <v>485</v>
+        <v>429</v>
       </c>
       <c r="C272" t="s">
-        <v>486</v>
+        <v>430</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>551</v>
+        <v>396</v>
       </c>
       <c r="B273" t="s">
-        <v>487</v>
+        <v>429</v>
       </c>
       <c r="C273" t="s">
-        <v>488</v>
+        <v>431</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>552</v>
+        <v>396</v>
       </c>
       <c r="B274" t="s">
-        <v>489</v>
+        <v>429</v>
       </c>
       <c r="C274" t="s">
-        <v>490</v>
+        <v>432</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>38</v>
+        <v>396</v>
       </c>
       <c r="B275" t="s">
-        <v>41</v>
+        <v>433</v>
       </c>
       <c r="C275" t="s">
-        <v>41</v>
+        <v>434</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>59</v>
+        <v>396</v>
       </c>
       <c r="B276" t="s">
-        <v>70</v>
+        <v>435</v>
       </c>
       <c r="C276" t="s">
-        <v>70</v>
+        <v>436</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>144</v>
+        <v>396</v>
       </c>
       <c r="B277" t="s">
-        <v>144</v>
+        <v>437</v>
       </c>
       <c r="C277" t="s">
-        <v>144</v>
+        <v>438</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>553</v>
+        <v>439</v>
       </c>
       <c r="B278" t="s">
-        <v>491</v>
+        <v>440</v>
       </c>
       <c r="C278" t="s">
-        <v>492</v>
+        <v>440</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>553</v>
+        <v>439</v>
       </c>
       <c r="B279" t="s">
-        <v>493</v>
+        <v>441</v>
       </c>
       <c r="C279" t="s">
-        <v>494</v>
+        <v>440</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>553</v>
+        <v>439</v>
       </c>
       <c r="B280" t="s">
-        <v>495</v>
+        <v>281</v>
       </c>
       <c r="C280" t="s">
-        <v>496</v>
+        <v>442</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>554</v>
+        <v>439</v>
       </c>
       <c r="B281" t="s">
-        <v>497</v>
+        <v>281</v>
       </c>
       <c r="C281" t="s">
-        <v>498</v>
+        <v>443</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>555</v>
+        <v>439</v>
       </c>
       <c r="B282" t="s">
-        <v>499</v>
+        <v>281</v>
       </c>
       <c r="C282" t="s">
-        <v>500</v>
+        <v>444</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>555</v>
+        <v>439</v>
       </c>
       <c r="B283" t="s">
-        <v>501</v>
+        <v>445</v>
       </c>
       <c r="C283" t="s">
-        <v>502</v>
+        <v>444</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>503</v>
+        <v>439</v>
       </c>
       <c r="B284" t="s">
-        <v>503</v>
+        <v>445</v>
       </c>
       <c r="C284" t="s">
-        <v>503</v>
+        <v>446</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>504</v>
+        <v>439</v>
       </c>
       <c r="B285" t="s">
-        <v>504</v>
+        <v>285</v>
       </c>
       <c r="C285" t="s">
-        <v>504</v>
+        <v>447</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>561</v>
+        <v>439</v>
       </c>
       <c r="B286" t="s">
-        <v>559</v>
+        <v>285</v>
       </c>
       <c r="C286" t="s">
-        <v>560</v>
+        <v>448</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>572</v>
-      </c>
-      <c r="B287" s="8" t="s">
-        <v>563</v>
-      </c>
-      <c r="C287" s="8" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288" t="s">
-        <v>573</v>
-      </c>
-      <c r="B288" s="8" t="s">
-        <v>565</v>
-      </c>
-      <c r="C288" s="8" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
-        <v>574</v>
-      </c>
-      <c r="B289" s="8" t="s">
-        <v>567</v>
-      </c>
-      <c r="C289" s="8" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
-        <v>575</v>
-      </c>
-      <c r="B290" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="C290" s="8" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
-        <v>575</v>
-      </c>
-      <c r="B291" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="C291" s="8" t="s">
-        <v>571</v>
+        <v>439</v>
+      </c>
+      <c r="B287" t="s">
+        <v>289</v>
+      </c>
+      <c r="C287" t="s">
+        <v>449</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:X286" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:C2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C177:C1048576 C149:C175 C1:C147">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/预测分析.xlsx
+++ b/预测分析.xlsx
@@ -1,34 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forecast\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forecast\预测分析\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE35E5B-AFC9-4B5C-86D6-1A32F9A184B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEEA6CD-22B1-4AC8-BFB0-C34F165F1055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="864" yWindow="804" windowWidth="17280" windowHeight="10044" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$C$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$X$286</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="576">
   <si>
     <t>晶圆</t>
   </si>
@@ -42,66 +51,21 @@
     <t>STC9D03E</t>
   </si>
   <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>2100-A-2100</t>
-  </si>
-  <si>
-    <t>2100HBL</t>
-  </si>
-  <si>
-    <t>NR.2100HBL-2100</t>
-  </si>
-  <si>
-    <t>2100S</t>
-  </si>
-  <si>
-    <t>2100S-2100</t>
-  </si>
-  <si>
-    <t>PSTC9D03E</t>
-  </si>
-  <si>
     <t>PSTC9D03E-4</t>
   </si>
   <si>
-    <t>SC4643SA-A</t>
-  </si>
-  <si>
-    <t>SC4643SA-A-4643</t>
-  </si>
-  <si>
     <t>SC4643SA-BK-Q</t>
   </si>
   <si>
     <t>SC4643SA-Q-DE-40HK-2100</t>
   </si>
   <si>
-    <t>SC4643VB</t>
-  </si>
-  <si>
-    <t>NR.SC4643VB-A-4643</t>
-  </si>
-  <si>
-    <t>SC4643VB-A-4643</t>
-  </si>
-  <si>
     <t>SC4643VB-2.5S</t>
   </si>
   <si>
     <t>SC4643VB-A-4643-2.5S</t>
   </si>
   <si>
-    <t>SC4643VB-A</t>
-  </si>
-  <si>
-    <t>NR.SC4643VB-A-FFH-L43</t>
-  </si>
-  <si>
-    <t>SC4643VB-A-FFH-L43</t>
-  </si>
-  <si>
     <t>SC4643VB-BK-Q</t>
   </si>
   <si>
@@ -111,27 +75,12 @@
     <t>SC4643VB-Q-DE-40CK-4643</t>
   </si>
   <si>
-    <t>SC4643VB-G</t>
-  </si>
-  <si>
-    <t>SC4643VB-G(STC9D03E)-4643</t>
-  </si>
-  <si>
     <t>SC4643VB-G-BK-Q</t>
   </si>
   <si>
     <t>SC4643VB-G-Q-DE-40CK-4643</t>
   </si>
   <si>
-    <t>SC4643VB-P</t>
-  </si>
-  <si>
-    <t>NR.SC4643VB-P(STC9D03E)-4643</t>
-  </si>
-  <si>
-    <t>SC4643VB-P(STC9D03E)-4643</t>
-  </si>
-  <si>
     <t>SC4643VB-P-2.5S</t>
   </si>
   <si>
@@ -144,12 +93,6 @@
     <t>SC4643VB-P-Q-DE-40CR-4643</t>
   </si>
   <si>
-    <t>SC4643VB-S</t>
-  </si>
-  <si>
-    <t>SC4643VB-S(STC9D03E)-4643</t>
-  </si>
-  <si>
     <t>SC4643VB-S-BK-Q</t>
   </si>
   <si>
@@ -177,36 +120,12 @@
     <t>STC9A001I</t>
   </si>
   <si>
-    <t>PSTC9A001I-1</t>
-  </si>
-  <si>
-    <t>SC9641TS-P</t>
-  </si>
-  <si>
-    <t>NR.SC9641TS-P-I(STC9A001I)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9641TS-P-I(STC9A001I)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9641TS-P-I（STC9A001I)-41CPA</t>
-  </si>
-  <si>
     <t>SC9641TS-P-BK</t>
   </si>
   <si>
     <t>SC9641TS-P-AI-10AK-41CPA</t>
   </si>
   <si>
-    <t>SC9641TS-PC</t>
-  </si>
-  <si>
-    <t>NR.SC9641TS-PC(STC9A001I)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9641TS-PC(STC9A001I)-41CPA</t>
-  </si>
-  <si>
     <t>SC9641TS-PC-BK-Q</t>
   </si>
   <si>
@@ -219,1184 +138,1750 @@
     <t>SC9641TS-PC-Q-AI-10LR-9641PC</t>
   </si>
   <si>
-    <t>SC9641TS-PC-Q-AI-10AR-9641PC</t>
-  </si>
-  <si>
     <t>SC9641TS-P-TR</t>
   </si>
   <si>
     <t>SC9641TS-P-AI-10AR-G1630</t>
   </si>
   <si>
+    <t>SC9641TS-P-AI-10AR-41CPA</t>
+  </si>
+  <si>
+    <t>SC9648TS-TR</t>
+  </si>
+  <si>
+    <t>SC9648TS-AI-10AR-9648</t>
+  </si>
+  <si>
+    <t>STC4011B</t>
+  </si>
+  <si>
+    <t>SC4011SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC4011SO-N-CB-90NR-49E</t>
+  </si>
+  <si>
+    <t>STC4011B-DS</t>
+  </si>
+  <si>
+    <t>STC9D01C</t>
+  </si>
+  <si>
+    <t>SC4688DC-TR-Q</t>
+  </si>
+  <si>
+    <t>SC4688DC-Q-DC-40CR-4688</t>
+  </si>
+  <si>
+    <t>SC4688SA-BK-Q</t>
+  </si>
+  <si>
+    <t>SC4688SA-Q-DC-40CK-4688</t>
+  </si>
+  <si>
+    <t>SC4688SA-Q-DC-40CK-888K</t>
+  </si>
+  <si>
+    <t>SC4688DC-TR</t>
+  </si>
+  <si>
+    <t>SC4688DC-DC-40AR-2425</t>
+  </si>
+  <si>
+    <t>SC1645A1-BK</t>
+  </si>
+  <si>
+    <t>SC1645B1-BK</t>
+  </si>
+  <si>
+    <t>STC9910BN</t>
+  </si>
+  <si>
+    <t>SC9641TS-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9641TS-Q-CB-10LR-9641</t>
+  </si>
+  <si>
+    <t>SC9641TS-362-Q-CB-10LR-9641</t>
+  </si>
+  <si>
+    <t>STC9A001H</t>
+  </si>
+  <si>
+    <t>SC9642TS-EC-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9642TS-EC-Q-AH-4XLR-9642</t>
+  </si>
+  <si>
+    <t>STC4011E</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-A-TR</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-A-CE-90NR-4015</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-4015</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-512</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-515</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-CY19</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-G01M</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-QX11</t>
+  </si>
+  <si>
+    <t>SC4015SO-N-CE-90NR-NM</t>
+  </si>
+  <si>
+    <t>STC4011E-DS</t>
+  </si>
+  <si>
+    <t>STC9906P</t>
+  </si>
+  <si>
+    <t>SC2442SO-N-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2442SO-N-Q-CP-10CR-2442</t>
+  </si>
+  <si>
+    <t>SC2442SO-N-Q-CP-10CR-2662</t>
+  </si>
+  <si>
+    <t>SC2442SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2442SO-N-CP-10CR-2442</t>
+  </si>
+  <si>
+    <t>STC1898AD</t>
+  </si>
+  <si>
+    <t>PSTC1898AD-0</t>
+  </si>
+  <si>
+    <t>PSTC1898AD</t>
+  </si>
+  <si>
+    <t>SC1245A1</t>
+  </si>
+  <si>
+    <t>SC1245A1-41F</t>
+  </si>
+  <si>
+    <t>SC1245B1</t>
+  </si>
+  <si>
+    <t>SC1245B1-41F</t>
+  </si>
+  <si>
+    <t>SC1245B1-613HA</t>
+  </si>
+  <si>
+    <t>SC1245SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC1245SO-N-CD-00NR-1245</t>
+  </si>
+  <si>
+    <t>SC1245A3-BK</t>
+  </si>
+  <si>
+    <t>SC1245A3-CD-00CK-41F</t>
+  </si>
+  <si>
+    <t>SC1245S2-BK</t>
+  </si>
+  <si>
+    <t>SC1245S2-CD-00AK-41HL</t>
+  </si>
+  <si>
+    <t>STC9D04C</t>
+  </si>
+  <si>
+    <t>PSTC9D04C</t>
+  </si>
+  <si>
+    <t>SC60220SS-TB</t>
+  </si>
+  <si>
+    <t>SC60220SS-DC-00CB-60220</t>
+  </si>
+  <si>
+    <t>SC60221</t>
+  </si>
+  <si>
+    <t>NP.SC60221-60221</t>
+  </si>
+  <si>
+    <t>SC60221-D-100</t>
+  </si>
+  <si>
+    <t>SC60221-D-256</t>
+  </si>
+  <si>
+    <t>SC60221-D-360</t>
+  </si>
+  <si>
+    <t>SC60221-D-400</t>
+  </si>
+  <si>
+    <t>SC60221-D-50</t>
+  </si>
+  <si>
+    <t>SC60221-D-64</t>
+  </si>
+  <si>
+    <t>SC60221-U-256-976</t>
+  </si>
+  <si>
+    <t>SC60221-U-P1-256</t>
+  </si>
+  <si>
+    <t>SC60221-U-P1-256-244-mai</t>
+  </si>
+  <si>
+    <t>SC60224-D-1000</t>
+  </si>
+  <si>
+    <t>SC60224-D-1024</t>
+  </si>
+  <si>
+    <t>SC60224-D-1024-976-BSD-01</t>
+  </si>
+  <si>
+    <t>SC60224-D-1024-Z1</t>
+  </si>
+  <si>
+    <t>SC60224-D-16</t>
+  </si>
+  <si>
+    <t>SC60224-D-200</t>
+  </si>
+  <si>
+    <t>SC60224-D-500</t>
+  </si>
+  <si>
+    <t>SC60224-D-600</t>
+  </si>
+  <si>
+    <t>SC60224-U-P1-1024</t>
+  </si>
+  <si>
+    <t>SC60224-U-P4-1024</t>
+  </si>
+  <si>
+    <t>SC60228DC-TR</t>
+  </si>
+  <si>
+    <t>SC60228DC-DC-00AR-60228</t>
+  </si>
+  <si>
+    <t>SC60228DC-DC-00AR-NM</t>
+  </si>
+  <si>
+    <t>STC2899AI</t>
+  </si>
+  <si>
+    <t>S41F1</t>
+  </si>
+  <si>
+    <t>S41F1-41F</t>
+  </si>
+  <si>
+    <t>S41F1-S41H</t>
+  </si>
+  <si>
+    <t>S41H</t>
+  </si>
+  <si>
+    <t>S41H-S41H</t>
+  </si>
+  <si>
+    <t>S41H-A2</t>
+  </si>
+  <si>
+    <t>SC1645A1-AI-00HK-4601H</t>
+  </si>
+  <si>
+    <t>SC1645S1-BK</t>
+  </si>
+  <si>
+    <t>SC1645S1-AI-00AK-4601H</t>
+  </si>
+  <si>
+    <t>SC1845F1-BK</t>
+  </si>
+  <si>
+    <t>SC1845F1-AI-00HK-41F</t>
+  </si>
+  <si>
+    <t>SC1845F1-AI-00HK-S41H</t>
+  </si>
+  <si>
+    <t>SC1845S1-BK</t>
+  </si>
+  <si>
+    <t>SC1845S1-AI-00AK-S41H</t>
+  </si>
+  <si>
+    <t>SC1645B2-BK</t>
+  </si>
+  <si>
+    <t>SC1645B2-AI-0EHK-4601</t>
+  </si>
+  <si>
+    <t>SC1645B1-AI-00HK-4601</t>
+  </si>
+  <si>
+    <t>SC2448SO-TR-Q</t>
+  </si>
+  <si>
+    <t>FD1014A</t>
+  </si>
+  <si>
+    <t>SD2276VB-BK</t>
+  </si>
+  <si>
+    <t>SD2276VB-CA-90AK-276</t>
+  </si>
+  <si>
+    <t>STC9905E</t>
+  </si>
+  <si>
+    <t>SC9632VB-BK</t>
+  </si>
+  <si>
+    <t>SC9632VB-CE-00CK-9632</t>
+  </si>
+  <si>
+    <t>STC9902J</t>
+  </si>
+  <si>
+    <t>PSTC9902J</t>
+  </si>
+  <si>
+    <t>SC2402SO-N</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-Ag0.8-2402</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-CJ-90NR-2402</t>
+  </si>
+  <si>
+    <t>SC2402UA-BK</t>
+  </si>
+  <si>
+    <t>NM.SC2402UA-CJ-00AK</t>
+  </si>
+  <si>
+    <t>STC11102B</t>
+  </si>
+  <si>
+    <t>SC2442SO-N-Q-DB-60CR-2442</t>
+  </si>
+  <si>
+    <t>SC2442SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2442SO-Q-DB-60CR-2442</t>
+  </si>
+  <si>
+    <t>SC2442UA-BK-Q</t>
+  </si>
+  <si>
+    <t>SC2442UA-Q-DB-60AK-2442</t>
+  </si>
+  <si>
+    <t>SC2498UA-N-BK-Q</t>
+  </si>
+  <si>
+    <t>SC2943A2-BK</t>
+  </si>
+  <si>
+    <t>SC2943A2-Q-DB-4XHK-S41H</t>
+  </si>
+  <si>
+    <t>SC2498CUA-N-BK-Q</t>
+  </si>
+  <si>
+    <t>STC1898AI</t>
+  </si>
+  <si>
+    <t>PSTC1898AI</t>
+  </si>
+  <si>
+    <t>SC1134SO-N-TR-Q</t>
+  </si>
+  <si>
+    <t>SC1134SO-N-Q-CI-00LR-1134</t>
+  </si>
+  <si>
+    <t>SC1134UA-BK</t>
+  </si>
+  <si>
+    <t>SC1134UA-CI-00AK-1134</t>
+  </si>
+  <si>
+    <t>SC1134UA-CI-00AK-43F</t>
+  </si>
+  <si>
+    <t>SC1134UA-CI-00AK-44E</t>
+  </si>
+  <si>
+    <t>SC1134UA-CI-00AK-44L</t>
+  </si>
+  <si>
+    <t>SC1134BU-TR</t>
+  </si>
+  <si>
+    <t>SC1134BU-CI-00CR-1134</t>
+  </si>
+  <si>
+    <t>STC9910E</t>
+  </si>
+  <si>
+    <t>SC9625VB-BK</t>
+  </si>
+  <si>
+    <t>SC9625VB-CE-00CK-9625L</t>
+  </si>
+  <si>
+    <t>STC9901AF</t>
+  </si>
+  <si>
+    <t>PSTC9901AF</t>
+  </si>
+  <si>
+    <t>SC9314UA-BK</t>
+  </si>
+  <si>
+    <t>SC9314UA-CF-0XAK-2414</t>
+  </si>
+  <si>
+    <t>SC9314UA-CF-0XAK-94M</t>
+  </si>
+  <si>
+    <t>SC9314UA-CF-0XAK-17CA</t>
+  </si>
+  <si>
+    <t>STC9906J</t>
+  </si>
+  <si>
+    <t>SC2462UA-BK</t>
+  </si>
+  <si>
+    <t>SC2462UA-CJ-10AK-2462</t>
+  </si>
+  <si>
+    <t>SC2462UA-CJ-10AK-6472</t>
+  </si>
+  <si>
+    <t>SC2464SO-TR</t>
+  </si>
+  <si>
+    <t>SC2464SO-CJ-10CR-2464</t>
+  </si>
+  <si>
+    <t>STC9906I</t>
+  </si>
+  <si>
+    <t>PSTC9906I</t>
+  </si>
+  <si>
+    <t>SC2430UA-BK</t>
+  </si>
+  <si>
+    <t>SC2430UA-CI-10AK-2430</t>
+  </si>
+  <si>
+    <t>SC2434UA-BK</t>
+  </si>
+  <si>
+    <t>SC2434SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2434SO-N-CI-10CR-2434</t>
+  </si>
+  <si>
+    <t>SC2432SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2432SO-N-CI-10CR-2432</t>
+  </si>
+  <si>
+    <t>SC2438UA-BK</t>
+  </si>
+  <si>
+    <t>SC2438UA-CI-10AK-2438</t>
+  </si>
+  <si>
+    <t>STC9G002A</t>
+  </si>
+  <si>
+    <t>PSTC9G002A-0</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-GA-00NR-2402</t>
+  </si>
+  <si>
+    <t>预测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出货</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>订单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4643SA-S-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4643SA-S-Q-DE-40HR-2100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9625VB-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM.SC9625VB-CE-00CK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM.SC1134UA-CI-00AK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM.SC2402UA-GB-00AK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402UA-CJ-90AK-2402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402UA-GB-00AK-177</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402UA-GB-0XAK-U18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402UA-GB-0XAK-2402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402UA-GB-00AK-6501</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9G002B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD211VB-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD211VB-CA-90AK-KH211</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD211VB-CA-90AK-211</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FD1016A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD2276VB-CA-90AK-KH276</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9648TS-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9648TS-AI-10AK-9648</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9314UA-CF-0XAK-9201L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9314UA-CF-0XAK-9209</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM.SC9314UA-CF-0XAK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9314UA-Q-CF-0XAK-94M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9314UA-BK-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC60226SS-TB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM.SC60226SS-DC-00CB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1245UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1245UA-CD-0XHX-41F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2464UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2464UA-CJ-10AK-2464</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2462SO-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2462SO-Q-CJ-10CR-2462</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2448UA-N-BK-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC11102B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2448SO-Q-DB-60CR-2448</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2443UA-BK-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2443UA-Q-DB-60AK-2443</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2443SO-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2443SO-Q-DB-60CR-2443</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2442UA-BK-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2442UA-Q-CP-10AK-2442</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9906P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2442SO-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2442SO-CR-10CR-2442</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9906R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2438SO-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2434UA-CI-10AK-2434</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2438SO-CM-10CR-2438</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2438SO-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9906M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436UA-CI-10AK-2436</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436UA-CI-10AK-6210</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436SO-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436SO-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436SO-Q-CM-10CR-2436</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2436SO-CM-10CR-2436</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2434SO-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2434SO-CM-10CR-2434</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432UA-CI-10AK-2432</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432UA-CI-10AK-6232</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-N-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-N-Q-CI-10CR-2432</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-Q-CM-10AR-NM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-Q-CM-10AR-2432</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2432SO-CM-10CR-2432</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134B1-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134B1-CI-00HK-43F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9633VB-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9634VB-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9633VB-CF-00CK-9633</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9634VB-CG-00CK-9634</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9634VB-CG-00CK-SZ48</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9625VB-BK-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9625VB-Q-CE-4XCK-9625L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9625VB-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9625VB-Q-CE-4XCR-9625L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2448UA-N-Q-DB-60AK-2448</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2438SO-Q-CM-10CR-2438</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645A2-AE-00HK-601HL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645A2-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1134UA-CI-00AK-3144</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1245A1-61HA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S41H-A2-S41H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645A1-AI-00HK-65HA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645A1-AI-00HK-1466</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4643VB-S-TR-Q</t>
+  </si>
+  <si>
+    <t>SC4643VB-S-Q-DE-40CR-4643</t>
+  </si>
+  <si>
+    <t>STC9D06F</t>
+  </si>
+  <si>
+    <t>SC4645VB-BK</t>
+  </si>
+  <si>
+    <t>SC4645VB-DF-00CK-4645</t>
+  </si>
+  <si>
+    <t>STC13103B</t>
+  </si>
+  <si>
+    <t>SC4665VB-BK</t>
+  </si>
+  <si>
+    <t>SC4665VB-HB-33CK-4665</t>
+  </si>
+  <si>
+    <t>SC2402SO-N-CJ-90NR-NM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9A001G</t>
+  </si>
+  <si>
+    <t>SC9642TS-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9642TS-Q-AG-4XHR-9642</t>
+  </si>
+  <si>
+    <t>SC9642TS-E-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9642TS-E-Q-AH-4XLR-9642</t>
+  </si>
+  <si>
+    <t>SC9642TS-E362-Q-AH-4XLR-9642</t>
+  </si>
+  <si>
+    <t>SC9641TS-P-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9641TS-P-Q-AI-10LR-9641P</t>
+  </si>
+  <si>
+    <t>SC9625VB-CE-00CR-9625L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC9625VB-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4688DC-Q-DC-40AR-6388</t>
+  </si>
+  <si>
+    <t>SC2462SO-TR</t>
+  </si>
+  <si>
+    <t>SC2462SO-CJ-10CR-2462</t>
+  </si>
+  <si>
+    <t>SC2498CUA-N-Q-DB-60CK-2498C</t>
+  </si>
+  <si>
+    <t>SC2498UA-N-Q-DB-60CK-2498</t>
+  </si>
+  <si>
+    <t>STC9910F</t>
+  </si>
+  <si>
+    <t>SC9621VB-BK</t>
+  </si>
+  <si>
+    <t>SC9621VB-CF-00CK-9621</t>
+  </si>
+  <si>
+    <t>SC9621VB-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9621VB-Q-CN-4XCR-9621</t>
+  </si>
+  <si>
+    <t>STC2899AE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645B1-AI-00HK-615HA</t>
+  </si>
+  <si>
+    <t>PSTC9G001C</t>
+  </si>
+  <si>
+    <t>SC1002N1-BK</t>
+  </si>
+  <si>
+    <t>SC1002N1-CL-00HK-42N</t>
+  </si>
+  <si>
+    <t>SC1002S1-BK</t>
+  </si>
+  <si>
+    <t>SC1002S1-CG-00AK-41F</t>
+  </si>
+  <si>
+    <t>SC1133UA-BK</t>
+  </si>
+  <si>
+    <t>SC1133UA-CJ-00AK-1133</t>
+  </si>
+  <si>
+    <t>SC1134BU-CI-00AR-1134</t>
+  </si>
+  <si>
+    <t>SC1134SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC1134SO-N-CF-00LR-1134</t>
+  </si>
+  <si>
+    <t>SC1138SO-N-TR-Q</t>
+  </si>
+  <si>
+    <t>SC1138SO-N-Q-CC-00LR-1138</t>
+  </si>
+  <si>
+    <t>SC1445A1</t>
+  </si>
+  <si>
+    <t>SC1445A1-41F</t>
+  </si>
+  <si>
+    <t>SC1645A1-AI-00HK-615HA</t>
+  </si>
+  <si>
+    <t>SC1645B1-AE-00HK-4601</t>
+  </si>
+  <si>
+    <t>SC1845S1-AI-00AK-41F</t>
+  </si>
+  <si>
+    <t>SC1945A1-BK</t>
+  </si>
+  <si>
+    <t>SC1945A1-AJ-00HK-N13</t>
+  </si>
+  <si>
+    <t>SC1945B1-BK</t>
+  </si>
+  <si>
+    <t>SC1945B1-AJ-00HK-N603</t>
+  </si>
+  <si>
+    <t>SC2063SO-TR</t>
+  </si>
+  <si>
+    <t>SC2063SO-GC-00NR-2063</t>
+  </si>
+  <si>
+    <t>SC2063UA-BK</t>
+  </si>
+  <si>
+    <t>SC2063UA-GC-00AK-2063</t>
+  </si>
+  <si>
+    <t>SC2064SO-TR</t>
+  </si>
+  <si>
+    <t>SC2064SO-GC-00NR-2064</t>
+  </si>
+  <si>
+    <t>SC2202SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2202SO-N-CE-00NR-2202</t>
+  </si>
+  <si>
+    <t>SC2242SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2242SO-Q-CH-10CR-2242</t>
+  </si>
+  <si>
+    <t>SC2242SO-Q-CH-10CR-2642</t>
+  </si>
+  <si>
+    <t>SC2242UA-BK</t>
+  </si>
+  <si>
+    <t>SC2242UA-CE-00AK-2242</t>
+  </si>
+  <si>
+    <t>SC2242UA-BK-Q</t>
+  </si>
+  <si>
+    <t>SC2242UA-Q-CH-10AK-2242</t>
+  </si>
+  <si>
+    <t>SC2413SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2413SO-N-CD-00LR-44E</t>
+  </si>
+  <si>
+    <t>SC2432SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2432SO-Q-CM-10CR-2432</t>
+  </si>
+  <si>
+    <t>SC243XSO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC243XSO-Q-CM-10CR-243X</t>
+  </si>
+  <si>
+    <t>SC2442UA-BK</t>
+  </si>
+  <si>
+    <t>SC2442UA-CP-10AK-2442</t>
+  </si>
+  <si>
+    <t>SC2442UA-CP-10AK-U18</t>
+  </si>
+  <si>
+    <t>SC2448SO-Q-DB-40CR-2448</t>
+  </si>
+  <si>
+    <t>SC2452SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2452SO-Q-DD-60AR-2452</t>
+  </si>
+  <si>
+    <t>SC2455SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2455SO-Q-CK-10CR-2455</t>
+  </si>
+  <si>
+    <t>SC2466SO-TR</t>
+  </si>
+  <si>
+    <t>SC2466SO-CO-10CR-2466</t>
+  </si>
+  <si>
+    <t>SC2498CUA-N-Q-DB-60AK-2498C</t>
+  </si>
+  <si>
+    <t>SC2498SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2498SO-Q-DB-60CR-2498</t>
+  </si>
+  <si>
+    <t>SC2498TSO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2498TSO-Q-CC-10CR-2498T</t>
+  </si>
+  <si>
+    <t>SC2498UA-N-Q-DB-60AK-2498</t>
+  </si>
+  <si>
+    <t>SC2527S6-AB-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2527S6-AB-Q-DA-40CR-2527</t>
+  </si>
+  <si>
+    <t>SC2527S6-SD-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2527S6-SD-Q-DA-40CR-2527</t>
+  </si>
+  <si>
+    <t>SC2546VB-AB-BK</t>
+  </si>
+  <si>
+    <t>SC2546VB-AB-DA-00AK-2546</t>
+  </si>
+  <si>
+    <t>SC25791CUA-A-Q</t>
+  </si>
+  <si>
+    <t>SC25791CUA-A(STC11210G-Q)-25791C</t>
+  </si>
+  <si>
+    <t>SC25791SE-TR-Q</t>
+  </si>
+  <si>
+    <t>SC25791SE-Q-CG-40CR-5791</t>
+  </si>
+  <si>
+    <t>SC25891CUA-A-Q</t>
+  </si>
+  <si>
+    <t>SC25891CUA-A-Q(STC11210G-Q)-25891C</t>
+  </si>
+  <si>
+    <t>SC25891SE-TR-Q</t>
+  </si>
+  <si>
+    <t>SC25891SE-Q-CG-40CR-5891</t>
+  </si>
+  <si>
+    <t>SC2943SO-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2943SO-Q-DB-60CR-2943</t>
+  </si>
+  <si>
+    <t>SC2948S2-BK</t>
+  </si>
+  <si>
+    <t>SC2948S2-DB-60AK-61H</t>
+  </si>
+  <si>
+    <t>SC2968S1-N-BK</t>
+  </si>
+  <si>
+    <t>SC2968S1-N-DC-4XAK-S21C</t>
+  </si>
+  <si>
+    <t>SC4001SE-TR</t>
+  </si>
+  <si>
+    <t>SC4001SE-CB-90CR-4001</t>
+  </si>
+  <si>
+    <t>SC4002BU-TR</t>
+  </si>
+  <si>
+    <t>SC4002BU-CA-00CR-4002</t>
+  </si>
+  <si>
+    <t>SC4002SO</t>
+  </si>
+  <si>
+    <t>SC4002SO(STC4000AA)-4002</t>
+  </si>
+  <si>
+    <t>SC4002SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC4002SO-N-CA-00NR-4002</t>
+  </si>
+  <si>
+    <t>SC4002UA-BK</t>
+  </si>
+  <si>
+    <t>SC4002UA-CA-00AK-4002</t>
+  </si>
+  <si>
+    <t>SC4002UA-CA-00AK-95A</t>
+  </si>
+  <si>
+    <t>SC4011DN</t>
+  </si>
+  <si>
+    <t>SC4011DN-4011</t>
+  </si>
+  <si>
+    <t>SC4019S7-BK</t>
+  </si>
+  <si>
+    <t>SC4019S7-CC-90AK-49E</t>
+  </si>
+  <si>
+    <t>SC4101DN</t>
+  </si>
+  <si>
+    <t>SC4101DN(STC11201B1)-4101</t>
+  </si>
+  <si>
+    <t>SC4103DN</t>
+  </si>
+  <si>
+    <t>SC4103DN(STC11201B1)-4103</t>
+  </si>
+  <si>
+    <t>SC4251D3-TR</t>
+  </si>
+  <si>
+    <t>SC4251D3-GA-00FR-4251</t>
+  </si>
+  <si>
+    <t>SC4391S6-TR</t>
+  </si>
+  <si>
+    <t>SC4391S6-GB-00NR-4391</t>
+  </si>
+  <si>
+    <t>SC4616BU</t>
+  </si>
+  <si>
+    <t>SC4616BU-4616</t>
+  </si>
+  <si>
+    <t>SC4616UA-10.2NF-BK</t>
+  </si>
+  <si>
+    <t>SC4616UA-10.2NF-CD-90AK-4616</t>
+  </si>
+  <si>
+    <t>SC4643SA-Q-DE-40CK-4643</t>
+  </si>
+  <si>
+    <t>SC4689SA-BK-Q</t>
+  </si>
+  <si>
+    <t>SC4689SA-Q-DF-40CK-4689</t>
+  </si>
+  <si>
+    <t>SC4703SO-TR</t>
+  </si>
+  <si>
+    <t>SC4703SO-GB-00NR-4703</t>
+  </si>
+  <si>
+    <t>SC4823S6-TR</t>
+  </si>
+  <si>
+    <t>SC4823S6-GA-00NR-4823</t>
+  </si>
+  <si>
+    <t>SC4923SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC4923SO-N-CD-00NR-4923</t>
+  </si>
+  <si>
+    <t>SC60104</t>
+  </si>
+  <si>
+    <t>NM.SC60104</t>
+  </si>
+  <si>
+    <t>SC60226SS-TB</t>
+  </si>
+  <si>
+    <t>NA.SC60226SS-DC</t>
+  </si>
+  <si>
+    <t>SC60370</t>
+  </si>
+  <si>
+    <t>SC60370(STC9D05C)-60370</t>
+  </si>
+  <si>
+    <t>SC69401DC-SPI-TR-Q</t>
+  </si>
+  <si>
+    <t>SC69401DC-SPI-Q-HD-4XCR-69401</t>
+  </si>
+  <si>
+    <t>SC69401DC-TR</t>
+  </si>
+  <si>
+    <t>SC69401DC-HD-4XCR-69401</t>
+  </si>
+  <si>
+    <t>SC69401DC-TR-Q</t>
+  </si>
+  <si>
+    <t>SC69401DC-Q-HD-4XCR-69401</t>
+  </si>
+  <si>
+    <t>SC69401HS-SPI-TR-Q</t>
+  </si>
+  <si>
+    <t>SC69401HS-SPI-Q-HD-4XTR-69401</t>
+  </si>
+  <si>
+    <t>SC69401HS-TR</t>
+  </si>
+  <si>
+    <t>SC69401HS-HD-4XTR-69401</t>
+  </si>
+  <si>
+    <t>SC69401HS-TR-Q</t>
+  </si>
+  <si>
+    <t>SC69401HS-Q-HD-4XTR-69401</t>
+  </si>
+  <si>
     <t>SC9641TS-P-AI-10LR-41CPA</t>
   </si>
   <si>
-    <t>SC9641TS-P-AI-10AR-41CPA</t>
-  </si>
-  <si>
-    <t>SC9648TS-P</t>
-  </si>
-  <si>
-    <t>NR.SC9648TS-P(STC9A001I)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9648TS-P(STC9A001I)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9648TS-P(STC9A001I)-9648</t>
-  </si>
-  <si>
-    <t>SC9648TS-P-9A001I(STC9A001I)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9648TS-P-9A001I(STC9A001I)-9648</t>
-  </si>
-  <si>
-    <t>SC9648TS-TR</t>
-  </si>
-  <si>
-    <t>SC9648TS-AI-10AR-9648</t>
-  </si>
-  <si>
-    <t>STC4011B</t>
-  </si>
-  <si>
-    <t>SC4011SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC4011SO-N-CB-90NR-49E</t>
-  </si>
-  <si>
-    <t>STC4011B-DS</t>
-  </si>
-  <si>
-    <t>STC9D01C</t>
-  </si>
-  <si>
-    <t>SC4688DA</t>
-  </si>
-  <si>
-    <t>SC4688DA(STC9D01C)-4688D</t>
-  </si>
-  <si>
-    <t>SC4688DC</t>
-  </si>
-  <si>
-    <t>SC4688DC-4688</t>
-  </si>
-  <si>
-    <t>SC4688DC-TR-Q</t>
-  </si>
-  <si>
-    <t>SC4688DC-Q-DC-40AR-4688</t>
-  </si>
-  <si>
-    <t>SC4688DC-Q-DC-40CR-6388</t>
-  </si>
-  <si>
-    <t>SC4688DC-Q-DC-40CR-4688</t>
-  </si>
-  <si>
-    <t>SC4688DC-DU-Q-DC-40AR-2425</t>
-  </si>
-  <si>
-    <t>SC4688SA</t>
-  </si>
-  <si>
-    <t>NP.SC4688SA-4688</t>
-  </si>
-  <si>
-    <t>NP.SC4688SA-888K</t>
-  </si>
-  <si>
-    <t>SC4688SA-A</t>
-  </si>
-  <si>
-    <t>SC4688SA-A(STC9D01C)-4688</t>
-  </si>
-  <si>
-    <t>SC4688SA-BK-Q</t>
-  </si>
-  <si>
-    <t>SC4688SA-Q-DC-40CK-4688</t>
-  </si>
-  <si>
-    <t>SC4688SA-Q-DC-40CK-888K</t>
-  </si>
-  <si>
-    <t>SC4695DC</t>
-  </si>
-  <si>
-    <t>SC4695DC-2425</t>
-  </si>
-  <si>
-    <t>SC4688DC-TR</t>
-  </si>
-  <si>
-    <t>SC4688DC-DC-40AR-2425</t>
+    <t>SC9642TS-E-TR</t>
+  </si>
+  <si>
+    <t>SC9642TS-E-AH-4XLR-9642</t>
+  </si>
+  <si>
+    <t>SC9675IM-HRF00-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9675IM-HRF00-Q-AB-4XAR-9675</t>
+  </si>
+  <si>
+    <t>SC9675IM-HRF11-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9675IM-HRF11-Q-AB-4XAR-9675</t>
+  </si>
+  <si>
+    <t>SC9675IM-LRF00-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9675IM-LRF00-Q-AB-4XAR-9675</t>
+  </si>
+  <si>
+    <t>SC9675IM-LRF01-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9675IM-LRF01-Q-AB-4XAR-9675</t>
+  </si>
+  <si>
+    <t>SC9675IM-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9675IM-Q-AB-4XAR-9675</t>
+  </si>
+  <si>
+    <t>SC9675T3-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9675T3-Q-AB-4XAR-9675</t>
+  </si>
+  <si>
+    <t>SC9683TS-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9683TS-Q-DB-4XAR-9683</t>
+  </si>
+  <si>
+    <t>SC9684TS-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9684TS-Q-DB-4XAR-9684</t>
+  </si>
+  <si>
+    <t>SC9685TS-RP120-TR-Q</t>
+  </si>
+  <si>
+    <t>SC9685TS-RP120-Q-DB-46AR-96852</t>
+  </si>
+  <si>
+    <t>SD477VB-BK</t>
+  </si>
+  <si>
+    <t>SD477VB-GC-90AK-477S</t>
+  </si>
+  <si>
+    <t>SD477VB-GC-90AK-KH477</t>
+  </si>
+  <si>
+    <t>SL002147DC-TR</t>
+  </si>
+  <si>
+    <t>SL002147DC-GB-00AR-2147</t>
+  </si>
+  <si>
+    <t>SL54123ADC-TR</t>
+  </si>
+  <si>
+    <t>SL54123ADC-GB-00AR-54123A</t>
+  </si>
+  <si>
+    <t>SPD3242</t>
+  </si>
+  <si>
+    <t>SPD3242(STC35301)</t>
+  </si>
+  <si>
+    <t>VE1430Q1BA3R5</t>
+  </si>
+  <si>
+    <t>TRVE1430Q1BA3R5(VA2201D)-1430Q</t>
+  </si>
+  <si>
+    <t>VE1430Q1CA3R33</t>
+  </si>
+  <si>
+    <t>TRVE1430Q1CA3R33(VA2201D)-1430Q</t>
+  </si>
+  <si>
+    <t>VE1430Q1CA3R5</t>
+  </si>
+  <si>
+    <t>TRVE1430Q1CA3R5-1430Q</t>
+  </si>
+  <si>
+    <t>VE1430Q1VA3RADJ</t>
+  </si>
+  <si>
+    <t>TRVE1430Q1VA3RADJ(VA2201E)-1430Q</t>
+  </si>
+  <si>
+    <t>VE8602A5R</t>
+  </si>
+  <si>
+    <t>TRVE8602A5R-8602</t>
+  </si>
+  <si>
+    <t>VE8602AKR</t>
+  </si>
+  <si>
+    <t>VE8602AKR-8602</t>
+  </si>
+  <si>
+    <t>ZH6338</t>
+  </si>
+  <si>
+    <t>ZH6531</t>
+  </si>
+  <si>
+    <t>SC3100VB-BK-Q</t>
+  </si>
+  <si>
+    <t>SC3100VB-DG-00CK-3100</t>
+  </si>
+  <si>
+    <t>SC2033SO-N-TR</t>
+  </si>
+  <si>
+    <t>SC2033SO-N-GD-00NR-2033</t>
+  </si>
+  <si>
+    <t>SC919SO-N-TR-Q</t>
+  </si>
+  <si>
+    <t>SC919SO-N-Q-CD-90CR-919H</t>
+  </si>
+  <si>
+    <t>SC1645B1-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645A1-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9G001C</t>
+  </si>
+  <si>
+    <t>STC9G001C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC1002AG</t>
+  </si>
+  <si>
+    <t>STC11102C</t>
+  </si>
+  <si>
+    <t>STC1002AL</t>
+  </si>
+  <si>
+    <t>STC1898AJ</t>
+  </si>
+  <si>
+    <t>STC1002AF</t>
+  </si>
+  <si>
+    <t>STC1898AC</t>
+  </si>
+  <si>
+    <t>STC2899AB</t>
   </si>
   <si>
     <t>STC2899AE</t>
   </si>
   <si>
-    <t>SC1645A1</t>
-  </si>
-  <si>
-    <t>SC1645A1-1466</t>
-  </si>
-  <si>
-    <t>SC1645A1-4601H</t>
-  </si>
-  <si>
-    <t>SC1645A1-61H</t>
-  </si>
-  <si>
-    <t>SC1645A1-65HA</t>
-  </si>
-  <si>
-    <t>SC1645A1-BK</t>
-  </si>
-  <si>
-    <t>SC1645A1-AE-00HK-4601H</t>
-  </si>
-  <si>
-    <t>SC1645A1-AE-00HK-65HA</t>
-  </si>
-  <si>
-    <t>SC1645A1-AE-00HK-1466</t>
-  </si>
-  <si>
-    <t>SC1645A1R12</t>
-  </si>
-  <si>
-    <t>SC1645A1R12-4601H</t>
-  </si>
-  <si>
-    <t>SC1645A2</t>
-  </si>
-  <si>
-    <t>SC1645A2-601HL</t>
-  </si>
-  <si>
-    <t>SC1645B1</t>
-  </si>
-  <si>
-    <t>SC1645B1-4601</t>
-  </si>
-  <si>
-    <t>SC1645B1-615HA</t>
-  </si>
-  <si>
-    <t>SC1645B1-65HA</t>
-  </si>
-  <si>
-    <t>SC1645B1-BK</t>
-  </si>
-  <si>
-    <t>SC1645B1-AE-00HK-615HA</t>
-  </si>
-  <si>
-    <t>STC9910BN</t>
-  </si>
-  <si>
-    <t>SC9641TS</t>
-  </si>
-  <si>
-    <t>SC9641TS-9641</t>
-  </si>
-  <si>
-    <t>SC9641TS-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9641TS-Q-CB-10LR-9641</t>
-  </si>
-  <si>
-    <t>SC9641TS-362-Q-CB-10LR-9641</t>
-  </si>
-  <si>
-    <t>STC9A001G</t>
-  </si>
-  <si>
-    <t>SC9642TS</t>
-  </si>
-  <si>
-    <t>SC9642TS(9A001G)-9642</t>
-  </si>
-  <si>
-    <t>STC9A001H</t>
-  </si>
-  <si>
-    <t>SC9642TS-E</t>
-  </si>
-  <si>
-    <t>SC9642TS(9A001H)-E-9642</t>
-  </si>
-  <si>
-    <t>SC9642TS(STC9A001H)-E-9642</t>
-  </si>
-  <si>
-    <t>SC9642TS(STC9A001H)-E-白板</t>
-  </si>
-  <si>
-    <t>SC9642TS-EC</t>
-  </si>
-  <si>
-    <t>SC9642TS(STC9A001H)-EC-9642</t>
-  </si>
-  <si>
-    <t>SC9642TS-EC-TR-Q</t>
-  </si>
-  <si>
-    <t>SC9642TS-EC-Q-AH-4XLR-9642</t>
-  </si>
-  <si>
-    <t>SC9642TS-EC-Q-AH-4XAR-9642</t>
-  </si>
-  <si>
-    <t>STC4011E</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-A-TR</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-A-CE-90NR-4015</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-4015</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-512</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-515</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-CY19</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-G01M</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-QX11</t>
-  </si>
-  <si>
-    <t>SC4015SO-N-CE-90NR-NM</t>
-  </si>
-  <si>
-    <t>STC4011E-DS</t>
-  </si>
-  <si>
-    <t>STC9906P</t>
-  </si>
-  <si>
-    <t>SC2442SE</t>
-  </si>
-  <si>
-    <t>SC2442SE-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-N</t>
-  </si>
-  <si>
-    <t>SC2442SO-N(STC9906P)-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-Q-CP-10CR-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-Q-CP-10CR-2662</t>
-  </si>
-  <si>
-    <t>SC2442UA</t>
-  </si>
-  <si>
-    <t>SC2442UA-2442</t>
-  </si>
-  <si>
-    <t>SC2442UA-U18</t>
-  </si>
-  <si>
-    <t>SC2662SO-N</t>
-  </si>
-  <si>
-    <t>SC2662SO-N-2662</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-CP-10CR-2442</t>
-  </si>
-  <si>
-    <t>STC1898AD</t>
-  </si>
-  <si>
-    <t>PSTC1898AD-0</t>
-  </si>
-  <si>
-    <t>PSTC1898AD</t>
-  </si>
-  <si>
-    <t>SC1245A1</t>
-  </si>
-  <si>
-    <t>SC1245A1-41F</t>
-  </si>
-  <si>
-    <t>SC1245A1-61HA</t>
-  </si>
-  <si>
-    <t>SC1245B1</t>
-  </si>
-  <si>
-    <t>SC1245B1-41F</t>
-  </si>
-  <si>
-    <t>SC1245B1-613HA</t>
-  </si>
-  <si>
-    <t>SC1245SO-N</t>
-  </si>
-  <si>
-    <t>SC1245SO-N-1245</t>
-  </si>
-  <si>
-    <t>SC1245SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC1245SO-N-CD-00NR-1245</t>
-  </si>
-  <si>
-    <t>SC1245UA</t>
-  </si>
-  <si>
-    <t>SC1245A3(STC1898AD)-41F</t>
-  </si>
-  <si>
-    <t>SC1245UA-1245</t>
-  </si>
-  <si>
-    <t>SC1245UA-41F</t>
-  </si>
-  <si>
-    <t>SC41HL-A2</t>
-  </si>
-  <si>
-    <t>SC41HL-A2-41HL</t>
-  </si>
-  <si>
-    <t>SC1245A3-BK</t>
-  </si>
-  <si>
-    <t>SC1245A3-CD-00CK-41F</t>
-  </si>
-  <si>
-    <t>SC1245S2-BK</t>
-  </si>
-  <si>
-    <t>SC1245S2-CD-00AK-41HL</t>
-  </si>
-  <si>
-    <t>STC9D04C</t>
-  </si>
-  <si>
-    <t>PSTC9D04C</t>
-  </si>
-  <si>
-    <t>SC60220</t>
-  </si>
-  <si>
-    <t>NP.SC60220-60220</t>
-  </si>
-  <si>
-    <t>SC60220-60220</t>
-  </si>
-  <si>
-    <t>SC60220SS-TB</t>
-  </si>
-  <si>
-    <t>SC60220SS-DC-00CB-60220</t>
-  </si>
-  <si>
-    <t>SC60221</t>
-  </si>
-  <si>
-    <t>NP.SC60221-60221</t>
-  </si>
-  <si>
-    <t>SC60221-D-100</t>
-  </si>
-  <si>
-    <t>SC60221-D-256</t>
-  </si>
-  <si>
-    <t>SC60221-D-360</t>
-  </si>
-  <si>
-    <t>SC60221-D-400</t>
-  </si>
-  <si>
-    <t>SC60221-D-50</t>
-  </si>
-  <si>
-    <t>SC60221-D-64</t>
-  </si>
-  <si>
-    <t>SC60221-U-256-976</t>
-  </si>
-  <si>
-    <t>SC60221-U-P1-256</t>
-  </si>
-  <si>
-    <t>SC60221-U-P1-256-244-mai</t>
-  </si>
-  <si>
-    <t>SC60224-D-1000</t>
-  </si>
-  <si>
-    <t>SC60224-D-1024</t>
-  </si>
-  <si>
-    <t>SC60224-D-1024-976-BSD-01</t>
-  </si>
-  <si>
-    <t>SC60224-D-1024-Z1</t>
-  </si>
-  <si>
-    <t>SC60224-D-16</t>
-  </si>
-  <si>
-    <t>SC60224-D-200</t>
-  </si>
-  <si>
-    <t>SC60224-D-500</t>
-  </si>
-  <si>
-    <t>SC60224-D-600</t>
-  </si>
-  <si>
-    <t>SC60224-U-P1-1024</t>
-  </si>
-  <si>
-    <t>SC60224-U-P4-1024</t>
-  </si>
-  <si>
-    <t>SC60226</t>
-  </si>
-  <si>
-    <t>NA.SC60226</t>
-  </si>
-  <si>
-    <t>NM.SC60226</t>
-  </si>
-  <si>
-    <t>NP.SC60226-60226</t>
-  </si>
-  <si>
-    <t>SC60228DC</t>
-  </si>
-  <si>
-    <t>NR.SC60228DC-60228</t>
-  </si>
-  <si>
-    <t>SC60228DC-60228</t>
-  </si>
-  <si>
-    <t>SC60228DC-白板</t>
-  </si>
-  <si>
-    <t>SC60228DC-TR</t>
-  </si>
-  <si>
-    <t>SC60228DC-DC-00AR-60228</t>
-  </si>
-  <si>
-    <t>SC60228DC-DC-00AR-NM</t>
-  </si>
-  <si>
-    <t>STC2899AI</t>
-  </si>
-  <si>
-    <t>S41F1</t>
-  </si>
-  <si>
-    <t>S41F1-41F</t>
-  </si>
-  <si>
-    <t>S41F1-S41H</t>
-  </si>
-  <si>
-    <t>S41H</t>
-  </si>
-  <si>
-    <t>S41H-S41H</t>
-  </si>
-  <si>
-    <t>S41H-A2</t>
-  </si>
-  <si>
-    <t>S41H-A2-S41H</t>
-  </si>
-  <si>
-    <t>SC1645A1(STC2899AI)-65HA</t>
-  </si>
-  <si>
-    <t>SC1645A1-AI-00HK-4601H</t>
-  </si>
-  <si>
-    <t>SC1645A2(STC2899AI)-601HL</t>
-  </si>
-  <si>
-    <t>SC1645B1(STC2899AI)-4601</t>
-  </si>
-  <si>
-    <t>SC1645B2</t>
-  </si>
-  <si>
-    <t>SC1645B2(STC2899AI)-4601</t>
-  </si>
-  <si>
-    <t>SC1645S1-BK</t>
-  </si>
-  <si>
-    <t>SC1645S1-AI-00AK-4601H</t>
-  </si>
-  <si>
-    <t>SC1845F1-BK</t>
-  </si>
-  <si>
-    <t>SC1845F1-AI-00HK-41F</t>
-  </si>
-  <si>
-    <t>SC1845F1-AI-00HK-S41H</t>
-  </si>
-  <si>
-    <t>SC1845S1-BK</t>
-  </si>
-  <si>
-    <t>SC1845S1-AI-00AK-S41H</t>
-  </si>
-  <si>
-    <t>SC1645B2-BK</t>
-  </si>
-  <si>
-    <t>SC1645B2-AI-0EHK-4601</t>
-  </si>
-  <si>
-    <t>SC1645B1-AI-00HK-4601</t>
-  </si>
-  <si>
-    <t>STC9906S</t>
-  </si>
-  <si>
-    <t>SC2448SO</t>
-  </si>
-  <si>
-    <t>SC2448SO-2448</t>
-  </si>
-  <si>
-    <t>SC2448UA-N</t>
-  </si>
-  <si>
-    <t>NM.SC2448UA-N</t>
-  </si>
-  <si>
-    <t>SC2448UA-N-2448</t>
-  </si>
-  <si>
-    <t>SC2448SO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2448SO-Q-CS-10CR-2448</t>
-  </si>
-  <si>
-    <t>FD1014A</t>
-  </si>
-  <si>
-    <t>KH276</t>
-  </si>
-  <si>
-    <t>SD2276(FD1014A)-KH276</t>
-  </si>
-  <si>
-    <t>PFD1014A</t>
-  </si>
-  <si>
-    <t>PFD1014A-0</t>
-  </si>
-  <si>
-    <t>SD2276</t>
-  </si>
-  <si>
-    <t>SD2276(FD1014A)-276</t>
-  </si>
-  <si>
-    <t>SD2276VB-BK</t>
-  </si>
-  <si>
-    <t>SD2276VB-CA-00AK-276</t>
-  </si>
-  <si>
-    <t>SD2276VB-CA-00AK-KH276</t>
-  </si>
-  <si>
-    <t>SD2276VB-CA-90AK-276</t>
-  </si>
-  <si>
-    <t>STC9905E</t>
-  </si>
-  <si>
-    <t>SC9632VB</t>
-  </si>
-  <si>
-    <t>SC9632VB-9632</t>
-  </si>
-  <si>
-    <t>SC9632VB-BK</t>
-  </si>
-  <si>
-    <t>SC9632VB-CE-00CK-9632</t>
-  </si>
-  <si>
-    <t>STC9902J</t>
-  </si>
-  <si>
-    <t>PSTC9902J</t>
-  </si>
-  <si>
-    <t>SC2402SO-N</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-2402</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-Ag0.8-2402</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-C(STC9902J)-2448</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-CJ-00NR-2402</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-CJ-0XLR-6571</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-CJ-90NR-2402</t>
-  </si>
-  <si>
-    <t>SC2402UA</t>
-  </si>
-  <si>
-    <t>NM.SC2402UA</t>
-  </si>
-  <si>
-    <t>SC2402UA-2402</t>
-  </si>
-  <si>
-    <t>SC2402UA-U18</t>
-  </si>
-  <si>
-    <t>SC2402UA-BK</t>
-  </si>
-  <si>
-    <t>NM.SC2402UA-CJ-00AK</t>
-  </si>
-  <si>
-    <t>STC11102B</t>
-  </si>
-  <si>
-    <t>SC2442SO</t>
-  </si>
-  <si>
-    <t>NM.SC2442SO(2943N1-1)</t>
-  </si>
-  <si>
-    <t>SC2442SO(2943N1-1)-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-N(2943S1)-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-N-Q-DB-60CR-2442</t>
-  </si>
-  <si>
-    <t>SC2442SO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2442SO-Q-DB-60CR-2442</t>
-  </si>
-  <si>
-    <t>SC2442UA(2943S1-1)-2442</t>
-  </si>
-  <si>
-    <t>SC2442UA(2943S1-1)-U18</t>
-  </si>
-  <si>
-    <t>SC2442UA-BK-Q</t>
-  </si>
-  <si>
-    <t>SC2442UA-Q-DB-60AK-2442</t>
-  </si>
-  <si>
-    <t>SC2448SO(2948N1)-2448</t>
-  </si>
-  <si>
-    <t>SC2448SO(2948N1-1)-2448</t>
-  </si>
-  <si>
-    <t>SC2498UA-N-BK-Q</t>
-  </si>
-  <si>
-    <t>SC2498UA-N-Q-DB-60CK-2498</t>
-  </si>
-  <si>
-    <t>SC2498UA-N-Q-DB-60AK-2498</t>
-  </si>
-  <si>
-    <t>SC2943A2-BK</t>
-  </si>
-  <si>
-    <t>SC2943A2-Q-DB-4XHK-S41H</t>
-  </si>
-  <si>
-    <t>SC2498CUA-N-BK-Q</t>
-  </si>
-  <si>
-    <t>SC2498CUA-N-Q-DB-60AK-2498C</t>
-  </si>
-  <si>
-    <t>STC9906W</t>
-  </si>
-  <si>
-    <t>SC2443UA</t>
-  </si>
-  <si>
-    <t>SC2443UA-W(STC9906W)-2443</t>
-  </si>
-  <si>
-    <t>STC1898AI</t>
-  </si>
-  <si>
-    <t>PSTC1898AI</t>
-  </si>
-  <si>
-    <t>SC1134B1</t>
-  </si>
-  <si>
-    <t>SC1134B1-43F</t>
-  </si>
-  <si>
-    <t>SC1134BU</t>
-  </si>
-  <si>
-    <t>SC1134BU-1134</t>
-  </si>
-  <si>
-    <t>SC1134S2-BK</t>
-  </si>
-  <si>
-    <t>NM.SC1134S2-CI-00AK</t>
-  </si>
-  <si>
-    <t>SC1134S2-CI-00AK-44E</t>
-  </si>
-  <si>
-    <t>SC1134SO-N</t>
-  </si>
-  <si>
-    <t>SC1134SO-N-1134</t>
-  </si>
-  <si>
-    <t>SC1134SO-N-TR-Q</t>
-  </si>
-  <si>
-    <t>SC1134SO-N-Q-CI-00LR-1134</t>
-  </si>
-  <si>
-    <t>SC1134UA</t>
-  </si>
-  <si>
-    <t>NM.SC1134UA</t>
-  </si>
-  <si>
-    <t>SC1134UA-04E</t>
-  </si>
-  <si>
-    <t>SC1134UA-1134</t>
-  </si>
-  <si>
-    <t>SC1134UA-3144</t>
-  </si>
-  <si>
-    <t>SC1134UA-43F</t>
-  </si>
-  <si>
-    <t>SC1134UA-44E</t>
-  </si>
-  <si>
-    <t>SC1134UA-44L</t>
-  </si>
-  <si>
-    <t>SC1134UA-BK</t>
-  </si>
-  <si>
-    <t>SC1134UA-CI-00AK-1134</t>
-  </si>
-  <si>
-    <t>SC1134UA-CI-00AK-43F</t>
-  </si>
-  <si>
-    <t>SC1134UA-CI-00AK-44E</t>
-  </si>
-  <si>
-    <t>SC1134UA-CI-00AK-44L</t>
-  </si>
-  <si>
-    <t>SC1134BU-TR</t>
-  </si>
-  <si>
-    <t>SC1134BU-CI-00AR-1134</t>
-  </si>
-  <si>
-    <t>SC1134BU-CI-00CR-1134</t>
-  </si>
-  <si>
-    <t>SC1134S1-BK</t>
-  </si>
-  <si>
-    <t>SC1134S1-CI-00AK-43F</t>
-  </si>
-  <si>
-    <t>STC9910E</t>
-  </si>
-  <si>
-    <t>SC9625VB</t>
-  </si>
-  <si>
-    <t>NM.SC9625VB(STC9910E)</t>
-  </si>
-  <si>
-    <t>NR.SC9625VB(STC9910E)-9625</t>
-  </si>
-  <si>
-    <t>SC9625VB-L</t>
-  </si>
-  <si>
-    <t>NR.SC9625VB-L-9625L</t>
-  </si>
-  <si>
-    <t>SC9625VB-L-9625L</t>
-  </si>
-  <si>
-    <t>SC9625VB-BK</t>
-  </si>
-  <si>
-    <t>SC9625VB-CE-00CK-9625L</t>
-  </si>
-  <si>
-    <t>STC9A001F</t>
-  </si>
-  <si>
-    <t>AS04</t>
-  </si>
-  <si>
-    <t>SC9641TS-P(9A001F)-AS04</t>
-  </si>
-  <si>
-    <t>NR.SC9641TS-P（9A001F)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9641TS-P(9A001F)-41CPA</t>
-  </si>
-  <si>
-    <t>SC9641TS-P（9A001F)-41CPA</t>
-  </si>
-  <si>
-    <t>STC9901AF</t>
-  </si>
-  <si>
-    <t>PSTC9901AF</t>
-  </si>
-  <si>
-    <t>SC9314UA</t>
-  </si>
-  <si>
-    <t>NM.SC9314UA</t>
-  </si>
-  <si>
-    <t>SC9314UA-17CA</t>
-  </si>
-  <si>
-    <t>SC9314UA-2414</t>
-  </si>
-  <si>
-    <t>SC9314UA-9201L</t>
-  </si>
-  <si>
-    <t>SC9314UA-9209</t>
-  </si>
-  <si>
-    <t>SC9314UA-94M</t>
-  </si>
-  <si>
-    <t>SC9314UA-BK</t>
-  </si>
-  <si>
-    <t>SC9314UA-CF-0XAK-2414</t>
-  </si>
-  <si>
-    <t>SC9314UA-CF-0XAK-94M</t>
-  </si>
-  <si>
-    <t>SC9314UA-CF-0XAK-17CA</t>
-  </si>
-  <si>
-    <t>STC9906J</t>
-  </si>
-  <si>
-    <t>SC2462SO</t>
-  </si>
-  <si>
-    <t>SC2462SO-2462</t>
-  </si>
-  <si>
-    <t>SC2462SO-6472</t>
-  </si>
-  <si>
-    <t>SC2462UA</t>
-  </si>
-  <si>
-    <t>SC2462UA-2462</t>
-  </si>
-  <si>
-    <t>SC2462UA-BK</t>
-  </si>
-  <si>
-    <t>SC2462UA-CJ-10AK-2462</t>
-  </si>
-  <si>
-    <t>SC2462UA-CJ-10AK-6472</t>
-  </si>
-  <si>
-    <t>SC2462UA-CJ-10HK-6472</t>
-  </si>
-  <si>
-    <t>SC2464SO</t>
-  </si>
-  <si>
-    <t>SC2464SO-2464</t>
-  </si>
-  <si>
-    <t>SC2464UA</t>
-  </si>
-  <si>
-    <t>SC2464UA-2464</t>
-  </si>
-  <si>
-    <t>SC2462SO-TR-Q</t>
-  </si>
-  <si>
-    <t>SC2462SO-Q-CJ-10CR-2462</t>
-  </si>
-  <si>
-    <t>SC2464SO-TR</t>
-  </si>
-  <si>
-    <t>SC2464SO-CJ-10CR-2464</t>
-  </si>
-  <si>
-    <t>STC9906I</t>
-  </si>
-  <si>
-    <t>PSTC9906I</t>
-  </si>
-  <si>
-    <t>SC2430UA</t>
-  </si>
-  <si>
-    <t>SC2430UA-2430</t>
-  </si>
-  <si>
-    <t>SC2430UA-BK</t>
-  </si>
-  <si>
-    <t>SC2430UA-CI-10AK-2430</t>
-  </si>
-  <si>
-    <t>SC2432HUA</t>
-  </si>
-  <si>
-    <t>SC2432HUA-2432H</t>
-  </si>
-  <si>
-    <t>SC2432SO</t>
-  </si>
-  <si>
-    <t>NM.SC2432SO</t>
-  </si>
-  <si>
-    <t>SC2432SO-2432</t>
-  </si>
-  <si>
-    <t>SC2432SO-N</t>
-  </si>
-  <si>
-    <t>SC2432SO-N-2432</t>
-  </si>
-  <si>
-    <t>SC2432UA</t>
-  </si>
-  <si>
-    <t>SC2432UA-1101</t>
-  </si>
-  <si>
-    <t>SC2432UA-2432</t>
-  </si>
-  <si>
-    <t>SC2432UA-6232</t>
-  </si>
-  <si>
-    <t>SC2434SO</t>
-  </si>
-  <si>
-    <t>SC2434SO-2434</t>
-  </si>
-  <si>
-    <t>SC2434SO-N</t>
-  </si>
-  <si>
-    <t>SC2434SO-N-2434</t>
-  </si>
-  <si>
-    <t>SC2434UA</t>
-  </si>
-  <si>
-    <t>SC2434UA-2434</t>
-  </si>
-  <si>
-    <t>SC2434UA-BK</t>
-  </si>
-  <si>
-    <t>SC2434UA-CI-10AK-2434</t>
-  </si>
-  <si>
-    <t>SC2436SO</t>
-  </si>
-  <si>
-    <t>SC2436SO-2436</t>
-  </si>
-  <si>
-    <t>SC2436UA</t>
-  </si>
-  <si>
-    <t>SC2436UA-2436</t>
-  </si>
-  <si>
-    <t>SC2438SO</t>
-  </si>
-  <si>
-    <t>SC2438SO-2438</t>
-  </si>
-  <si>
-    <t>SC2438UA</t>
-  </si>
-  <si>
-    <t>SC2438UA-2438</t>
-  </si>
-  <si>
-    <t>SC243XUA</t>
-  </si>
-  <si>
-    <t>NA.SC243XUA</t>
-  </si>
-  <si>
-    <t>NF.SC243XUA-243X</t>
-  </si>
-  <si>
-    <t>SC243XUA-243X</t>
-  </si>
-  <si>
-    <t>SC2434SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC2434SO-N-CI-10CR-2434</t>
-  </si>
-  <si>
-    <t>SC2432SO-N-TR</t>
-  </si>
-  <si>
-    <t>SC2432SO-N-CI-10CR-2432</t>
-  </si>
-  <si>
-    <t>SC2438UA-BK</t>
-  </si>
-  <si>
-    <t>SC2438UA-CI-10AK-2438</t>
-  </si>
-  <si>
-    <t>STC9G002A</t>
-  </si>
-  <si>
-    <t>PSTC9G002A</t>
-  </si>
-  <si>
-    <t>PSTC9G002A-0</t>
-  </si>
-  <si>
-    <t>SC2402LSO-N-177</t>
-  </si>
-  <si>
-    <t>SC2402LSO-N-2402</t>
-  </si>
-  <si>
-    <t>SC2402SO-N（STC9G002A)-G-2402</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-G</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-G(STC9G002A)-177</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-GA-00LR-2402</t>
-  </si>
-  <si>
-    <t>SC2402SO-N-GA-00NR-2402</t>
-  </si>
-  <si>
-    <t>SC2402LUA-2402</t>
-  </si>
-  <si>
-    <t>预测</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>未交</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出货</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>订单</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
+    <t>STC2899AJ</t>
+  </si>
+  <si>
+    <t>STC9902E</t>
+  </si>
+  <si>
+    <t>STC9906H</t>
+  </si>
+  <si>
+    <t>STC9902D</t>
+  </si>
+  <si>
+    <t>STC9906M</t>
+  </si>
+  <si>
+    <t>STC11103D</t>
+  </si>
+  <si>
+    <t>STC9906K</t>
+  </si>
+  <si>
+    <t>STC9906O</t>
+  </si>
+  <si>
+    <t>STC11300C</t>
+  </si>
+  <si>
+    <t>STC11131A</t>
+  </si>
+  <si>
+    <t>STC11210G-Q</t>
+  </si>
+  <si>
+    <t>STC4001AB</t>
+  </si>
+  <si>
+    <t>STC4000AA</t>
+  </si>
+  <si>
+    <t>STC4011C</t>
+  </si>
+  <si>
+    <t>STC11201B1</t>
+  </si>
+  <si>
+    <t>STC11401A</t>
+  </si>
+  <si>
+    <t>STC11202B</t>
+  </si>
+  <si>
+    <t>STC9907D</t>
+  </si>
+  <si>
+    <t>STC9D01F</t>
+  </si>
+  <si>
+    <t>STC11205B</t>
+  </si>
+  <si>
+    <t>STC11205A_T</t>
+  </si>
+  <si>
+    <t>SC4009D</t>
+  </si>
+  <si>
+    <t>STC9D02C</t>
+  </si>
+  <si>
+    <t>STC9D05C</t>
+  </si>
+  <si>
+    <t>STC9H002DQ</t>
+  </si>
+  <si>
+    <t>STC9A002B</t>
+  </si>
+  <si>
+    <t>STC12100B</t>
+  </si>
+  <si>
+    <t>STC22304C</t>
+  </si>
+  <si>
+    <t>STC16100B</t>
+  </si>
+  <si>
+    <t>STC35301</t>
+  </si>
+  <si>
+    <t>VA2201D</t>
+  </si>
+  <si>
+    <t>VA2201E</t>
+  </si>
+  <si>
+    <t>V2302C</t>
+  </si>
+  <si>
+    <t>STC9D06G</t>
+  </si>
+  <si>
+    <t>STC9G001D</t>
+  </si>
+  <si>
+    <t>STC9913D</t>
+  </si>
+  <si>
+    <t>SC1945B1</t>
+  </si>
+  <si>
+    <t>SC1945B1(STC2899AJ)-N13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC2899AJ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2402SO-N-CJ-90NR-6571</t>
+  </si>
+  <si>
+    <t>SC1002N2W-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1002N2W-CL-00AK-N41F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1919UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1919UA-CD-90AK-919H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4001UA-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NM.SC4001UA-CB-90AK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYLM358DC-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYLM358DC-GC-90AR-LM358</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYLM358DC-GC-90AR-NM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC1002AL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9913D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC4001AB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9G005C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1404,7 +1889,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1418,6 +1903,20 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1446,7 +1945,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1454,20 +1953,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2 4 2 2" xfId="1" xr:uid="{9C7ED766-84C1-4343-B919-15B8593B06F8}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1743,7 +2285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X287"/>
+  <dimension ref="A1:X291"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
@@ -1753,207 +2295,207 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D1" s="3" t="s">
-        <v>450</v>
+        <v>202</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>453</v>
+        <v>205</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>452</v>
+        <v>204</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>450</v>
+        <v>202</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>451</v>
+        <v>203</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>452</v>
+        <v>204</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>450</v>
+        <v>202</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>451</v>
+        <v>203</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>452</v>
+        <v>204</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>450</v>
+        <v>202</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>451</v>
+        <v>203</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>452</v>
+        <v>204</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>450</v>
+        <v>202</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>451</v>
+        <v>203</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>452</v>
+        <v>204</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>451</v>
+        <v>203</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>450</v>
+        <v>202</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>452</v>
+        <v>204</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>450</v>
+        <v>202</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>451</v>
+        <v>203</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="5">
         <v>7</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="6">
         <v>7</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="7">
         <v>7</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="5">
         <v>8</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="6">
         <v>8</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="7">
         <v>8</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="5">
         <v>9</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="6">
         <v>9</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="7">
         <v>9</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="5">
         <v>10</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="6">
         <v>10</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="7">
         <v>10</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="5">
         <v>11</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="6">
         <v>11</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="7">
         <v>11</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="6">
         <v>12</v>
       </c>
-      <c r="T2" s="3">
+      <c r="T2" s="5">
         <v>12</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U2" s="7">
         <v>12</v>
       </c>
-      <c r="V2" s="3">
+      <c r="V2" s="5">
         <v>1</v>
       </c>
-      <c r="W2" s="1">
+      <c r="W2" s="6">
         <v>1</v>
       </c>
-      <c r="X2" s="2">
+      <c r="X2" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>177</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>189</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -1961,3076 +2503,3123 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>514</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>199</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>517</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>330</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>515</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>332</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>518</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>334</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>335</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>278</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>171</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>519</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>337</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>338</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>164</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
-        <v>45</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>166</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>211</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>520</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>339</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>235</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>521</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>341</v>
       </c>
       <c r="C40" t="s">
-        <v>67</v>
+        <v>342</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>296</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B43" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>512</v>
       </c>
       <c r="C44" t="s">
-        <v>72</v>
+        <v>343</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>327</v>
       </c>
       <c r="B45" t="s">
-        <v>68</v>
+        <v>292</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>328</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>522</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>511</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="C49" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="B51" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="C51" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="B52" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="B53" t="s">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="C53" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="B54" t="s">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="C54" t="s">
-        <v>89</v>
+        <v>345</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>80</v>
+        <v>523</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>346</v>
       </c>
       <c r="C55" t="s">
-        <v>91</v>
+        <v>347</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>80</v>
+        <v>523</v>
       </c>
       <c r="B56" t="s">
-        <v>90</v>
+        <v>348</v>
       </c>
       <c r="C56" t="s">
-        <v>92</v>
+        <v>349</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>557</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>507</v>
       </c>
       <c r="C57" t="s">
-        <v>94</v>
+        <v>508</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>80</v>
+        <v>513</v>
       </c>
       <c r="B58" t="s">
-        <v>95</v>
+        <v>350</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
+        <v>351</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>513</v>
       </c>
       <c r="B59" t="s">
-        <v>95</v>
+        <v>352</v>
       </c>
       <c r="C59" t="s">
-        <v>97</v>
+        <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>80</v>
+        <v>513</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
+        <v>354</v>
       </c>
       <c r="C60" t="s">
-        <v>99</v>
+        <v>355</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>524</v>
       </c>
       <c r="B61" t="s">
-        <v>100</v>
+        <v>356</v>
       </c>
       <c r="C61" t="s">
-        <v>101</v>
+        <v>357</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>102</v>
+        <v>525</v>
       </c>
       <c r="B62" t="s">
-        <v>103</v>
+        <v>358</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>359</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>102</v>
+        <v>525</v>
       </c>
       <c r="B63" t="s">
-        <v>103</v>
+        <v>358</v>
       </c>
       <c r="C63" t="s">
-        <v>105</v>
+        <v>360</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>524</v>
       </c>
       <c r="B64" t="s">
-        <v>103</v>
+        <v>361</v>
       </c>
       <c r="C64" t="s">
-        <v>106</v>
+        <v>362</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>525</v>
       </c>
       <c r="B65" t="s">
-        <v>103</v>
+        <v>363</v>
       </c>
       <c r="C65" t="s">
-        <v>107</v>
+        <v>364</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C66" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="B67" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="C67" t="s">
-        <v>110</v>
+        <v>201</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="C68" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="B69" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="C69" t="s">
-        <v>113</v>
+        <v>306</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="B70" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="C70" t="s">
-        <v>115</v>
+        <v>562</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>102</v>
+        <v>220</v>
       </c>
       <c r="B71" t="s">
-        <v>116</v>
+        <v>213</v>
       </c>
       <c r="C71" t="s">
-        <v>117</v>
+        <v>217</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>102</v>
+        <v>220</v>
       </c>
       <c r="B72" t="s">
-        <v>116</v>
+        <v>213</v>
       </c>
       <c r="C72" t="s">
-        <v>118</v>
+        <v>218</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>102</v>
+        <v>220</v>
       </c>
       <c r="B73" t="s">
-        <v>116</v>
+        <v>213</v>
       </c>
       <c r="C73" t="s">
-        <v>119</v>
+        <v>219</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>102</v>
+        <v>220</v>
       </c>
       <c r="B74" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="C74" t="s">
-        <v>121</v>
+        <v>216</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>122</v>
+        <v>220</v>
       </c>
       <c r="B75" t="s">
-        <v>123</v>
+        <v>213</v>
       </c>
       <c r="C75" t="s">
-        <v>124</v>
+        <v>214</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="B76" t="s">
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="C76" t="s">
-        <v>126</v>
+        <v>215</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="B77" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>128</v>
+        <v>526</v>
       </c>
       <c r="B78" t="s">
-        <v>129</v>
+        <v>365</v>
       </c>
       <c r="C78" t="s">
-        <v>130</v>
+        <v>366</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="B79" t="s">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="C79" t="s">
-        <v>133</v>
+        <v>191</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="B80" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="C80" t="s">
-        <v>134</v>
+        <v>196</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="B81" t="s">
-        <v>132</v>
+        <v>271</v>
       </c>
       <c r="C81" t="s">
-        <v>135</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>131</v>
+        <v>258</v>
       </c>
       <c r="B82" t="s">
-        <v>136</v>
+        <v>276</v>
       </c>
       <c r="C82" t="s">
-        <v>137</v>
+        <v>277</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>131</v>
+        <v>258</v>
       </c>
       <c r="B83" t="s">
-        <v>138</v>
+        <v>273</v>
       </c>
       <c r="C83" t="s">
-        <v>139</v>
+        <v>274</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>131</v>
+        <v>258</v>
       </c>
       <c r="B84" t="s">
-        <v>138</v>
+        <v>273</v>
       </c>
       <c r="C84" t="s">
-        <v>140</v>
+        <v>275</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>141</v>
+        <v>527</v>
       </c>
       <c r="B85" t="s">
-        <v>142</v>
+        <v>367</v>
       </c>
       <c r="C85" t="s">
-        <v>143</v>
+        <v>368</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="B86" t="s">
-        <v>144</v>
+        <v>268</v>
       </c>
       <c r="C86" t="s">
-        <v>145</v>
+        <v>270</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="B87" t="s">
-        <v>144</v>
+        <v>268</v>
       </c>
       <c r="C87" t="s">
-        <v>146</v>
+        <v>269</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="B88" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="C88" t="s">
-        <v>147</v>
+        <v>194</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>141</v>
+        <v>258</v>
       </c>
       <c r="B89" t="s">
-        <v>144</v>
+        <v>266</v>
       </c>
       <c r="C89" t="s">
-        <v>148</v>
+        <v>267</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="B90" t="s">
-        <v>144</v>
+        <v>192</v>
       </c>
       <c r="C90" t="s">
-        <v>149</v>
+        <v>255</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>141</v>
+        <v>258</v>
       </c>
       <c r="B91" t="s">
-        <v>144</v>
+        <v>262</v>
       </c>
       <c r="C91" t="s">
-        <v>150</v>
+        <v>265</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>141</v>
+        <v>258</v>
       </c>
       <c r="B92" t="s">
-        <v>144</v>
+        <v>263</v>
       </c>
       <c r="C92" t="s">
-        <v>151</v>
+        <v>264</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="B93" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="C93" t="s">
-        <v>152</v>
+        <v>261</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="B94" t="s">
-        <v>154</v>
+        <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>155</v>
+        <v>260</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>153</v>
+        <v>258</v>
       </c>
       <c r="B95" t="s">
-        <v>156</v>
+        <v>254</v>
       </c>
       <c r="C95" t="s">
-        <v>157</v>
+        <v>256</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>153</v>
+        <v>258</v>
       </c>
       <c r="B96" t="s">
-        <v>156</v>
+        <v>257</v>
       </c>
       <c r="C96" t="s">
-        <v>158</v>
+        <v>290</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="B97" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="C97" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>153</v>
+        <v>527</v>
       </c>
       <c r="B98" t="s">
-        <v>159</v>
+        <v>369</v>
       </c>
       <c r="C98" t="s">
-        <v>161</v>
+        <v>370</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
       <c r="B99" t="s">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="C99" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
       <c r="B100" t="s">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="C100" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
       <c r="B101" t="s">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="C101" t="s">
-        <v>166</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>152</v>
+      </c>
+      <c r="B102" t="s">
+        <v>72</v>
+      </c>
+      <c r="C102" t="s">
         <v>153</v>
-      </c>
-      <c r="B102" t="s">
-        <v>167</v>
-      </c>
-      <c r="C102" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>169</v>
+        <v>253</v>
       </c>
       <c r="B103" t="s">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="C103" t="s">
-        <v>171</v>
+        <v>252</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B104" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C104" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="B105" t="s">
-        <v>172</v>
+        <v>371</v>
       </c>
       <c r="C105" t="s">
-        <v>174</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="B106" t="s">
-        <v>175</v>
+        <v>371</v>
       </c>
       <c r="C106" t="s">
-        <v>176</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>169</v>
+        <v>250</v>
       </c>
       <c r="B107" t="s">
-        <v>175</v>
+        <v>248</v>
       </c>
       <c r="C107" t="s">
-        <v>177</v>
+        <v>249</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B108" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="C108" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>169</v>
+        <v>242</v>
       </c>
       <c r="B109" t="s">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="C109" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>169</v>
+        <v>242</v>
       </c>
       <c r="B110" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="C110" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>169</v>
+        <v>242</v>
       </c>
       <c r="B111" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="C111" t="s">
-        <v>184</v>
+        <v>243</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B112" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="C112" t="s">
-        <v>185</v>
+        <v>374</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>169</v>
+        <v>242</v>
       </c>
       <c r="B113" t="s">
-        <v>186</v>
+        <v>241</v>
       </c>
       <c r="C113" t="s">
-        <v>187</v>
+        <v>289</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>169</v>
+        <v>528</v>
       </c>
       <c r="B114" t="s">
-        <v>188</v>
+        <v>375</v>
       </c>
       <c r="C114" t="s">
-        <v>189</v>
+        <v>376</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>169</v>
+        <v>529</v>
       </c>
       <c r="B115" t="s">
-        <v>190</v>
+        <v>377</v>
       </c>
       <c r="C115" t="s">
-        <v>191</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B116" t="s">
-        <v>193</v>
+        <v>318</v>
       </c>
       <c r="C116" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B117" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="C117" t="s">
-        <v>195</v>
+        <v>240</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B118" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C118" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B119" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="C119" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B120" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="C120" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B121" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="C121" t="s">
-        <v>201</v>
+        <v>238</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>192</v>
+        <v>530</v>
       </c>
       <c r="B122" t="s">
-        <v>202</v>
+        <v>379</v>
       </c>
       <c r="C122" t="s">
-        <v>202</v>
+        <v>380</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="B123" t="s">
-        <v>203</v>
+        <v>161</v>
       </c>
       <c r="C123" t="s">
-        <v>203</v>
+        <v>320</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="B124" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="C124" t="s">
-        <v>204</v>
+        <v>381</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="B125" t="s">
-        <v>205</v>
+        <v>382</v>
       </c>
       <c r="C125" t="s">
-        <v>205</v>
+        <v>383</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>192</v>
+        <v>531</v>
       </c>
       <c r="B126" t="s">
-        <v>206</v>
+        <v>384</v>
       </c>
       <c r="C126" t="s">
-        <v>206</v>
+        <v>385</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="B127" t="s">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="C127" t="s">
-        <v>207</v>
+        <v>321</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="B128" t="s">
-        <v>208</v>
+        <v>158</v>
       </c>
       <c r="C128" t="s">
-        <v>208</v>
+        <v>386</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>192</v>
+        <v>532</v>
       </c>
       <c r="B129" t="s">
-        <v>209</v>
+        <v>387</v>
       </c>
       <c r="C129" t="s">
-        <v>209</v>
+        <v>388</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>192</v>
+        <v>532</v>
       </c>
       <c r="B130" t="s">
-        <v>210</v>
+        <v>389</v>
       </c>
       <c r="C130" t="s">
-        <v>210</v>
+        <v>390</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>192</v>
+        <v>532</v>
       </c>
       <c r="B131" t="s">
-        <v>211</v>
+        <v>391</v>
       </c>
       <c r="C131" t="s">
-        <v>211</v>
+        <v>392</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>192</v>
+        <v>533</v>
       </c>
       <c r="B132" t="s">
-        <v>212</v>
+        <v>393</v>
       </c>
       <c r="C132" t="s">
-        <v>212</v>
+        <v>394</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>192</v>
+        <v>533</v>
       </c>
       <c r="B133" t="s">
-        <v>213</v>
+        <v>395</v>
       </c>
       <c r="C133" t="s">
-        <v>213</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>192</v>
+        <v>533</v>
       </c>
       <c r="B134" t="s">
-        <v>214</v>
+        <v>397</v>
       </c>
       <c r="C134" t="s">
-        <v>214</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>192</v>
+        <v>533</v>
       </c>
       <c r="B135" t="s">
-        <v>215</v>
+        <v>399</v>
       </c>
       <c r="C135" t="s">
-        <v>215</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="B136" t="s">
-        <v>216</v>
+        <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>216</v>
+        <v>160</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="B137" t="s">
-        <v>217</v>
+        <v>401</v>
       </c>
       <c r="C137" t="s">
-        <v>217</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="B138" t="s">
-        <v>218</v>
+        <v>403</v>
       </c>
       <c r="C138" t="s">
-        <v>218</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>192</v>
+        <v>516</v>
       </c>
       <c r="B139" t="s">
-        <v>219</v>
+        <v>405</v>
       </c>
       <c r="C139" t="s">
-        <v>219</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>192</v>
+        <v>556</v>
       </c>
       <c r="B140" t="s">
-        <v>220</v>
+        <v>505</v>
       </c>
       <c r="C140" t="s">
-        <v>221</v>
+        <v>506</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>192</v>
+        <v>534</v>
       </c>
       <c r="B141" t="s">
-        <v>220</v>
+        <v>407</v>
       </c>
       <c r="C141" t="s">
-        <v>222</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>192</v>
+        <v>535</v>
       </c>
       <c r="B142" t="s">
-        <v>220</v>
+        <v>409</v>
       </c>
       <c r="C142" t="s">
-        <v>223</v>
+        <v>410</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>192</v>
+        <v>535</v>
       </c>
       <c r="B143" t="s">
-        <v>224</v>
+        <v>411</v>
       </c>
       <c r="C143" t="s">
-        <v>225</v>
+        <v>412</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>192</v>
+        <v>535</v>
       </c>
       <c r="B144" t="s">
-        <v>224</v>
+        <v>413</v>
       </c>
       <c r="C144" t="s">
-        <v>226</v>
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>192</v>
+        <v>535</v>
       </c>
       <c r="B145" t="s">
-        <v>224</v>
+        <v>415</v>
       </c>
       <c r="C145" t="s">
-        <v>227</v>
+        <v>416</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>192</v>
+        <v>535</v>
       </c>
       <c r="B146" t="s">
-        <v>228</v>
+        <v>415</v>
       </c>
       <c r="C146" t="s">
-        <v>229</v>
+        <v>417</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>192</v>
+        <v>38</v>
       </c>
       <c r="B147" t="s">
-        <v>228</v>
+        <v>418</v>
       </c>
       <c r="C147" t="s">
-        <v>230</v>
+        <v>419</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>231</v>
+        <v>38</v>
       </c>
       <c r="B148" t="s">
-        <v>232</v>
+        <v>39</v>
       </c>
       <c r="C148" t="s">
-        <v>233</v>
+        <v>40</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B149" t="s">
-        <v>232</v>
+        <v>60</v>
       </c>
       <c r="C149" t="s">
-        <v>234</v>
+        <v>61</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B150" t="s">
-        <v>235</v>
+        <v>62</v>
       </c>
       <c r="C150" t="s">
-        <v>236</v>
+        <v>68</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B151" t="s">
-        <v>237</v>
+        <v>62</v>
       </c>
       <c r="C151" t="s">
-        <v>238</v>
+        <v>69</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B152" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>239</v>
+        <v>67</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B153" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="C153" t="s">
-        <v>240</v>
+        <v>66</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B154" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="C154" t="s">
-        <v>241</v>
+        <v>65</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B155" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="C155" t="s">
-        <v>242</v>
+        <v>64</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="B156" t="s">
-        <v>243</v>
+        <v>62</v>
       </c>
       <c r="C156" t="s">
-        <v>244</v>
+        <v>63</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>231</v>
+        <v>536</v>
       </c>
       <c r="B157" t="s">
-        <v>245</v>
+        <v>420</v>
       </c>
       <c r="C157" t="s">
-        <v>246</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>231</v>
+        <v>537</v>
       </c>
       <c r="B158" t="s">
-        <v>247</v>
+        <v>422</v>
       </c>
       <c r="C158" t="s">
-        <v>248</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>231</v>
+        <v>537</v>
       </c>
       <c r="B159" t="s">
-        <v>247</v>
+        <v>424</v>
       </c>
       <c r="C159" t="s">
-        <v>249</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>231</v>
+        <v>538</v>
       </c>
       <c r="B160" t="s">
-        <v>250</v>
+        <v>426</v>
       </c>
       <c r="C160" t="s">
-        <v>251</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>231</v>
+        <v>539</v>
       </c>
       <c r="B161" t="s">
-        <v>252</v>
+        <v>428</v>
       </c>
       <c r="C161" t="s">
-        <v>253</v>
+        <v>429</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>231</v>
+        <v>540</v>
       </c>
       <c r="B162" t="s">
-        <v>120</v>
+        <v>430</v>
       </c>
       <c r="C162" t="s">
-        <v>254</v>
+        <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>255</v>
+        <v>540</v>
       </c>
       <c r="B163" t="s">
-        <v>256</v>
+        <v>432</v>
       </c>
       <c r="C163" t="s">
-        <v>257</v>
+        <v>433</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>255</v>
+        <v>3</v>
       </c>
       <c r="B164" t="s">
-        <v>258</v>
+        <v>5</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>255</v>
+        <v>3</v>
       </c>
       <c r="B165" t="s">
-        <v>258</v>
+        <v>5</v>
       </c>
       <c r="C165" t="s">
-        <v>260</v>
+        <v>434</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>255</v>
+        <v>3</v>
       </c>
       <c r="B166" t="s">
-        <v>261</v>
+        <v>24</v>
       </c>
       <c r="C166" t="s">
-        <v>262</v>
+        <v>25</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B167" t="s">
-        <v>264</v>
+        <v>207</v>
       </c>
       <c r="C167" t="s">
-        <v>265</v>
+        <v>208</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B168" t="s">
-        <v>266</v>
+        <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>266</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B169" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
       <c r="C169" t="s">
-        <v>267</v>
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B170" t="s">
-        <v>268</v>
+        <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>269</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B171" t="s">
-        <v>270</v>
+        <v>12</v>
       </c>
       <c r="C171" t="s">
-        <v>271</v>
+        <v>13</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B172" t="s">
-        <v>270</v>
+        <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>272</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B173" t="s">
-        <v>270</v>
+        <v>22</v>
       </c>
       <c r="C173" t="s">
-        <v>273</v>
+        <v>23</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>263</v>
+        <v>3</v>
       </c>
       <c r="B174" t="s">
-        <v>263</v>
+        <v>16</v>
       </c>
       <c r="C174" t="s">
-        <v>263</v>
+        <v>17</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>274</v>
+        <v>3</v>
       </c>
       <c r="B175" t="s">
-        <v>275</v>
+        <v>18</v>
       </c>
       <c r="C175" t="s">
-        <v>276</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>274</v>
+        <v>3</v>
       </c>
       <c r="B176" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="C176" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>279</v>
+        <v>3</v>
       </c>
       <c r="B177" t="s">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="C177" t="s">
-        <v>280</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="B178" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="C178" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="B179" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="C179" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>279</v>
+        <v>42</v>
       </c>
       <c r="B180" t="s">
-        <v>281</v>
+        <v>48</v>
       </c>
       <c r="C180" t="s">
-        <v>284</v>
+        <v>49</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>279</v>
+        <v>42</v>
       </c>
       <c r="B181" t="s">
-        <v>285</v>
+        <v>43</v>
       </c>
       <c r="C181" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>279</v>
+        <v>42</v>
       </c>
       <c r="B182" t="s">
-        <v>285</v>
+        <v>43</v>
       </c>
       <c r="C182" t="s">
-        <v>287</v>
+        <v>44</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>279</v>
+        <v>42</v>
       </c>
       <c r="B183" t="s">
-        <v>285</v>
+        <v>45</v>
       </c>
       <c r="C183" t="s">
-        <v>288</v>
+        <v>47</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>279</v>
+        <v>42</v>
       </c>
       <c r="B184" t="s">
-        <v>289</v>
+        <v>45</v>
       </c>
       <c r="C184" t="s">
-        <v>290</v>
+        <v>46</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>279</v>
+        <v>541</v>
       </c>
       <c r="B185" t="s">
-        <v>289</v>
+        <v>435</v>
       </c>
       <c r="C185" t="s">
-        <v>291</v>
+        <v>436</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>279</v>
+        <v>542</v>
       </c>
       <c r="B186" t="s">
-        <v>289</v>
+        <v>437</v>
       </c>
       <c r="C186" t="s">
-        <v>292</v>
+        <v>438</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>279</v>
+        <v>543</v>
       </c>
       <c r="B187" t="s">
-        <v>293</v>
+        <v>439</v>
       </c>
       <c r="C187" t="s">
-        <v>294</v>
+        <v>440</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>279</v>
+        <v>544</v>
       </c>
       <c r="B188" t="s">
-        <v>279</v>
+        <v>441</v>
       </c>
       <c r="C188" t="s">
-        <v>279</v>
+        <v>442</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>295</v>
+        <v>545</v>
       </c>
       <c r="B189" t="s">
-        <v>296</v>
+        <v>443</v>
       </c>
       <c r="C189" t="s">
-        <v>297</v>
+        <v>444</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B190" t="s">
-        <v>296</v>
+        <v>93</v>
       </c>
       <c r="C190" t="s">
-        <v>298</v>
+        <v>94</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B191" t="s">
-        <v>156</v>
+        <v>95</v>
       </c>
       <c r="C191" t="s">
-        <v>299</v>
+        <v>96</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B192" t="s">
-        <v>159</v>
+        <v>97</v>
       </c>
       <c r="C192" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B193" t="s">
-        <v>301</v>
+        <v>98</v>
       </c>
       <c r="C193" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B194" t="s">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="C194" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B195" t="s">
-        <v>162</v>
+        <v>100</v>
       </c>
       <c r="C195" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B196" t="s">
-        <v>305</v>
+        <v>101</v>
       </c>
       <c r="C196" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B197" t="s">
-        <v>256</v>
+        <v>102</v>
       </c>
       <c r="C197" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B198" t="s">
-        <v>256</v>
+        <v>103</v>
       </c>
       <c r="C198" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B199" t="s">
-        <v>309</v>
+        <v>104</v>
       </c>
       <c r="C199" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B200" t="s">
-        <v>309</v>
+        <v>105</v>
       </c>
       <c r="C200" t="s">
-        <v>311</v>
-      </c>
-      <c r="G200" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B201" t="s">
-        <v>312</v>
+        <v>106</v>
       </c>
       <c r="C201" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>295</v>
+        <v>91</v>
       </c>
       <c r="B202" t="s">
-        <v>314</v>
+        <v>107</v>
       </c>
       <c r="C202" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>316</v>
+        <v>91</v>
       </c>
       <c r="B203" t="s">
-        <v>317</v>
+        <v>108</v>
       </c>
       <c r="C203" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B204" t="s">
-        <v>320</v>
+        <v>109</v>
       </c>
       <c r="C204" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B205" t="s">
-        <v>321</v>
+        <v>110</v>
       </c>
       <c r="C205" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>323</v>
+        <v>111</v>
       </c>
       <c r="C206" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B207" t="s">
-        <v>325</v>
+        <v>112</v>
       </c>
       <c r="C207" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B208" t="s">
-        <v>325</v>
+        <v>113</v>
       </c>
       <c r="C208" t="s">
-        <v>327</v>
+        <v>113</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B209" t="s">
-        <v>328</v>
+        <v>114</v>
       </c>
       <c r="C209" t="s">
-        <v>329</v>
+        <v>114</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B210" t="s">
-        <v>330</v>
+        <v>115</v>
       </c>
       <c r="C210" t="s">
-        <v>331</v>
+        <v>115</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B211" t="s">
-        <v>332</v>
+        <v>233</v>
       </c>
       <c r="C211" t="s">
-        <v>333</v>
+        <v>234</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B212" t="s">
-        <v>332</v>
+        <v>445</v>
       </c>
       <c r="C212" t="s">
-        <v>334</v>
+        <v>446</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B213" t="s">
-        <v>332</v>
+        <v>116</v>
       </c>
       <c r="C213" t="s">
-        <v>335</v>
+        <v>118</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>319</v>
+        <v>91</v>
       </c>
       <c r="B214" t="s">
-        <v>332</v>
+        <v>116</v>
       </c>
       <c r="C214" t="s">
-        <v>336</v>
+        <v>117</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>319</v>
+        <v>546</v>
       </c>
       <c r="B215" t="s">
-        <v>332</v>
+        <v>447</v>
       </c>
       <c r="C215" t="s">
-        <v>337</v>
+        <v>448</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>319</v>
+        <v>547</v>
       </c>
       <c r="B216" t="s">
-        <v>332</v>
+        <v>449</v>
       </c>
       <c r="C216" t="s">
-        <v>338</v>
+        <v>450</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>319</v>
+        <v>547</v>
       </c>
       <c r="B217" t="s">
-        <v>332</v>
+        <v>451</v>
       </c>
       <c r="C217" t="s">
-        <v>339</v>
+        <v>452</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>319</v>
+        <v>547</v>
       </c>
       <c r="B218" t="s">
-        <v>340</v>
+        <v>453</v>
       </c>
       <c r="C218" t="s">
-        <v>341</v>
+        <v>454</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>319</v>
+        <v>547</v>
       </c>
       <c r="B219" t="s">
-        <v>340</v>
+        <v>455</v>
       </c>
       <c r="C219" t="s">
-        <v>342</v>
+        <v>456</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>319</v>
+        <v>547</v>
       </c>
       <c r="B220" t="s">
-        <v>340</v>
+        <v>457</v>
       </c>
       <c r="C220" t="s">
-        <v>343</v>
+        <v>458</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>319</v>
+        <v>547</v>
       </c>
       <c r="B221" t="s">
-        <v>340</v>
+        <v>459</v>
       </c>
       <c r="C221" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>319</v>
+        <v>558</v>
       </c>
       <c r="B222" t="s">
-        <v>345</v>
+        <v>509</v>
       </c>
       <c r="C222" t="s">
-        <v>346</v>
+        <v>510</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>319</v>
+        <v>176</v>
       </c>
       <c r="B223" t="s">
-        <v>345</v>
+        <v>178</v>
       </c>
       <c r="C223" t="s">
-        <v>347</v>
+        <v>180</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>319</v>
+        <v>176</v>
       </c>
       <c r="B224" t="s">
-        <v>348</v>
+        <v>178</v>
       </c>
       <c r="C224" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>350</v>
+        <v>176</v>
       </c>
       <c r="B225" t="s">
-        <v>351</v>
+        <v>178</v>
       </c>
       <c r="C225" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>350</v>
+        <v>176</v>
       </c>
       <c r="B226" t="s">
-        <v>351</v>
+        <v>178</v>
       </c>
       <c r="C226" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>350</v>
+        <v>176</v>
       </c>
       <c r="B227" t="s">
-        <v>354</v>
+        <v>178</v>
       </c>
       <c r="C227" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>350</v>
+        <v>176</v>
       </c>
       <c r="B228" t="s">
-        <v>354</v>
+        <v>178</v>
       </c>
       <c r="C228" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>350</v>
+        <v>176</v>
       </c>
       <c r="B229" t="s">
-        <v>357</v>
+        <v>232</v>
       </c>
       <c r="C229" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+      <c r="G229" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>359</v>
+        <v>322</v>
       </c>
       <c r="B230" t="s">
-        <v>360</v>
+        <v>323</v>
       </c>
       <c r="C230" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>359</v>
+        <v>322</v>
       </c>
       <c r="B231" t="s">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="C231" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>359</v>
+        <v>173</v>
       </c>
       <c r="B232" t="s">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="C232" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>359</v>
+        <v>173</v>
       </c>
       <c r="B233" t="s">
-        <v>50</v>
+        <v>209</v>
       </c>
       <c r="C233" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>365</v>
+        <v>173</v>
       </c>
       <c r="B234" t="s">
-        <v>366</v>
+        <v>285</v>
       </c>
       <c r="C234" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>365</v>
+        <v>173</v>
       </c>
       <c r="B235" t="s">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="C235" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>365</v>
+        <v>173</v>
       </c>
       <c r="B236" t="s">
-        <v>367</v>
+        <v>287</v>
       </c>
       <c r="C236" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>365</v>
+        <v>141</v>
       </c>
       <c r="B237" t="s">
-        <v>367</v>
+        <v>142</v>
       </c>
       <c r="C237" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>365</v>
+        <v>141</v>
       </c>
       <c r="B238" t="s">
-        <v>367</v>
+        <v>280</v>
       </c>
       <c r="C238" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>365</v>
+        <v>141</v>
       </c>
       <c r="B239" t="s">
-        <v>367</v>
+        <v>281</v>
       </c>
       <c r="C239" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>365</v>
+        <v>141</v>
       </c>
       <c r="B240" t="s">
-        <v>367</v>
+        <v>281</v>
       </c>
       <c r="C240" t="s">
-        <v>373</v>
+        <v>283</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>365</v>
+        <v>26</v>
       </c>
       <c r="B241" t="s">
-        <v>374</v>
+        <v>27</v>
       </c>
       <c r="C241" t="s">
-        <v>375</v>
+        <v>28</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>365</v>
+        <v>26</v>
       </c>
       <c r="B242" t="s">
-        <v>374</v>
+        <v>29</v>
       </c>
       <c r="C242" t="s">
-        <v>376</v>
+        <v>30</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>365</v>
+        <v>26</v>
       </c>
       <c r="B243" t="s">
-        <v>374</v>
+        <v>31</v>
       </c>
       <c r="C243" t="s">
-        <v>377</v>
+        <v>32</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>378</v>
+        <v>26</v>
       </c>
       <c r="B244" t="s">
-        <v>379</v>
+        <v>33</v>
       </c>
       <c r="C244" t="s">
-        <v>380</v>
+        <v>34</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>378</v>
+        <v>26</v>
       </c>
       <c r="B245" t="s">
-        <v>379</v>
+        <v>33</v>
       </c>
       <c r="C245" t="s">
-        <v>381</v>
+        <v>35</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>378</v>
+        <v>26</v>
       </c>
       <c r="B246" t="s">
-        <v>382</v>
+        <v>33</v>
       </c>
       <c r="C246" t="s">
-        <v>383</v>
+        <v>461</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>378</v>
+        <v>26</v>
       </c>
       <c r="B247" t="s">
-        <v>384</v>
+        <v>313</v>
       </c>
       <c r="C247" t="s">
-        <v>385</v>
+        <v>314</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>378</v>
+        <v>52</v>
       </c>
       <c r="B248" t="s">
-        <v>384</v>
+        <v>53</v>
       </c>
       <c r="C248" t="s">
-        <v>386</v>
+        <v>54</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>378</v>
+        <v>52</v>
       </c>
       <c r="B249" t="s">
-        <v>384</v>
+        <v>53</v>
       </c>
       <c r="C249" t="s">
-        <v>387</v>
+        <v>55</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>378</v>
+        <v>56</v>
       </c>
       <c r="B250" t="s">
-        <v>388</v>
+        <v>57</v>
       </c>
       <c r="C250" t="s">
-        <v>389</v>
+        <v>58</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>378</v>
+        <v>56</v>
       </c>
       <c r="B251" t="s">
-        <v>390</v>
+        <v>462</v>
       </c>
       <c r="C251" t="s">
-        <v>391</v>
+        <v>463</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>378</v>
+        <v>56</v>
       </c>
       <c r="B252" t="s">
-        <v>392</v>
+        <v>310</v>
       </c>
       <c r="C252" t="s">
-        <v>393</v>
+        <v>311</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>378</v>
+        <v>56</v>
       </c>
       <c r="B253" t="s">
-        <v>394</v>
+        <v>310</v>
       </c>
       <c r="C253" t="s">
-        <v>395</v>
+        <v>312</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>396</v>
+        <v>307</v>
       </c>
       <c r="B254" t="s">
-        <v>397</v>
+        <v>308</v>
       </c>
       <c r="C254" t="s">
-        <v>397</v>
+        <v>309</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>396</v>
+        <v>26</v>
       </c>
       <c r="B255" t="s">
-        <v>398</v>
+        <v>226</v>
       </c>
       <c r="C255" t="s">
-        <v>399</v>
+        <v>227</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>396</v>
+        <v>26</v>
       </c>
       <c r="B256" t="s">
-        <v>400</v>
+        <v>36</v>
       </c>
       <c r="C256" t="s">
-        <v>401</v>
+        <v>37</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>396</v>
+        <v>548</v>
       </c>
       <c r="B257" t="s">
-        <v>402</v>
+        <v>464</v>
       </c>
       <c r="C257" t="s">
-        <v>403</v>
+        <v>465</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>396</v>
+        <v>548</v>
       </c>
       <c r="B258" t="s">
-        <v>404</v>
+        <v>466</v>
       </c>
       <c r="C258" t="s">
-        <v>405</v>
+        <v>467</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>396</v>
+        <v>548</v>
       </c>
       <c r="B259" t="s">
-        <v>404</v>
+        <v>468</v>
       </c>
       <c r="C259" t="s">
-        <v>406</v>
+        <v>469</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>396</v>
+        <v>548</v>
       </c>
       <c r="B260" t="s">
-        <v>407</v>
+        <v>470</v>
       </c>
       <c r="C260" t="s">
-        <v>408</v>
+        <v>471</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>396</v>
+        <v>548</v>
       </c>
       <c r="B261" t="s">
-        <v>409</v>
+        <v>472</v>
       </c>
       <c r="C261" t="s">
-        <v>410</v>
+        <v>473</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>396</v>
+        <v>548</v>
       </c>
       <c r="B262" t="s">
-        <v>409</v>
+        <v>474</v>
       </c>
       <c r="C262" t="s">
-        <v>411</v>
+        <v>475</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>396</v>
+        <v>549</v>
       </c>
       <c r="B263" t="s">
-        <v>409</v>
+        <v>476</v>
       </c>
       <c r="C263" t="s">
-        <v>412</v>
+        <v>477</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>396</v>
+        <v>549</v>
       </c>
       <c r="B264" t="s">
-        <v>413</v>
+        <v>478</v>
       </c>
       <c r="C264" t="s">
-        <v>414</v>
+        <v>479</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>396</v>
+        <v>549</v>
       </c>
       <c r="B265" t="s">
-        <v>415</v>
+        <v>480</v>
       </c>
       <c r="C265" t="s">
-        <v>416</v>
+        <v>481</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>396</v>
+        <v>224</v>
       </c>
       <c r="B266" t="s">
-        <v>417</v>
+        <v>221</v>
       </c>
       <c r="C266" t="s">
-        <v>418</v>
+        <v>222</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>396</v>
+        <v>224</v>
       </c>
       <c r="B267" t="s">
-        <v>419</v>
+        <v>221</v>
       </c>
       <c r="C267" t="s">
-        <v>420</v>
+        <v>223</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>396</v>
+        <v>138</v>
       </c>
       <c r="B268" t="s">
-        <v>421</v>
+        <v>139</v>
       </c>
       <c r="C268" t="s">
-        <v>422</v>
+        <v>225</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>396</v>
+        <v>138</v>
       </c>
       <c r="B269" t="s">
-        <v>423</v>
+        <v>139</v>
       </c>
       <c r="C269" t="s">
-        <v>424</v>
+        <v>140</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>396</v>
+        <v>550</v>
       </c>
       <c r="B270" t="s">
-        <v>425</v>
+        <v>482</v>
       </c>
       <c r="C270" t="s">
-        <v>426</v>
+        <v>483</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>396</v>
+        <v>550</v>
       </c>
       <c r="B271" t="s">
-        <v>427</v>
+        <v>482</v>
       </c>
       <c r="C271" t="s">
-        <v>428</v>
+        <v>484</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>396</v>
+        <v>551</v>
       </c>
       <c r="B272" t="s">
-        <v>429</v>
+        <v>485</v>
       </c>
       <c r="C272" t="s">
-        <v>430</v>
+        <v>486</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>396</v>
+        <v>551</v>
       </c>
       <c r="B273" t="s">
-        <v>429</v>
+        <v>487</v>
       </c>
       <c r="C273" t="s">
-        <v>431</v>
+        <v>488</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>396</v>
+        <v>552</v>
       </c>
       <c r="B274" t="s">
-        <v>429</v>
+        <v>489</v>
       </c>
       <c r="C274" t="s">
-        <v>432</v>
+        <v>490</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>396</v>
+        <v>38</v>
       </c>
       <c r="B275" t="s">
-        <v>433</v>
+        <v>41</v>
       </c>
       <c r="C275" t="s">
-        <v>434</v>
+        <v>41</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>396</v>
+        <v>59</v>
       </c>
       <c r="B276" t="s">
-        <v>435</v>
+        <v>70</v>
       </c>
       <c r="C276" t="s">
-        <v>436</v>
+        <v>70</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>396</v>
+        <v>144</v>
       </c>
       <c r="B277" t="s">
-        <v>437</v>
+        <v>144</v>
       </c>
       <c r="C277" t="s">
-        <v>438</v>
+        <v>144</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>439</v>
+        <v>553</v>
       </c>
       <c r="B278" t="s">
-        <v>440</v>
+        <v>491</v>
       </c>
       <c r="C278" t="s">
-        <v>440</v>
+        <v>492</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>439</v>
+        <v>553</v>
       </c>
       <c r="B279" t="s">
-        <v>441</v>
+        <v>493</v>
       </c>
       <c r="C279" t="s">
-        <v>440</v>
+        <v>494</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>439</v>
+        <v>553</v>
       </c>
       <c r="B280" t="s">
-        <v>281</v>
+        <v>495</v>
       </c>
       <c r="C280" t="s">
-        <v>442</v>
+        <v>496</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>439</v>
+        <v>554</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>497</v>
       </c>
       <c r="C281" t="s">
-        <v>443</v>
+        <v>498</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>439</v>
+        <v>555</v>
       </c>
       <c r="B282" t="s">
-        <v>281</v>
+        <v>499</v>
       </c>
       <c r="C282" t="s">
-        <v>444</v>
+        <v>500</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>439</v>
+        <v>555</v>
       </c>
       <c r="B283" t="s">
-        <v>445</v>
+        <v>501</v>
       </c>
       <c r="C283" t="s">
-        <v>444</v>
+        <v>502</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>439</v>
+        <v>503</v>
       </c>
       <c r="B284" t="s">
-        <v>445</v>
+        <v>503</v>
       </c>
       <c r="C284" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>439</v>
+        <v>504</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>504</v>
       </c>
       <c r="C285" t="s">
-        <v>447</v>
+        <v>504</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>439</v>
+        <v>561</v>
       </c>
       <c r="B286" t="s">
-        <v>285</v>
+        <v>559</v>
       </c>
       <c r="C286" t="s">
-        <v>448</v>
+        <v>560</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>439</v>
-      </c>
-      <c r="B287" t="s">
-        <v>289</v>
-      </c>
-      <c r="C287" t="s">
-        <v>449</v>
+        <v>572</v>
+      </c>
+      <c r="B287" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="C287" s="8" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>573</v>
+      </c>
+      <c r="B288" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="C288" s="8" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>574</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="C289" s="8" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>575</v>
+      </c>
+      <c r="B290" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="C290" s="8" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>575</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="C291" s="8" t="s">
+        <v>571</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:X286" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C177:C1048576 C149:C175 C1:C147">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/预测分析.xlsx
+++ b/预测分析.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forecast\预测分析\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEEA6CD-22B1-4AC8-BFB0-C34F165F1055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0819B79-FC45-484B-9BC8-F122567721C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="864" yWindow="804" windowWidth="17280" windowHeight="10044" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$X$286</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$Y$314</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,8 +36,43 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Pedro Yang(杨小鸿_SM)</author>
+  </authors>
+  <commentList>
+    <comment ref="B302" authorId="0" shapeId="0" xr:uid="{6B5DF088-E59A-4CC0-AE73-52270BCDBEBC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Pedro Yang(杨小鸿_SM):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+消费， 豆浆机
+单极 19-45Gs</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="618">
   <si>
     <t>晶圆</t>
   </si>
@@ -1294,9 +1329,6 @@
     <t>SC2498TSO-TR-Q</t>
   </si>
   <si>
-    <t>SC2498TSO-Q-CC-10CR-2498T</t>
-  </si>
-  <si>
     <t>SC2498UA-N-Q-DB-60AK-2498</t>
   </si>
   <si>
@@ -1883,13 +1915,176 @@
   <si>
     <t>STC9G005C</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1002A3-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1002A3-CG-00UK-41HS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1002N1W-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1002N1W-CL-00AK-N41H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1002S1-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1002S1-CG-00AK-41H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1002S2-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1002S2-CG-00AK-41F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1245UA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1245UA-1245</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1445A1-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1445A1-AB-00HK-4451H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1445A2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1445A2-713B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1445B2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1445B2-713</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645S1-BK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC1645S1-AI-00AK-4601</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2242SO-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2242SO-CH-90NR-2242</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2413SO-N-TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2413SO-N-CD-00NR-44E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC25898CUB-BK-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC25898CUB-Q-DD-60AK-25898</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2919SO-N-TR-Q</t>
+  </si>
+  <si>
+    <t>SC2919SO-N-Q-CD-90AR-2919</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2943UA-BK-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2943UA-Q-DB-60AK-2943</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2943UA-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2943UA-Q-K01-DB-60AR-2943</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2948SO-TR-Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC2948SO-Q-DB-60AR-2948</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4001SE-CB-90LR-4001</t>
+  </si>
+  <si>
+    <t>SC4015SO-L-CE-90NR-CY19</t>
+  </si>
+  <si>
+    <t>SC2498TSO-Q-DB-60CR-2498T</t>
+  </si>
+  <si>
+    <t>SC4015SO-H-CE-90NR-CY19</t>
+  </si>
+  <si>
+    <t>SC4624SP20B5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4624SP20B5-SC4624</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4823S6-GB-00NR-4823</t>
+  </si>
+  <si>
+    <t>SC60228DC-DC-90AR-60228</t>
+  </si>
+  <si>
+    <t>SC69401DC-SPI3P3-TR-Q</t>
+  </si>
+  <si>
+    <t>SC69401DC-SPI3P3-Q-HD-4XCR-69401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC11102D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1913,10 +2108,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="思源黑体 CN Regular"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1945,7 +2160,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1953,27 +2168,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1990,15 +2193,33 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 4 2 2" xfId="1" xr:uid="{9C7ED766-84C1-4343-B919-15B8593B06F8}"/>
+    <cellStyle name="常规 7 2" xfId="2" xr:uid="{6091A728-022E-4531-89CE-1A6489418057}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2284,81 +2505,82 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X291"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Y314"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="D1" s="3" t="s">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="E1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2368,71 +2590,71 @@
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5">
+      <c r="E2" s="5">
         <v>7</v>
       </c>
-      <c r="E2" s="6">
+      <c r="F2" s="6">
         <v>7</v>
       </c>
-      <c r="F2" s="7">
+      <c r="G2" s="7">
         <v>7</v>
       </c>
-      <c r="G2" s="5">
+      <c r="H2" s="5">
         <v>8</v>
       </c>
-      <c r="H2" s="6">
+      <c r="I2" s="6">
         <v>8</v>
       </c>
-      <c r="I2" s="7">
+      <c r="J2" s="7">
         <v>8</v>
       </c>
-      <c r="J2" s="5">
+      <c r="K2" s="5">
         <v>9</v>
       </c>
-      <c r="K2" s="6">
+      <c r="L2" s="6">
         <v>9</v>
       </c>
-      <c r="L2" s="7">
+      <c r="M2" s="7">
         <v>9</v>
       </c>
-      <c r="M2" s="5">
+      <c r="N2" s="5">
         <v>10</v>
       </c>
-      <c r="N2" s="6">
+      <c r="O2" s="6">
         <v>10</v>
       </c>
-      <c r="O2" s="7">
+      <c r="P2" s="7">
         <v>10</v>
       </c>
-      <c r="P2" s="5">
+      <c r="Q2" s="5">
         <v>11</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="R2" s="6">
         <v>11</v>
       </c>
-      <c r="R2" s="7">
+      <c r="S2" s="7">
         <v>11</v>
       </c>
-      <c r="S2" s="6">
+      <c r="T2" s="6">
         <v>12</v>
       </c>
-      <c r="T2" s="5">
+      <c r="U2" s="5">
         <v>12</v>
       </c>
-      <c r="U2" s="7">
+      <c r="V2" s="7">
         <v>12</v>
       </c>
-      <c r="V2" s="5">
+      <c r="W2" s="5">
         <v>1</v>
       </c>
-      <c r="W2" s="6">
+      <c r="X2" s="6">
         <v>1</v>
       </c>
-      <c r="X2" s="7">
+      <c r="Y2" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -2443,7 +2665,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>77</v>
       </c>
@@ -2454,7 +2676,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>162</v>
       </c>
@@ -2465,7 +2687,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>176</v>
       </c>
@@ -2476,7 +2698,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>144</v>
       </c>
@@ -2487,7 +2709,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>188</v>
       </c>
@@ -2498,7 +2720,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2509,7 +2731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>91</v>
       </c>
@@ -2520,9 +2742,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B11" t="s">
         <v>329</v>
@@ -2531,7 +2753,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>199</v>
       </c>
@@ -2542,7 +2764,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>119</v>
       </c>
@@ -2553,7 +2775,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>119</v>
       </c>
@@ -2564,7 +2786,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>119</v>
       </c>
@@ -2575,7 +2797,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>119</v>
       </c>
@@ -2588,7 +2810,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B17" t="s">
         <v>330</v>
@@ -2599,7 +2821,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B18" t="s">
         <v>332</v>
@@ -2610,7 +2832,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B19" t="s">
         <v>334</v>
@@ -2654,7 +2876,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B23" t="s">
         <v>337</v>
@@ -2742,7 +2964,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B31" t="s">
         <v>339</v>
@@ -2841,7 +3063,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B40" t="s">
         <v>341</v>
@@ -2888,7 +3110,7 @@
         <v>119</v>
       </c>
       <c r="B44" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C44" t="s">
         <v>343</v>
@@ -2929,10 +3151,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B48" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C48" t="s">
         <v>344</v>
@@ -3006,7 +3228,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B55" t="s">
         <v>346</v>
@@ -3017,7 +3239,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B56" t="s">
         <v>348</v>
@@ -3028,18 +3250,18 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B57" t="s">
+        <v>506</v>
+      </c>
+      <c r="C57" t="s">
         <v>507</v>
-      </c>
-      <c r="C57" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B58" t="s">
         <v>350</v>
@@ -3050,7 +3272,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B59" t="s">
         <v>352</v>
@@ -3061,7 +3283,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B60" t="s">
         <v>354</v>
@@ -3072,7 +3294,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B61" t="s">
         <v>356</v>
@@ -3083,7 +3305,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B62" t="s">
         <v>358</v>
@@ -3094,7 +3316,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B63" t="s">
         <v>358</v>
@@ -3105,7 +3327,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B64" t="s">
         <v>361</v>
@@ -3116,7 +3338,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B65" t="s">
         <v>363</v>
@@ -3177,7 +3399,7 @@
         <v>148</v>
       </c>
       <c r="C70" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3259,7 +3481,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B78" t="s">
         <v>365</v>
@@ -3336,7 +3558,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B85" t="s">
         <v>367</v>
@@ -3479,7 +3701,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B98" t="s">
         <v>369</v>
@@ -3655,7 +3877,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B114" t="s">
         <v>375</v>
@@ -3666,7 +3888,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B115" t="s">
         <v>377</v>
@@ -3743,7 +3965,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B122" t="s">
         <v>379</v>
@@ -3787,13 +4009,13 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B126" t="s">
         <v>384</v>
       </c>
       <c r="C126" t="s">
-        <v>385</v>
+        <v>609</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3815,84 +4037,84 @@
         <v>158</v>
       </c>
       <c r="C128" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B129" t="s">
+        <v>386</v>
+      </c>
+      <c r="C129" t="s">
         <v>387</v>
-      </c>
-      <c r="C129" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B130" t="s">
+        <v>388</v>
+      </c>
+      <c r="C130" t="s">
         <v>389</v>
-      </c>
-      <c r="C130" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B131" t="s">
+        <v>390</v>
+      </c>
+      <c r="C131" t="s">
         <v>391</v>
-      </c>
-      <c r="C131" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B132" t="s">
+        <v>392</v>
+      </c>
+      <c r="C132" t="s">
         <v>393</v>
-      </c>
-      <c r="C132" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B133" t="s">
+        <v>394</v>
+      </c>
+      <c r="C133" t="s">
         <v>395</v>
-      </c>
-      <c r="C133" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B134" t="s">
+        <v>396</v>
+      </c>
+      <c r="C134" t="s">
         <v>397</v>
-      </c>
-      <c r="C134" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B135" t="s">
+        <v>398</v>
+      </c>
+      <c r="C135" t="s">
         <v>399</v>
-      </c>
-      <c r="C135" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3911,10 +4133,10 @@
         <v>152</v>
       </c>
       <c r="B137" t="s">
+        <v>400</v>
+      </c>
+      <c r="C137" t="s">
         <v>401</v>
-      </c>
-      <c r="C137" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3922,98 +4144,98 @@
         <v>152</v>
       </c>
       <c r="B138" t="s">
+        <v>402</v>
+      </c>
+      <c r="C138" t="s">
         <v>403</v>
-      </c>
-      <c r="C138" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B139" t="s">
+        <v>404</v>
+      </c>
+      <c r="C139" t="s">
         <v>405</v>
-      </c>
-      <c r="C139" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B140" t="s">
+        <v>504</v>
+      </c>
+      <c r="C140" t="s">
         <v>505</v>
-      </c>
-      <c r="C140" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B141" t="s">
+        <v>406</v>
+      </c>
+      <c r="C141" t="s">
         <v>407</v>
-      </c>
-      <c r="C141" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B142" t="s">
+        <v>408</v>
+      </c>
+      <c r="C142" t="s">
         <v>409</v>
-      </c>
-      <c r="C142" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B143" t="s">
+        <v>410</v>
+      </c>
+      <c r="C143" t="s">
         <v>411</v>
-      </c>
-      <c r="C143" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B144" t="s">
+        <v>412</v>
+      </c>
+      <c r="C144" t="s">
         <v>413</v>
-      </c>
-      <c r="C144" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B145" t="s">
+        <v>414</v>
+      </c>
+      <c r="C145" t="s">
         <v>415</v>
-      </c>
-      <c r="C145" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B146" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C146" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -4021,10 +4243,10 @@
         <v>38</v>
       </c>
       <c r="B147" t="s">
+        <v>417</v>
+      </c>
+      <c r="C147" t="s">
         <v>418</v>
-      </c>
-      <c r="C147" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -4128,79 +4350,79 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B157" t="s">
+        <v>419</v>
+      </c>
+      <c r="C157" t="s">
         <v>420</v>
-      </c>
-      <c r="C157" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B158" t="s">
+        <v>421</v>
+      </c>
+      <c r="C158" t="s">
         <v>422</v>
-      </c>
-      <c r="C158" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B159" t="s">
+        <v>423</v>
+      </c>
+      <c r="C159" t="s">
         <v>424</v>
-      </c>
-      <c r="C159" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B160" t="s">
+        <v>425</v>
+      </c>
+      <c r="C160" t="s">
         <v>426</v>
-      </c>
-      <c r="C160" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B161" t="s">
+        <v>427</v>
+      </c>
+      <c r="C161" t="s">
         <v>428</v>
-      </c>
-      <c r="C161" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B162" t="s">
+        <v>429</v>
+      </c>
+      <c r="C162" t="s">
         <v>430</v>
-      </c>
-      <c r="C162" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B163" t="s">
+        <v>431</v>
+      </c>
+      <c r="C163" t="s">
         <v>432</v>
-      </c>
-      <c r="C163" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4222,7 +4444,7 @@
         <v>5</v>
       </c>
       <c r="C165" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4436,57 +4658,57 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B185" t="s">
+        <v>434</v>
+      </c>
+      <c r="C185" t="s">
         <v>435</v>
-      </c>
-      <c r="C185" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B186" t="s">
+        <v>436</v>
+      </c>
+      <c r="C186" t="s">
         <v>437</v>
-      </c>
-      <c r="C186" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B187" t="s">
+        <v>438</v>
+      </c>
+      <c r="C187" t="s">
         <v>439</v>
-      </c>
-      <c r="C187" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B188" t="s">
+        <v>440</v>
+      </c>
+      <c r="C188" t="s">
         <v>441</v>
-      </c>
-      <c r="C188" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B189" t="s">
+        <v>442</v>
+      </c>
+      <c r="C189" t="s">
         <v>443</v>
-      </c>
-      <c r="C189" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4736,10 +4958,10 @@
         <v>91</v>
       </c>
       <c r="B212" t="s">
+        <v>444</v>
+      </c>
+      <c r="C212" t="s">
         <v>445</v>
-      </c>
-      <c r="C212" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4766,90 +4988,90 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B215" t="s">
+        <v>446</v>
+      </c>
+      <c r="C215" t="s">
         <v>447</v>
-      </c>
-      <c r="C215" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B216" t="s">
+        <v>448</v>
+      </c>
+      <c r="C216" t="s">
         <v>449</v>
-      </c>
-      <c r="C216" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B217" t="s">
+        <v>450</v>
+      </c>
+      <c r="C217" t="s">
         <v>451</v>
-      </c>
-      <c r="C217" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B218" t="s">
+        <v>452</v>
+      </c>
+      <c r="C218" t="s">
         <v>453</v>
-      </c>
-      <c r="C218" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B219" t="s">
+        <v>454</v>
+      </c>
+      <c r="C219" t="s">
         <v>455</v>
-      </c>
-      <c r="C219" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B220" t="s">
+        <v>456</v>
+      </c>
+      <c r="C220" t="s">
         <v>457</v>
-      </c>
-      <c r="C220" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B221" t="s">
+        <v>458</v>
+      </c>
+      <c r="C221" t="s">
         <v>459</v>
-      </c>
-      <c r="C221" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B222" t="s">
+        <v>508</v>
+      </c>
+      <c r="C222" t="s">
         <v>509</v>
-      </c>
-      <c r="C222" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4874,7 +5096,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>176</v>
       </c>
@@ -4885,7 +5107,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>176</v>
       </c>
@@ -4896,7 +5118,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>176</v>
       </c>
@@ -4907,7 +5129,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>176</v>
       </c>
@@ -4918,7 +5140,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>176</v>
       </c>
@@ -4928,11 +5150,11 @@
       <c r="C229" t="s">
         <v>231</v>
       </c>
-      <c r="G229" t="s">
+      <c r="H229" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>322</v>
       </c>
@@ -4943,7 +5165,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>322</v>
       </c>
@@ -4954,7 +5176,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>173</v>
       </c>
@@ -4965,7 +5187,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>173</v>
       </c>
@@ -4976,7 +5198,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>173</v>
       </c>
@@ -4987,7 +5209,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>173</v>
       </c>
@@ -4998,7 +5220,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>173</v>
       </c>
@@ -5009,7 +5231,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>141</v>
       </c>
@@ -5020,7 +5242,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>141</v>
       </c>
@@ -5031,7 +5253,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>141</v>
       </c>
@@ -5042,7 +5264,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>141</v>
       </c>
@@ -5116,7 +5338,7 @@
         <v>33</v>
       </c>
       <c r="C246" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -5168,10 +5390,10 @@
         <v>56</v>
       </c>
       <c r="B251" t="s">
+        <v>461</v>
+      </c>
+      <c r="C251" t="s">
         <v>462</v>
-      </c>
-      <c r="C251" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -5231,101 +5453,101 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B257" t="s">
+        <v>463</v>
+      </c>
+      <c r="C257" t="s">
         <v>464</v>
-      </c>
-      <c r="C257" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B258" t="s">
+        <v>465</v>
+      </c>
+      <c r="C258" t="s">
         <v>466</v>
-      </c>
-      <c r="C258" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B259" t="s">
+        <v>467</v>
+      </c>
+      <c r="C259" t="s">
         <v>468</v>
-      </c>
-      <c r="C259" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B260" t="s">
+        <v>469</v>
+      </c>
+      <c r="C260" t="s">
         <v>470</v>
-      </c>
-      <c r="C260" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B261" t="s">
+        <v>471</v>
+      </c>
+      <c r="C261" t="s">
         <v>472</v>
-      </c>
-      <c r="C261" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B262" t="s">
+        <v>473</v>
+      </c>
+      <c r="C262" t="s">
         <v>474</v>
-      </c>
-      <c r="C262" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B263" t="s">
+        <v>475</v>
+      </c>
+      <c r="C263" t="s">
         <v>476</v>
-      </c>
-      <c r="C263" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B264" t="s">
+        <v>477</v>
+      </c>
+      <c r="C264" t="s">
         <v>478</v>
-      </c>
-      <c r="C264" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B265" t="s">
+        <v>479</v>
+      </c>
+      <c r="C265" t="s">
         <v>480</v>
-      </c>
-      <c r="C265" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -5374,57 +5596,57 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B270" t="s">
+        <v>481</v>
+      </c>
+      <c r="C270" t="s">
         <v>482</v>
-      </c>
-      <c r="C270" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B271" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C271" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B272" t="s">
+        <v>484</v>
+      </c>
+      <c r="C272" t="s">
         <v>485</v>
-      </c>
-      <c r="C272" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B273" t="s">
+        <v>486</v>
+      </c>
+      <c r="C273" t="s">
         <v>487</v>
-      </c>
-      <c r="C273" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B274" t="s">
+        <v>488</v>
+      </c>
+      <c r="C274" t="s">
         <v>489</v>
-      </c>
-      <c r="C274" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -5462,164 +5684,428 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B278" t="s">
+        <v>490</v>
+      </c>
+      <c r="C278" t="s">
         <v>491</v>
-      </c>
-      <c r="C278" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B279" t="s">
+        <v>492</v>
+      </c>
+      <c r="C279" t="s">
         <v>493</v>
-      </c>
-      <c r="C279" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B280" t="s">
+        <v>494</v>
+      </c>
+      <c r="C280" t="s">
         <v>495</v>
-      </c>
-      <c r="C280" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B281" t="s">
+        <v>496</v>
+      </c>
+      <c r="C281" t="s">
         <v>497</v>
-      </c>
-      <c r="C281" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B282" t="s">
+        <v>498</v>
+      </c>
+      <c r="C282" t="s">
         <v>499</v>
-      </c>
-      <c r="C282" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B283" t="s">
+        <v>500</v>
+      </c>
+      <c r="C283" t="s">
         <v>501</v>
-      </c>
-      <c r="C283" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B284" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C284" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B285" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C285" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B286" t="s">
+        <v>558</v>
+      </c>
+      <c r="C286" t="s">
         <v>559</v>
-      </c>
-      <c r="C286" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>572</v>
-      </c>
-      <c r="B287" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="B287" t="s">
+        <v>562</v>
+      </c>
+      <c r="C287" t="s">
         <v>563</v>
-      </c>
-      <c r="C287" s="8" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>573</v>
-      </c>
-      <c r="B288" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="B288" t="s">
+        <v>564</v>
+      </c>
+      <c r="C288" t="s">
         <v>565</v>
-      </c>
-      <c r="C288" s="8" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>574</v>
-      </c>
-      <c r="B289" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="B289" t="s">
+        <v>566</v>
+      </c>
+      <c r="C289" t="s">
         <v>567</v>
-      </c>
-      <c r="C289" s="8" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>575</v>
-      </c>
-      <c r="B290" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="B290" t="s">
+        <v>568</v>
+      </c>
+      <c r="C290" t="s">
         <v>569</v>
-      </c>
-      <c r="C290" s="8" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
+        <v>574</v>
+      </c>
+      <c r="B291" t="s">
+        <v>568</v>
+      </c>
+      <c r="C291" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>514</v>
+      </c>
+      <c r="B292" t="s">
         <v>575</v>
       </c>
-      <c r="B291" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="C291" s="8" t="s">
-        <v>571</v>
+      <c r="C292" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>516</v>
+      </c>
+      <c r="B293" t="s">
+        <v>577</v>
+      </c>
+      <c r="C293" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>514</v>
+      </c>
+      <c r="B294" t="s">
+        <v>579</v>
+      </c>
+      <c r="C294" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>514</v>
+      </c>
+      <c r="B295" t="s">
+        <v>581</v>
+      </c>
+      <c r="C295" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>77</v>
+      </c>
+      <c r="B296" t="s">
+        <v>583</v>
+      </c>
+      <c r="C296" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>520</v>
+      </c>
+      <c r="B297" t="s">
+        <v>585</v>
+      </c>
+      <c r="C297" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>520</v>
+      </c>
+      <c r="B298" t="s">
+        <v>587</v>
+      </c>
+      <c r="C298" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>520</v>
+      </c>
+      <c r="B299" t="s">
+        <v>589</v>
+      </c>
+      <c r="C299" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>119</v>
+      </c>
+      <c r="B300" t="s">
+        <v>591</v>
+      </c>
+      <c r="C300" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>524</v>
+      </c>
+      <c r="B301" t="s">
+        <v>593</v>
+      </c>
+      <c r="C301" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>525</v>
+      </c>
+      <c r="B302" t="s">
+        <v>595</v>
+      </c>
+      <c r="C302" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>617</v>
+      </c>
+      <c r="B303" t="s">
+        <v>597</v>
+      </c>
+      <c r="C303" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>557</v>
+      </c>
+      <c r="B304" t="s">
+        <v>599</v>
+      </c>
+      <c r="C304" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>152</v>
+      </c>
+      <c r="B305" t="s">
+        <v>601</v>
+      </c>
+      <c r="C305" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>152</v>
+      </c>
+      <c r="B306" t="s">
+        <v>603</v>
+      </c>
+      <c r="C306" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>152</v>
+      </c>
+      <c r="B307" t="s">
+        <v>605</v>
+      </c>
+      <c r="C307" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>533</v>
+      </c>
+      <c r="B308" t="s">
+        <v>406</v>
+      </c>
+      <c r="C308" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>59</v>
+      </c>
+      <c r="B309" t="s">
+        <v>62</v>
+      </c>
+      <c r="C309" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>59</v>
+      </c>
+      <c r="B310" t="s">
+        <v>62</v>
+      </c>
+      <c r="C310" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>300</v>
+      </c>
+      <c r="B311" t="s">
+        <v>611</v>
+      </c>
+      <c r="C311" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>541</v>
+      </c>
+      <c r="B312" t="s">
+        <v>438</v>
+      </c>
+      <c r="C312" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>91</v>
+      </c>
+      <c r="B313" t="s">
+        <v>116</v>
+      </c>
+      <c r="C313" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>546</v>
+      </c>
+      <c r="B314" t="s">
+        <v>615</v>
+      </c>
+      <c r="C314" t="s">
+        <v>616</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:X286" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <protectedRanges>
+    <protectedRange sqref="B294:C294" name="区域1_3_4_1"/>
+    <protectedRange sqref="C296" name="区域1_3_4_1_1"/>
+    <protectedRange sqref="B299" name="区域1_3_4_2_2_1"/>
+    <protectedRange sqref="B300:C300" name="区域1_27_2_4" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1129)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1131)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1172)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1178)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1181)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1182)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1184)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1239)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1265)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1381)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1408)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1410)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1392)"/>
+    <protectedRange sqref="C310" name="区域1_22_2_1_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1129)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1131)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1172)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1178)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1181)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1182)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1184)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1239)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1265)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1381)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1408)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1410)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1392)"/>
+  </protectedRanges>
+  <autoFilter ref="A2:Y314" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C177:C1048576 C149:C175 C1:C147">
+  <conditionalFormatting sqref="C149:D175 C1:D147 C177:D1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/预测分析.xlsx
+++ b/预测分析.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forecast\预测分析\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0819B79-FC45-484B-9BC8-F122567721C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93043F9-9404-438E-97CC-5FF6A91C5FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$Y$314</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$Z$314</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="620">
   <si>
     <t>晶圆</t>
   </si>
@@ -2078,6 +2078,14 @@
   </si>
   <si>
     <t>STC11102D</t>
+  </si>
+  <si>
+    <t>代理商</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>终端客户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2199,17 +2207,7 @@
     <cellStyle name="常规 2 4 2 2" xfId="1" xr:uid="{9C7ED766-84C1-4343-B919-15B8593B06F8}"/>
     <cellStyle name="常规 7 2" xfId="2" xr:uid="{6091A728-022E-4531-89CE-1A6489418057}"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2506,81 +2504,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y314"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:Z314"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.5546875" customWidth="1"/>
+    <col min="4" max="4" width="26.5546875" customWidth="1"/>
+    <col min="5" max="5" width="28.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="E1" s="3" t="s">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="F1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2590,71 +2590,77 @@
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5">
+      <c r="D2" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="F2" s="5">
         <v>7</v>
       </c>
-      <c r="F2" s="6">
+      <c r="G2" s="6">
         <v>7</v>
       </c>
-      <c r="G2" s="7">
+      <c r="H2" s="7">
         <v>7</v>
       </c>
-      <c r="H2" s="5">
+      <c r="I2" s="5">
         <v>8</v>
       </c>
-      <c r="I2" s="6">
+      <c r="J2" s="6">
         <v>8</v>
       </c>
-      <c r="J2" s="7">
+      <c r="K2" s="7">
         <v>8</v>
       </c>
-      <c r="K2" s="5">
+      <c r="L2" s="5">
         <v>9</v>
       </c>
-      <c r="L2" s="6">
+      <c r="M2" s="6">
         <v>9</v>
       </c>
-      <c r="M2" s="7">
+      <c r="N2" s="7">
         <v>9</v>
       </c>
-      <c r="N2" s="5">
+      <c r="O2" s="5">
         <v>10</v>
       </c>
-      <c r="O2" s="6">
+      <c r="P2" s="6">
         <v>10</v>
       </c>
-      <c r="P2" s="7">
+      <c r="Q2" s="7">
         <v>10</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="R2" s="5">
         <v>11</v>
       </c>
-      <c r="R2" s="6">
+      <c r="S2" s="6">
         <v>11</v>
       </c>
-      <c r="S2" s="7">
+      <c r="T2" s="7">
         <v>11</v>
       </c>
-      <c r="T2" s="6">
+      <c r="U2" s="6">
         <v>12</v>
       </c>
-      <c r="U2" s="5">
+      <c r="V2" s="5">
         <v>12</v>
       </c>
-      <c r="V2" s="7">
+      <c r="W2" s="7">
         <v>12</v>
       </c>
-      <c r="W2" s="5">
+      <c r="X2" s="5">
         <v>1</v>
       </c>
-      <c r="X2" s="6">
+      <c r="Y2" s="6">
         <v>1</v>
       </c>
-      <c r="Y2" s="7">
+      <c r="Z2" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -2665,7 +2671,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>77</v>
       </c>
@@ -2676,7 +2682,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>162</v>
       </c>
@@ -2687,7 +2693,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>176</v>
       </c>
@@ -2698,7 +2704,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>144</v>
       </c>
@@ -2709,7 +2715,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>188</v>
       </c>
@@ -2720,7 +2726,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2731,7 +2737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>91</v>
       </c>
@@ -2742,7 +2748,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>513</v>
       </c>
@@ -2753,7 +2759,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>199</v>
       </c>
@@ -2764,7 +2770,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>119</v>
       </c>
@@ -2775,7 +2781,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>119</v>
       </c>
@@ -2786,7 +2792,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>119</v>
       </c>
@@ -2797,7 +2803,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>119</v>
       </c>
@@ -5096,7 +5102,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>176</v>
       </c>
@@ -5107,7 +5113,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>176</v>
       </c>
@@ -5118,7 +5124,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>176</v>
       </c>
@@ -5129,7 +5135,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>176</v>
       </c>
@@ -5140,7 +5146,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>176</v>
       </c>
@@ -5150,11 +5156,11 @@
       <c r="C229" t="s">
         <v>231</v>
       </c>
-      <c r="H229" t="s">
+      <c r="I229" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>322</v>
       </c>
@@ -5165,7 +5171,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>322</v>
       </c>
@@ -5176,7 +5182,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>173</v>
       </c>
@@ -5187,7 +5193,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>173</v>
       </c>
@@ -5198,7 +5204,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>173</v>
       </c>
@@ -5209,7 +5215,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>173</v>
       </c>
@@ -5220,7 +5226,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>173</v>
       </c>
@@ -5231,7 +5237,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>141</v>
       </c>
@@ -5242,7 +5248,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>141</v>
       </c>
@@ -5253,7 +5259,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>141</v>
       </c>
@@ -5264,7 +5270,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>141</v>
       </c>
@@ -6097,13 +6103,13 @@
     <protectedRange sqref="B300:C300" name="区域1_27_2_4" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1129)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1131)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1172)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1178)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1181)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1182)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1184)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1239)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1265)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1381)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1408)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1410)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1392)"/>
     <protectedRange sqref="C310" name="区域1_22_2_1_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1129)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1131)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1172)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1178)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1181)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1182)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1184)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1239)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1265)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1381)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1408)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1410)(A;;CC;;;S-1-5-21-1389180225-3847734526-4071883183-1392)"/>
   </protectedRanges>
-  <autoFilter ref="A2:Y314" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:Z314" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C149:D175 C1:D147 C177:D1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="C149:E175 C1:E147 C177:E1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
